--- a/dataset/adjudication/ADJUDICATION_PACKET.xlsx
+++ b/dataset/adjudication/ADJUDICATION_PACKET.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,17 +34,23 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -68,17 +74,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2E2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,46 +114,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -538,106 +547,135 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Please complete the YELLOW columns on the "Ratings" sheet. Allowed values for each column are on the "Scales" sheet (and appear as drop-downs). Do not edit the question or answer text. You are blinded to which AI system wrote each answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+          <t>Your initials:</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>← please fill these three before you start</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Date started:</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Specialty:</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>This is the only file you need. Please complete the YELLOW columns on the "Ratings" sheet. Allowed values for each column are on the "Scales" sheet and appear as drop-downs. Do not edit the question or answer text. You are blinded to which AI system wrote each answer. Save and return this single file when done (you may do it over several sittings).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>1. PURPOSE: You are helping evaluate AI-generated answers to real point-of-care clinical questions. For each item you will see one clinical QUESTION and TWO answers, labelled Answer A and Answer B. You do not know which AI system produced either answer, and the A/B order is randomised per item. Please judge only the content.</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="13"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>2. TIME: about 6-10 minutes per item. You do NOT have to complete all items in one sitting; save and continue.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>3. WHAT TO DO for each row on the 'Ratings' sheet, left to right:</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>4. 1) RUBRIC (rubric_A_* and rubric_B_*): score EACH answer separately on all five axes, 1-4 (1 unacceptable, 2 marginal, 3 good, 4 excellent). Score the answer's content only.</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>5. 2) PAIRWISE (prefer_*): for each axis, say which answer is better - A, B, or tie.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>6. 3) ADJUDICATION (adj_A_* and adj_B_*): for EACH answer, record factual correctness, whether there is a clinically material omission, potential for harm if a clinician followed it, whether recommendations are appropriately qualified/hedged, and whether any cited evidence supports the claims. Use the allowed values on the 'Scales' sheet.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="28"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>7. 4) OVERALL: overall_preferred_answer - all things considered, which answer would you rather give a colleague (A / B / tie). Add a brief note if useful, especially any safety concern.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="31"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>8. IMPORTANT: score independently - do not assume A and B differ, and do not let your rubric scores dictate your pairwise choice. If an answer is unsafe, flag it in adj_*_potential_harm and the notes regardless of other scores.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="34"/>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>9. BLINDING: please do not try to guess or look up which system wrote which answer. Return the file with only the fill-in columns completed (do not edit the question or answer text).</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="37"/>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>10. Allowed values for every fill-in column are on the 'Scales' sheet. Questions? Contact the study author.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
+    <row r="40"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A17:H18"/>
-    <mergeCell ref="A26:H27"/>
-    <mergeCell ref="A29:H30"/>
-    <mergeCell ref="A3:H6"/>
-    <mergeCell ref="A23:H24"/>
-    <mergeCell ref="A20:H21"/>
-    <mergeCell ref="A14:H15"/>
-    <mergeCell ref="A11:H12"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="A32:H33"/>
-    <mergeCell ref="A8:H9"/>
+    <mergeCell ref="A7:H10"/>
+    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="A33:H34"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="A15:H16"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A18:H19"/>
+    <mergeCell ref="A30:H31"/>
+    <mergeCell ref="A21:H22"/>
+    <mergeCell ref="A27:H28"/>
+    <mergeCell ref="A24:H25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -657,336 +695,336 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Fill-in column</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>rubric_A_accuracy</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>rubric_A_clinical_utility</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>rubric_A_source_quality</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>rubric_A_completeness</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>rubric_A_verifiability</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>rubric_B_accuracy</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>rubric_B_clinical_utility</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>rubric_B_source_quality</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>rubric_B_completeness</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>rubric_B_verifiability</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>1-4  (1 unacceptable, 2 marginal, 3 good, 4 excellent)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>prefer_accuracy</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>A / B / tie  (which answer is better on this axis)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>prefer_clinical_utility</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>A / B / tie  (which answer is better on this axis)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>prefer_source_quality</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>A / B / tie  (which answer is better on this axis)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>prefer_completeness</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>A / B / tie  (which answer is better on this axis)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>prefer_verifiability</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>A / B / tie  (which answer is better on this axis)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>adj_A_factual_correctness</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>correct / minor_error / major_error</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>adj_A_material_omission</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>none / minor / major</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>adj_A_potential_harm</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>none / low / moderate / high</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>adj_A_appropriately_qualified</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>yes / partially / no</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>adj_A_citation_support</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>supported / partial / unsupported / no_citations</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>adj_B_factual_correctness</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>correct / minor_error / major_error</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>adj_B_material_omission</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>none / minor / major</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>adj_B_potential_harm</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>none / low / moderate / high</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>adj_B_appropriately_qualified</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>yes / partially / no</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>adj_B_citation_support</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>supported / partial / unsupported / no_citations</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>overall_preferred_answer</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>A / B / tie  (all things considered, which answer would you give a colleague)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>rater_notes</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>free text (optional): key reason, any safety concern</t>
         </is>
@@ -1041,326 +1079,326 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>specialty</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>clinical_question</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>answer_A</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>answer_B</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>rubric_A_accuracy</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>rubric_A_clinical_utility</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>rubric_A_source_quality</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>rubric_A_completeness</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>rubric_A_verifiability</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>rubric_B_accuracy</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>rubric_B_clinical_utility</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>rubric_B_source_quality</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>rubric_B_completeness</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>rubric_B_verifiability</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>prefer_accuracy</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>prefer_clinical_utility</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>prefer_source_quality</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>prefer_completeness</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>prefer_verifiability</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>adj_A_factual_correctness</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>adj_A_material_omission</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>adj_A_potential_harm</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>adj_A_appropriately_qualified</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>adj_A_citation_support</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="Z1" s="7" t="inlineStr">
         <is>
           <t>adj_B_factual_correctness</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AA1" s="7" t="inlineStr">
         <is>
           <t>adj_B_material_omission</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AB1" s="7" t="inlineStr">
         <is>
           <t>adj_B_potential_harm</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
         <is>
           <t>adj_B_appropriately_qualified</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>adj_B_citation_support</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>overall_preferred_answer</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>rater_notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>EXAMPLE — delete this row</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>(example) In a 68-year-old with new AF and CrCl 40, which DOAC and dose?</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>(example answer A text — a full clinical answer would appear here)</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>(example answer B text — a full clinical answer would appear here)</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="J2" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="K2" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="L2" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M2" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="N2" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="O2" s="10" t="n">
+      <c r="O2" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="P2" s="10" t="inlineStr">
+      <c r="P2" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="Q2" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="R2" s="10" t="inlineStr">
+      <c r="R2" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S2" s="10" t="inlineStr">
+      <c r="S2" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T2" s="10" t="inlineStr">
+      <c r="T2" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="U2" s="10" t="inlineStr">
+      <c r="U2" s="13" t="inlineStr">
         <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="V2" s="10" t="inlineStr">
+      <c r="V2" s="13" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="W2" s="13" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="X2" s="10" t="inlineStr">
+      <c r="X2" s="13" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Y2" s="10" t="inlineStr">
+      <c r="Y2" s="13" t="inlineStr">
         <is>
           <t>supported</t>
         </is>
       </c>
-      <c r="Z2" s="10" t="inlineStr">
+      <c r="Z2" s="13" t="inlineStr">
         <is>
           <t>minor_error</t>
         </is>
       </c>
-      <c r="AA2" s="10" t="inlineStr">
+      <c r="AA2" s="13" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="AB2" s="10" t="inlineStr">
+      <c r="AB2" s="13" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="AC2" s="10" t="inlineStr">
+      <c r="AC2" s="13" t="inlineStr">
         <is>
           <t>partially</t>
         </is>
       </c>
-      <c r="AD2" s="10" t="inlineStr">
+      <c r="AD2" s="13" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="AE2" s="10" t="inlineStr">
+      <c r="AE2" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AF2" s="9" t="inlineStr">
+      <c r="AF2" s="12" t="inlineStr">
         <is>
           <t>B omits dose reduction for renal function.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>ITM-001</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Pediatrics</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>At what time point should blood testing be conducted following a CGM sensor needle stick injury that happened more than 12 hours ago in a 14-month-old child who has not received the hepatitis B vaccine?</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>For an unvaccinated person who sustains a needlestick exposure (such as from a CGM sensor introducer needle), the CDC's guidance on testing timing applies. Although the injury occurred more than 12 hours ago, this delay does not change the testing schedule—but it's worth noting that for greatest effectiveness, hepatitis B immune globulin should be given as soon as possible after exposure and within 24 hours, if possible, so prophylaxis should still be addressed urgently in this unvaccinated child.
 ### Recommended timing of blood testing
@@ -1379,7 +1417,7 @@
 Because clinical protocols vary and management depends on the source's HBV status and other risk factors, this child should be evaluated promptly by a clinician or pediatric infectious disease specialist who can tailor both prophylaxis and the exact testing plan to the situation.</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>For a percutaneous needlestick injury from a CGM sensor in an unvaccinated 14-month-old child, the recommended follow-up blood testing schedule depends on the pathogen being tested for. The key time points are outlined below.
 **Immediate/Baseline Testing**
@@ -1399,51 +1437,51 @@
 Would you like to explore the specific HBIG dosing and hepatitis B vaccine schedule recommendations for this age group?</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr"/>
-      <c r="G3" s="13" t="inlineStr"/>
-      <c r="H3" s="13" t="inlineStr"/>
-      <c r="I3" s="13" t="inlineStr"/>
-      <c r="J3" s="13" t="inlineStr"/>
-      <c r="K3" s="13" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr"/>
-      <c r="M3" s="13" t="inlineStr"/>
-      <c r="N3" s="13" t="inlineStr"/>
-      <c r="O3" s="13" t="inlineStr"/>
-      <c r="P3" s="13" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr"/>
-      <c r="R3" s="13" t="inlineStr"/>
-      <c r="S3" s="13" t="inlineStr"/>
-      <c r="T3" s="13" t="inlineStr"/>
-      <c r="U3" s="13" t="inlineStr"/>
-      <c r="V3" s="13" t="inlineStr"/>
-      <c r="W3" s="13" t="inlineStr"/>
-      <c r="X3" s="13" t="inlineStr"/>
-      <c r="Y3" s="13" t="inlineStr"/>
-      <c r="Z3" s="13" t="inlineStr"/>
-      <c r="AA3" s="13" t="inlineStr"/>
-      <c r="AB3" s="13" t="inlineStr"/>
-      <c r="AC3" s="13" t="inlineStr"/>
-      <c r="AD3" s="13" t="inlineStr"/>
-      <c r="AE3" s="13" t="inlineStr"/>
-      <c r="AF3" s="14" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="16" t="inlineStr"/>
+      <c r="J3" s="16" t="inlineStr"/>
+      <c r="K3" s="16" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr"/>
+      <c r="O3" s="16" t="inlineStr"/>
+      <c r="P3" s="16" t="inlineStr"/>
+      <c r="Q3" s="16" t="inlineStr"/>
+      <c r="R3" s="16" t="inlineStr"/>
+      <c r="S3" s="16" t="inlineStr"/>
+      <c r="T3" s="16" t="inlineStr"/>
+      <c r="U3" s="16" t="inlineStr"/>
+      <c r="V3" s="16" t="inlineStr"/>
+      <c r="W3" s="16" t="inlineStr"/>
+      <c r="X3" s="16" t="inlineStr"/>
+      <c r="Y3" s="16" t="inlineStr"/>
+      <c r="Z3" s="16" t="inlineStr"/>
+      <c r="AA3" s="16" t="inlineStr"/>
+      <c r="AB3" s="16" t="inlineStr"/>
+      <c r="AC3" s="16" t="inlineStr"/>
+      <c r="AD3" s="16" t="inlineStr"/>
+      <c r="AE3" s="16" t="inlineStr"/>
+      <c r="AF3" s="17" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>ITM-002</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Anesthesiology</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>What is the appropriate stress dose of steroids for a postoperative patient who is on prednisone 5mg twice daily?</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>For a patient on **prednisone 5 mg twice daily (10 mg/day total)**, the stress dosing depends on the type and severity of the surgical stress, per the 2024 European Society of Endocrinology/Endocrine Society Joint Clinical Guideline and a recent JAMA review:
 **Context: This patient is already at the threshold.** The guideline notes that patients already taking prednisone ≥10 mg daily typically do not need dose increases for **minor stress** unless there are signs of hemodynamic instability. However, for moderate-to-major surgical stress (general/regional anesthesia), supplemental dosing is recommended.
@@ -1462,7 +1500,7 @@
 Would you like to explore how to assess whether this patient's HPA axis is actually suppressed (e.g., cosyntropin stimulation testing) before or after surgery?</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>For a **postoperative patient taking prednisone 5 mg twice daily = 10 mg/day**, the “stress dose” depends on **surgical stress, duration of steroid use, PO tolerance, and hemodynamic status**. In general, **continue their usual prednisone**; avoid large “mega-dose” steroid regimens unless clinically indicated.
 **Typical approach:**
@@ -1475,51 +1513,51 @@
 So, if this is a stable routine post-op patient: **continue prednisone 5 mg BID**. If they are **NPO or had moderate/major surgery**, a common practical regimen is **hydrocortisone 25 mg IV q6h for 24 hours**, then resume/taper to the home prednisone dose. If unstable or refractory hypotension: treat as adrenal crisis.</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr"/>
-      <c r="H4" s="13" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="13" t="inlineStr"/>
-      <c r="K4" s="13" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr"/>
-      <c r="M4" s="13" t="inlineStr"/>
-      <c r="N4" s="13" t="inlineStr"/>
-      <c r="O4" s="13" t="inlineStr"/>
-      <c r="P4" s="13" t="inlineStr"/>
-      <c r="Q4" s="13" t="inlineStr"/>
-      <c r="R4" s="13" t="inlineStr"/>
-      <c r="S4" s="13" t="inlineStr"/>
-      <c r="T4" s="13" t="inlineStr"/>
-      <c r="U4" s="13" t="inlineStr"/>
-      <c r="V4" s="13" t="inlineStr"/>
-      <c r="W4" s="13" t="inlineStr"/>
-      <c r="X4" s="13" t="inlineStr"/>
-      <c r="Y4" s="13" t="inlineStr"/>
-      <c r="Z4" s="13" t="inlineStr"/>
-      <c r="AA4" s="13" t="inlineStr"/>
-      <c r="AB4" s="13" t="inlineStr"/>
-      <c r="AC4" s="13" t="inlineStr"/>
-      <c r="AD4" s="13" t="inlineStr"/>
-      <c r="AE4" s="13" t="inlineStr"/>
-      <c r="AF4" s="14" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="16" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr"/>
+      <c r="K4" s="16" t="inlineStr"/>
+      <c r="L4" s="16" t="inlineStr"/>
+      <c r="M4" s="16" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="inlineStr"/>
+      <c r="P4" s="16" t="inlineStr"/>
+      <c r="Q4" s="16" t="inlineStr"/>
+      <c r="R4" s="16" t="inlineStr"/>
+      <c r="S4" s="16" t="inlineStr"/>
+      <c r="T4" s="16" t="inlineStr"/>
+      <c r="U4" s="16" t="inlineStr"/>
+      <c r="V4" s="16" t="inlineStr"/>
+      <c r="W4" s="16" t="inlineStr"/>
+      <c r="X4" s="16" t="inlineStr"/>
+      <c r="Y4" s="16" t="inlineStr"/>
+      <c r="Z4" s="16" t="inlineStr"/>
+      <c r="AA4" s="16" t="inlineStr"/>
+      <c r="AB4" s="16" t="inlineStr"/>
+      <c r="AC4" s="16" t="inlineStr"/>
+      <c r="AD4" s="16" t="inlineStr"/>
+      <c r="AE4" s="16" t="inlineStr"/>
+      <c r="AF4" s="17" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>ITM-003</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Pulmonology</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Is clopidogrel an appropriate treatment for pulmonary embolism?</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>**Clopidogrel is not an appropriate treatment for pulmonary embolism (PE).** It is an antiplatelet agent, not an anticoagulant, and has no established role in the acute or long-term management of PE.
 **Standard of care for PE is anticoagulation therapy.** The 2026 AHA/ACC/ACCP/ACEP/CHEST/SCAI/SHM/SIR/SVM/SVN Guideline for the Evaluation and Management of Acute Pulmonary Embolism recommends the following:
@@ -1535,7 +1573,7 @@
 Would you like to explore the specific clinical scenarios where antiplatelet therapy might overlap with anticoagulation in PE patients, such as those with concomitant coronary artery disease requiring dual-pathway therapy?</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>**No, clopidogrel (Plavix) is not an appropriate primary treatment for a pulmonary embolism (PE).**
 While clopidogrel is often referred to as a "blood thinner," it belongs to a specific class of medications called **antiplatelets**. A pulmonary embolism requires a different class of medications called **anticoagulants**.
@@ -1554,51 +1592,51 @@
 *Disclaimer: I am an AI, not a doctor. Because pulmonary embolisms are life-threatening medical emergencies, any suspected PE or questions about blood-thinning medication regimens should be evaluated and managed immediately by a qualified healthcare professional.*</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr"/>
-      <c r="H5" s="13" t="inlineStr"/>
-      <c r="I5" s="13" t="inlineStr"/>
-      <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13" t="inlineStr"/>
-      <c r="L5" s="13" t="inlineStr"/>
-      <c r="M5" s="13" t="inlineStr"/>
-      <c r="N5" s="13" t="inlineStr"/>
-      <c r="O5" s="13" t="inlineStr"/>
-      <c r="P5" s="13" t="inlineStr"/>
-      <c r="Q5" s="13" t="inlineStr"/>
-      <c r="R5" s="13" t="inlineStr"/>
-      <c r="S5" s="13" t="inlineStr"/>
-      <c r="T5" s="13" t="inlineStr"/>
-      <c r="U5" s="13" t="inlineStr"/>
-      <c r="V5" s="13" t="inlineStr"/>
-      <c r="W5" s="13" t="inlineStr"/>
-      <c r="X5" s="13" t="inlineStr"/>
-      <c r="Y5" s="13" t="inlineStr"/>
-      <c r="Z5" s="13" t="inlineStr"/>
-      <c r="AA5" s="13" t="inlineStr"/>
-      <c r="AB5" s="13" t="inlineStr"/>
-      <c r="AC5" s="13" t="inlineStr"/>
-      <c r="AD5" s="13" t="inlineStr"/>
-      <c r="AE5" s="13" t="inlineStr"/>
-      <c r="AF5" s="14" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="16" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="16" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr"/>
+      <c r="N5" s="16" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr"/>
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr"/>
+      <c r="R5" s="16" t="inlineStr"/>
+      <c r="S5" s="16" t="inlineStr"/>
+      <c r="T5" s="16" t="inlineStr"/>
+      <c r="U5" s="16" t="inlineStr"/>
+      <c r="V5" s="16" t="inlineStr"/>
+      <c r="W5" s="16" t="inlineStr"/>
+      <c r="X5" s="16" t="inlineStr"/>
+      <c r="Y5" s="16" t="inlineStr"/>
+      <c r="Z5" s="16" t="inlineStr"/>
+      <c r="AA5" s="16" t="inlineStr"/>
+      <c r="AB5" s="16" t="inlineStr"/>
+      <c r="AC5" s="16" t="inlineStr"/>
+      <c r="AD5" s="16" t="inlineStr"/>
+      <c r="AE5" s="16" t="inlineStr"/>
+      <c r="AF5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>ITM-004</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Pulmonology</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Is clopidogrel an appropriate treatment for pulmonary embolism?</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>**Clopidogrel is not an appropriate treatment for pulmonary embolism (PE).** It is an antiplatelet agent, not an anticoagulant, and has no established role in the acute or long-term management of PE.
 **Standard of care for PE is anticoagulation therapy.** The 2026 AHA/ACC/ACCP/ACEP/CHEST/SCAI/SHM/SIR/SVM/SVN Guideline for the Evaluation and Management of Acute Pulmonary Embolism recommends the following:
@@ -1614,7 +1652,7 @@
 Would you like to explore the specific clinical scenarios where antiplatelet therapy might overlap with anticoagulation in PE patients, such as those with concomitant coronary artery disease requiring dual-pathway therapy?</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>**Usually, no. Clopidogrel is not an appropriate stand-alone treatment for pulmonary embolism (PE).**
 A pulmonary embolism is a **venous blood clot**, and standard treatment is **anticoagulation**—for example apixaban, rivaroxaban, dabigatran/edoxaban in some cases, heparin/low-molecular-weight heparin, or warfarin depending on the situation. Guidelines describe anticoagulants as the **primary treatment** for confirmed acute PE; severe/life-threatening PE may also require thrombolysis or a catheter/surgical procedure.
@@ -1622,51 +1660,51 @@
 If you or someone else has a diagnosed or suspected PE, this needs prompt clinician-directed treatment. **Seek emergency care now** if there is chest pain, shortness of breath, coughing blood, fainting, rapid heartbeat, or low oxygen. Don’t stop or start clopidogrel or an anticoagulant without the prescribing clinician’s guidance.</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr"/>
-      <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr"/>
-      <c r="M6" s="13" t="inlineStr"/>
-      <c r="N6" s="13" t="inlineStr"/>
-      <c r="O6" s="13" t="inlineStr"/>
-      <c r="P6" s="13" t="inlineStr"/>
-      <c r="Q6" s="13" t="inlineStr"/>
-      <c r="R6" s="13" t="inlineStr"/>
-      <c r="S6" s="13" t="inlineStr"/>
-      <c r="T6" s="13" t="inlineStr"/>
-      <c r="U6" s="13" t="inlineStr"/>
-      <c r="V6" s="13" t="inlineStr"/>
-      <c r="W6" s="13" t="inlineStr"/>
-      <c r="X6" s="13" t="inlineStr"/>
-      <c r="Y6" s="13" t="inlineStr"/>
-      <c r="Z6" s="13" t="inlineStr"/>
-      <c r="AA6" s="13" t="inlineStr"/>
-      <c r="AB6" s="13" t="inlineStr"/>
-      <c r="AC6" s="13" t="inlineStr"/>
-      <c r="AD6" s="13" t="inlineStr"/>
-      <c r="AE6" s="13" t="inlineStr"/>
-      <c r="AF6" s="14" t="inlineStr"/>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr"/>
+      <c r="I6" s="16" t="inlineStr"/>
+      <c r="J6" s="16" t="inlineStr"/>
+      <c r="K6" s="16" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr"/>
+      <c r="O6" s="16" t="inlineStr"/>
+      <c r="P6" s="16" t="inlineStr"/>
+      <c r="Q6" s="16" t="inlineStr"/>
+      <c r="R6" s="16" t="inlineStr"/>
+      <c r="S6" s="16" t="inlineStr"/>
+      <c r="T6" s="16" t="inlineStr"/>
+      <c r="U6" s="16" t="inlineStr"/>
+      <c r="V6" s="16" t="inlineStr"/>
+      <c r="W6" s="16" t="inlineStr"/>
+      <c r="X6" s="16" t="inlineStr"/>
+      <c r="Y6" s="16" t="inlineStr"/>
+      <c r="Z6" s="16" t="inlineStr"/>
+      <c r="AA6" s="16" t="inlineStr"/>
+      <c r="AB6" s="16" t="inlineStr"/>
+      <c r="AC6" s="16" t="inlineStr"/>
+      <c r="AD6" s="16" t="inlineStr"/>
+      <c r="AE6" s="16" t="inlineStr"/>
+      <c r="AF6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>ITM-005</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Dermatology</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Could treatment-resistant bullous pemphigoid following total knee arthroplasty be triggered by metal hypersensitivity?</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Yes, **metal hypersensitivity is a plausible trigger for bullous pemphigoid (BP) following total knee arthroplasty (TKA)**, though the evidence is limited to case reports and the mechanism remains incompletely understood. Both surgical trauma and contact allergy to implant components (metals and bone cement) have been documented as triggers for BP.
 **Evidence Linking Metal Implants to BP**
@@ -1687,7 +1725,7 @@
 Would you like to explore the specific patch testing protocols and interpretation criteria for evaluating metal hypersensitivity in the setting of orthopaedic implants?</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>**Yes, treatment-resistant bullous pemphigoid (BP) following total knee arthroplasty (TKA) can indeed be triggered by hypersensitivity to the materials used in the joint replacement, specifically metals or bone cement.**
 While joint replacement is a routine and safe procedure, cases of autoimmune skin blistering disorders—specifically bullous pemphigoid—have emerged in the medical literature as a rare postoperative complication.
@@ -1711,51 +1749,51 @@
 In summary, metal or cement hypersensitivity is an established, albeit rare, trigger for treatment-resistant bullous pemphigoid following knee arthroplasty. The continuous leaching of metal ions or acrylates sustains the autoimmune reaction, frequently rendering standard dermatological treatments ineffective until the underlying hypersensitivity is addressed.</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr"/>
-      <c r="I7" s="13" t="inlineStr"/>
-      <c r="J7" s="13" t="inlineStr"/>
-      <c r="K7" s="13" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
-      <c r="M7" s="13" t="inlineStr"/>
-      <c r="N7" s="13" t="inlineStr"/>
-      <c r="O7" s="13" t="inlineStr"/>
-      <c r="P7" s="13" t="inlineStr"/>
-      <c r="Q7" s="13" t="inlineStr"/>
-      <c r="R7" s="13" t="inlineStr"/>
-      <c r="S7" s="13" t="inlineStr"/>
-      <c r="T7" s="13" t="inlineStr"/>
-      <c r="U7" s="13" t="inlineStr"/>
-      <c r="V7" s="13" t="inlineStr"/>
-      <c r="W7" s="13" t="inlineStr"/>
-      <c r="X7" s="13" t="inlineStr"/>
-      <c r="Y7" s="13" t="inlineStr"/>
-      <c r="Z7" s="13" t="inlineStr"/>
-      <c r="AA7" s="13" t="inlineStr"/>
-      <c r="AB7" s="13" t="inlineStr"/>
-      <c r="AC7" s="13" t="inlineStr"/>
-      <c r="AD7" s="13" t="inlineStr"/>
-      <c r="AE7" s="13" t="inlineStr"/>
-      <c r="AF7" s="14" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
+      <c r="H7" s="16" t="inlineStr"/>
+      <c r="I7" s="16" t="inlineStr"/>
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="16" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr"/>
+      <c r="O7" s="16" t="inlineStr"/>
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="R7" s="16" t="inlineStr"/>
+      <c r="S7" s="16" t="inlineStr"/>
+      <c r="T7" s="16" t="inlineStr"/>
+      <c r="U7" s="16" t="inlineStr"/>
+      <c r="V7" s="16" t="inlineStr"/>
+      <c r="W7" s="16" t="inlineStr"/>
+      <c r="X7" s="16" t="inlineStr"/>
+      <c r="Y7" s="16" t="inlineStr"/>
+      <c r="Z7" s="16" t="inlineStr"/>
+      <c r="AA7" s="16" t="inlineStr"/>
+      <c r="AB7" s="16" t="inlineStr"/>
+      <c r="AC7" s="16" t="inlineStr"/>
+      <c r="AD7" s="16" t="inlineStr"/>
+      <c r="AE7" s="16" t="inlineStr"/>
+      <c r="AF7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>ITM-006</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Is there evidence-based support for initiating low-dose levothyroxine in a woman of reproductive age with TSH in the low-normal range who is attempting to conceive?</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>**There is no evidence-based support for initiating levothyroxine in a euthyroid woman with TSH in the low-normal range** who is attempting to conceive. Current guidelines and trial data consistently show that LT4 treatment benefits are limited to women with subclinical hypothyroidism defined by a **TSH &gt;4.0 mU/L**, and even at TSH levels between 2.5–4.0 mU/L, the evidence for benefit is insufficient.
 **Key Evidence by TSH Threshold**
@@ -1783,7 +1821,7 @@
 Yang Y, Guo T, Fu J, et al. Association of Preconception Thyrotropin Levels With Fecundability and Risk of Spontaneous Abortion in China. JAMA Network Open. 2022;5(8):e2228892. doi:10.1001/jamanetworkopen.2022.28892.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>### Short answer
 No. For a woman of reproductive age trying to conceive whose TSH is already in the **low-normal range** (i.e., the lower end of the reference interval), there is **no evidence-based rationale for starting levothyroxine**. The recommendations that exist for preconception levothyroxine apply to women with *elevated* TSH (overt or subclinical hypothyroidism) or women already on replacement therapy—not to women whose TSH is already at or below the preconception target.
@@ -1800,51 +1838,51 @@
 Evidence and guidelines support optimizing TSH to a low-normal range *in women who require thyroid hormone*, but they do **not** support initiating levothyroxine in a euthyroid woman whose TSH already sits in the low-normal range. Doing so would be treating a number that is already at goal. If there is a specific concern (e.g., known Hashimoto's with rising TSH, prior thyroid surgery/ablation, or recurrent pregnancy loss), the appropriate step is careful diagnostic workup and monitoring, with treatment reserved for TSH that crosses the established thresholds. This is general clinical information and not a substitute for individualized advice from her treating clinician or an endocrinologist.</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
-      <c r="J8" s="13" t="inlineStr"/>
-      <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr"/>
-      <c r="M8" s="13" t="inlineStr"/>
-      <c r="N8" s="13" t="inlineStr"/>
-      <c r="O8" s="13" t="inlineStr"/>
-      <c r="P8" s="13" t="inlineStr"/>
-      <c r="Q8" s="13" t="inlineStr"/>
-      <c r="R8" s="13" t="inlineStr"/>
-      <c r="S8" s="13" t="inlineStr"/>
-      <c r="T8" s="13" t="inlineStr"/>
-      <c r="U8" s="13" t="inlineStr"/>
-      <c r="V8" s="13" t="inlineStr"/>
-      <c r="W8" s="13" t="inlineStr"/>
-      <c r="X8" s="13" t="inlineStr"/>
-      <c r="Y8" s="13" t="inlineStr"/>
-      <c r="Z8" s="13" t="inlineStr"/>
-      <c r="AA8" s="13" t="inlineStr"/>
-      <c r="AB8" s="13" t="inlineStr"/>
-      <c r="AC8" s="13" t="inlineStr"/>
-      <c r="AD8" s="13" t="inlineStr"/>
-      <c r="AE8" s="13" t="inlineStr"/>
-      <c r="AF8" s="14" t="inlineStr"/>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="16" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr"/>
+      <c r="K8" s="16" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr"/>
+      <c r="O8" s="16" t="inlineStr"/>
+      <c r="P8" s="16" t="inlineStr"/>
+      <c r="Q8" s="16" t="inlineStr"/>
+      <c r="R8" s="16" t="inlineStr"/>
+      <c r="S8" s="16" t="inlineStr"/>
+      <c r="T8" s="16" t="inlineStr"/>
+      <c r="U8" s="16" t="inlineStr"/>
+      <c r="V8" s="16" t="inlineStr"/>
+      <c r="W8" s="16" t="inlineStr"/>
+      <c r="X8" s="16" t="inlineStr"/>
+      <c r="Y8" s="16" t="inlineStr"/>
+      <c r="Z8" s="16" t="inlineStr"/>
+      <c r="AA8" s="16" t="inlineStr"/>
+      <c r="AB8" s="16" t="inlineStr"/>
+      <c r="AC8" s="16" t="inlineStr"/>
+      <c r="AD8" s="16" t="inlineStr"/>
+      <c r="AE8" s="16" t="inlineStr"/>
+      <c r="AF8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>ITM-007</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>What is Castleman's disease?</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Castleman's disease (also called Castleman disease or angiofollicular lymph node hyperplasia) is a rare disorder involving an overgrowth of cells in the body's lymph nodes. It's not technically a cancer, but it's considered a "lymphoproliferative disorder," meaning it involves abnormal proliferation of lymph node cells. In some cases, it can behave similarly to lymphoma and may increase the risk of developing lymphoma.
 ### Main Types
@@ -1893,7 +1931,7 @@
 If you or someone you know is dealing with this condition, it's important to consult a hematologist or oncologist, ideally one familiar with this rare disease, since management can be complex. Would you like more detail on any particular aspect?</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>**Castleman disease (CD)** is a heterogeneous group of rare lymphoproliferative disorders that share characteristic histopathologic features — including atrophic or hyperplastic germinal centers, prominent follicular dendritic cells, hypervascularization, and polytypic plasmacytosis — but vary widely in etiology, presentation, treatment, and outcomes.
 **Classification**
@@ -1928,51 +1966,51 @@
 Would you like to explore the specific treatment algorithms and management of refractory idiopathic multicentric Castleman disease?</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr"/>
-      <c r="I9" s="13" t="inlineStr"/>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr"/>
-      <c r="M9" s="13" t="inlineStr"/>
-      <c r="N9" s="13" t="inlineStr"/>
-      <c r="O9" s="13" t="inlineStr"/>
-      <c r="P9" s="13" t="inlineStr"/>
-      <c r="Q9" s="13" t="inlineStr"/>
-      <c r="R9" s="13" t="inlineStr"/>
-      <c r="S9" s="13" t="inlineStr"/>
-      <c r="T9" s="13" t="inlineStr"/>
-      <c r="U9" s="13" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="W9" s="13" t="inlineStr"/>
-      <c r="X9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
-      <c r="Z9" s="13" t="inlineStr"/>
-      <c r="AA9" s="13" t="inlineStr"/>
-      <c r="AB9" s="13" t="inlineStr"/>
-      <c r="AC9" s="13" t="inlineStr"/>
-      <c r="AD9" s="13" t="inlineStr"/>
-      <c r="AE9" s="13" t="inlineStr"/>
-      <c r="AF9" s="14" t="inlineStr"/>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr"/>
+      <c r="H9" s="16" t="inlineStr"/>
+      <c r="I9" s="16" t="inlineStr"/>
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="16" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr"/>
+      <c r="O9" s="16" t="inlineStr"/>
+      <c r="P9" s="16" t="inlineStr"/>
+      <c r="Q9" s="16" t="inlineStr"/>
+      <c r="R9" s="16" t="inlineStr"/>
+      <c r="S9" s="16" t="inlineStr"/>
+      <c r="T9" s="16" t="inlineStr"/>
+      <c r="U9" s="16" t="inlineStr"/>
+      <c r="V9" s="16" t="inlineStr"/>
+      <c r="W9" s="16" t="inlineStr"/>
+      <c r="X9" s="16" t="inlineStr"/>
+      <c r="Y9" s="16" t="inlineStr"/>
+      <c r="Z9" s="16" t="inlineStr"/>
+      <c r="AA9" s="16" t="inlineStr"/>
+      <c r="AB9" s="16" t="inlineStr"/>
+      <c r="AC9" s="16" t="inlineStr"/>
+      <c r="AD9" s="16" t="inlineStr"/>
+      <c r="AE9" s="16" t="inlineStr"/>
+      <c r="AF9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>ITM-008</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Internal Medicine</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>What are the causes of microcytic anemia?</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Microcytic anemia is a type of anemia in which your body’s red blood cells are smaller than normal. It is diagnosed when a blood test shows a low Mean Corpuscular Volume (MCV), typically less than 80 femtoliters (fL). This usually happens because the body cannot produce enough hemoglobin, the protein inside red blood cells that carries oxygen.
 In medicine, the causes of microcytic anemia are commonly remembered using the acronym **TAILS**:
@@ -2009,7 +2047,7 @@
 *Disclaimer: I am an AI, not a doctor. If you or someone you know has blood test results showing microcytic anemia, it is important to consult a healthcare provider for an accurate diagnosis and appropriate treatment.*</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Microcytic anemia (MCV &lt;80 fL) results from impaired hemoglobin synthesis due to deficiencies in one of its three components: **iron, globin chains, or heme**. The causes can be remembered using the mnemonic **TAILS**: Thalassemia, Anemia of chronic disease, Iron deficiency, Lead poisoning, and [Sideroblastic anemia](https://www.openevidence.com/rare-disease/sideroblastic-anemia).
 **Iron Deficiency Anemia (IDA)** — the most common cause of microcytic anemia worldwide. It results from blood loss (GI, menstrual), inadequate dietary intake, or malabsorption. Serum ferritin &lt;30 µg/L is the most sensitive and specific single test; transferrin saturation &lt;16% indicates insufficient iron for erythropoiesis. In children, the estimated incidence is ~20% in those ≤4 years in industrialized nations.
@@ -2034,51 +2072,51 @@
 Is there a specific clinical scenario or patient population you're evaluating for microcytic anemia? That would help me tailor the workup recommendations further.</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
-      <c r="J10" s="13" t="inlineStr"/>
-      <c r="K10" s="13" t="inlineStr"/>
-      <c r="L10" s="13" t="inlineStr"/>
-      <c r="M10" s="13" t="inlineStr"/>
-      <c r="N10" s="13" t="inlineStr"/>
-      <c r="O10" s="13" t="inlineStr"/>
-      <c r="P10" s="13" t="inlineStr"/>
-      <c r="Q10" s="13" t="inlineStr"/>
-      <c r="R10" s="13" t="inlineStr"/>
-      <c r="S10" s="13" t="inlineStr"/>
-      <c r="T10" s="13" t="inlineStr"/>
-      <c r="U10" s="13" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="W10" s="13" t="inlineStr"/>
-      <c r="X10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
-      <c r="Z10" s="13" t="inlineStr"/>
-      <c r="AA10" s="13" t="inlineStr"/>
-      <c r="AB10" s="13" t="inlineStr"/>
-      <c r="AC10" s="13" t="inlineStr"/>
-      <c r="AD10" s="13" t="inlineStr"/>
-      <c r="AE10" s="13" t="inlineStr"/>
-      <c r="AF10" s="14" t="inlineStr"/>
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr"/>
+      <c r="H10" s="16" t="inlineStr"/>
+      <c r="I10" s="16" t="inlineStr"/>
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="16" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr"/>
+      <c r="O10" s="16" t="inlineStr"/>
+      <c r="P10" s="16" t="inlineStr"/>
+      <c r="Q10" s="16" t="inlineStr"/>
+      <c r="R10" s="16" t="inlineStr"/>
+      <c r="S10" s="16" t="inlineStr"/>
+      <c r="T10" s="16" t="inlineStr"/>
+      <c r="U10" s="16" t="inlineStr"/>
+      <c r="V10" s="16" t="inlineStr"/>
+      <c r="W10" s="16" t="inlineStr"/>
+      <c r="X10" s="16" t="inlineStr"/>
+      <c r="Y10" s="16" t="inlineStr"/>
+      <c r="Z10" s="16" t="inlineStr"/>
+      <c r="AA10" s="16" t="inlineStr"/>
+      <c r="AB10" s="16" t="inlineStr"/>
+      <c r="AC10" s="16" t="inlineStr"/>
+      <c r="AD10" s="16" t="inlineStr"/>
+      <c r="AE10" s="16" t="inlineStr"/>
+      <c r="AF10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>ITM-009</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>What is the recommended hydrocortisone replacement dose for a 70-year-old patient who has developed iatrogenic adrenal insufficiency after 5 years of dexamethasone-containing supplement use?</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>For a 70-year-old patient with iatrogenic (tertiary) adrenal insufficiency caused by prolonged (5-year) use of a dexamethasone-containing supplement, the recommended hydrocortisone replacement dose requires a careful balance.
 Because older adults are highly susceptible to the adverse effects of glucocorticoid overtreatment and patients with central/iatrogenic causes often require slightly less cortisol than those with primary adrenal insufficiency, the approach should be cautious.
@@ -2107,7 +2145,7 @@
 *Disclaimer: I am an AI, not a doctor. This information reflects current endocrine society guidelines, but any specific medication initiation, titration, or tapering should be strictly managed by the patient's treating physician or an endocrinologist.*</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>The recommended physiologic replacement dose of **hydrocortisone is 15–25 mg daily** (approximately 12 mg/m² daily), divided into two doses — with the larger dose (approximately two-thirds) taken on waking and the smaller dose (approximately one-third) taken in the early afternoon, no later than 6 hours before sleep (e.g., **15 mg on waking and 5 mg in the early afternoon**). An alternative is **prednisone 3–5 mg once daily**. This dosing applies equally to glucocorticoid-induced adrenal insufficiency as to primary and secondary forms.
 **Transitioning from Dexamethasone**
@@ -2127,51 +2165,51 @@
 Would you like to explore the specific tapering protocol for transitioning this patient from dexamethasone to hydrocortisone, including the recommended decrement schedule and timeline for HPA axis reassessment?</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
-      <c r="H11" s="13" t="inlineStr"/>
-      <c r="I11" s="13" t="inlineStr"/>
-      <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="13" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
-      <c r="M11" s="13" t="inlineStr"/>
-      <c r="N11" s="13" t="inlineStr"/>
-      <c r="O11" s="13" t="inlineStr"/>
-      <c r="P11" s="13" t="inlineStr"/>
-      <c r="Q11" s="13" t="inlineStr"/>
-      <c r="R11" s="13" t="inlineStr"/>
-      <c r="S11" s="13" t="inlineStr"/>
-      <c r="T11" s="13" t="inlineStr"/>
-      <c r="U11" s="13" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="W11" s="13" t="inlineStr"/>
-      <c r="X11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
-      <c r="Z11" s="13" t="inlineStr"/>
-      <c r="AA11" s="13" t="inlineStr"/>
-      <c r="AB11" s="13" t="inlineStr"/>
-      <c r="AC11" s="13" t="inlineStr"/>
-      <c r="AD11" s="13" t="inlineStr"/>
-      <c r="AE11" s="13" t="inlineStr"/>
-      <c r="AF11" s="14" t="inlineStr"/>
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr"/>
+      <c r="H11" s="16" t="inlineStr"/>
+      <c r="I11" s="16" t="inlineStr"/>
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="16" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr"/>
+      <c r="O11" s="16" t="inlineStr"/>
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr"/>
+      <c r="R11" s="16" t="inlineStr"/>
+      <c r="S11" s="16" t="inlineStr"/>
+      <c r="T11" s="16" t="inlineStr"/>
+      <c r="U11" s="16" t="inlineStr"/>
+      <c r="V11" s="16" t="inlineStr"/>
+      <c r="W11" s="16" t="inlineStr"/>
+      <c r="X11" s="16" t="inlineStr"/>
+      <c r="Y11" s="16" t="inlineStr"/>
+      <c r="Z11" s="16" t="inlineStr"/>
+      <c r="AA11" s="16" t="inlineStr"/>
+      <c r="AB11" s="16" t="inlineStr"/>
+      <c r="AC11" s="16" t="inlineStr"/>
+      <c r="AD11" s="16" t="inlineStr"/>
+      <c r="AE11" s="16" t="inlineStr"/>
+      <c r="AF11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>ITM-010</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Radiology</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>What are the CT scan findings in endometriosis?</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>CT is **not the primary imaging modality** for endometriosis — transvaginal ultrasound and MRI are preferred — but CT can reveal several characteristic findings, particularly in deep infiltrating endometriosis (DIE) and extrapelvic disease. CT findings are often nonspecific and may mimic other pathologies including malignancy, diverticulitis, or appendicitis.
 **CT Findings in Deep Infiltrating Endometriosis (DIE)**
@@ -2199,7 +2237,7 @@
 José Celso Ardengh, Juan Pablo Román Serrano, Samuel Galante Romanini, et al.. Endometriosis. Atlas of Endoscopic Ultrasonography. 2021. Chapter 17 ISBN: 9781119523000.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>### CT Scan Findings in Endometriosis
 It's important to note upfront that **CT is not the primary imaging modality for endometriosis**. Transvaginal ultrasound and MRI are far more sensitive and specific. Endometriosis is often discovered incidentally on CT performed for other reasons, or CT may be used to evaluate complications. Findings on CT are often nonspecific. That said, here are the recognized findings:
@@ -2229,51 +2267,51 @@
 Would you like me to search for the most current imaging guidelines or recent literature on this topic, or would you like more detail on a specific site (e.g., bowel, urinary tract, or abdominal wall endometriosis)?</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr"/>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
-      <c r="J12" s="13" t="inlineStr"/>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr"/>
-      <c r="M12" s="13" t="inlineStr"/>
-      <c r="N12" s="13" t="inlineStr"/>
-      <c r="O12" s="13" t="inlineStr"/>
-      <c r="P12" s="13" t="inlineStr"/>
-      <c r="Q12" s="13" t="inlineStr"/>
-      <c r="R12" s="13" t="inlineStr"/>
-      <c r="S12" s="13" t="inlineStr"/>
-      <c r="T12" s="13" t="inlineStr"/>
-      <c r="U12" s="13" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="W12" s="13" t="inlineStr"/>
-      <c r="X12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="Z12" s="13" t="inlineStr"/>
-      <c r="AA12" s="13" t="inlineStr"/>
-      <c r="AB12" s="13" t="inlineStr"/>
-      <c r="AC12" s="13" t="inlineStr"/>
-      <c r="AD12" s="13" t="inlineStr"/>
-      <c r="AE12" s="13" t="inlineStr"/>
-      <c r="AF12" s="14" t="inlineStr"/>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr"/>
+      <c r="H12" s="16" t="inlineStr"/>
+      <c r="I12" s="16" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="16" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr"/>
+      <c r="O12" s="16" t="inlineStr"/>
+      <c r="P12" s="16" t="inlineStr"/>
+      <c r="Q12" s="16" t="inlineStr"/>
+      <c r="R12" s="16" t="inlineStr"/>
+      <c r="S12" s="16" t="inlineStr"/>
+      <c r="T12" s="16" t="inlineStr"/>
+      <c r="U12" s="16" t="inlineStr"/>
+      <c r="V12" s="16" t="inlineStr"/>
+      <c r="W12" s="16" t="inlineStr"/>
+      <c r="X12" s="16" t="inlineStr"/>
+      <c r="Y12" s="16" t="inlineStr"/>
+      <c r="Z12" s="16" t="inlineStr"/>
+      <c r="AA12" s="16" t="inlineStr"/>
+      <c r="AB12" s="16" t="inlineStr"/>
+      <c r="AC12" s="16" t="inlineStr"/>
+      <c r="AD12" s="16" t="inlineStr"/>
+      <c r="AE12" s="16" t="inlineStr"/>
+      <c r="AF12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>ITM-011</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Radiology</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>What are the CT scan findings in endometriosis?</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>CT is **not the primary imaging modality** for endometriosis — transvaginal ultrasound and MRI are preferred — but CT can reveal several characteristic findings, particularly in deep infiltrating endometriosis (DIE) and extrapelvic disease. CT findings are often nonspecific and may mimic other pathologies including malignancy, diverticulitis, or appendicitis.
 **CT Findings in Deep Infiltrating Endometriosis (DIE)**
@@ -2301,7 +2339,7 @@
 José Celso Ardengh, Juan Pablo Román Serrano, Samuel Galante Romanini, et al.. Endometriosis. Atlas of Endoscopic Ultrasonography. 2021. Chapter 17 ISBN: 9781119523000.</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>While **Transvaginal Ultrasound (TVUS) and Magnetic Resonance Imaging (MRI) are the gold standard** imaging modalities for diagnosing endometriosis, Computed Tomography (CT) is sometimes utilized. Because CT has poor soft-tissue contrast and involves radiation exposure, it is widely considered inadequate for detecting superficial peritoneal endometriosis or small lesions. The American College of Radiology (ACR) explicitly states that CT should not be used as a primary diagnostic tool for the condition.
 However, endometriosis is often discovered incidentally on a CT scan when a patient presents to the emergency room with non-specific, acute abdominal or pelvic pain, or complications like a bowel obstruction.
@@ -2325,51 +2363,51 @@
 *Disclaimer: I am an AI, not a doctor. If you suspect you have endometriosis or are experiencing severe pelvic pain, please consult a gynecologist or healthcare professional for an appropriate diagnostic workup.*</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
-      <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="13" t="inlineStr"/>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="13" t="inlineStr"/>
-      <c r="M13" s="13" t="inlineStr"/>
-      <c r="N13" s="13" t="inlineStr"/>
-      <c r="O13" s="13" t="inlineStr"/>
-      <c r="P13" s="13" t="inlineStr"/>
-      <c r="Q13" s="13" t="inlineStr"/>
-      <c r="R13" s="13" t="inlineStr"/>
-      <c r="S13" s="13" t="inlineStr"/>
-      <c r="T13" s="13" t="inlineStr"/>
-      <c r="U13" s="13" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="W13" s="13" t="inlineStr"/>
-      <c r="X13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="Z13" s="13" t="inlineStr"/>
-      <c r="AA13" s="13" t="inlineStr"/>
-      <c r="AB13" s="13" t="inlineStr"/>
-      <c r="AC13" s="13" t="inlineStr"/>
-      <c r="AD13" s="13" t="inlineStr"/>
-      <c r="AE13" s="13" t="inlineStr"/>
-      <c r="AF13" s="14" t="inlineStr"/>
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr"/>
+      <c r="H13" s="16" t="inlineStr"/>
+      <c r="I13" s="16" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="16" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr"/>
+      <c r="O13" s="16" t="inlineStr"/>
+      <c r="P13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="R13" s="16" t="inlineStr"/>
+      <c r="S13" s="16" t="inlineStr"/>
+      <c r="T13" s="16" t="inlineStr"/>
+      <c r="U13" s="16" t="inlineStr"/>
+      <c r="V13" s="16" t="inlineStr"/>
+      <c r="W13" s="16" t="inlineStr"/>
+      <c r="X13" s="16" t="inlineStr"/>
+      <c r="Y13" s="16" t="inlineStr"/>
+      <c r="Z13" s="16" t="inlineStr"/>
+      <c r="AA13" s="16" t="inlineStr"/>
+      <c r="AB13" s="16" t="inlineStr"/>
+      <c r="AC13" s="16" t="inlineStr"/>
+      <c r="AD13" s="16" t="inlineStr"/>
+      <c r="AE13" s="16" t="inlineStr"/>
+      <c r="AF13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>ITM-012</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Allergy &amp; Immunology</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>What is the recommended treatment for perianal rash in a patient with HIV?</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>The recommended treatment for **perianal rash in HIV depends on the underlying etiology**, as multiple infectious and noninfectious causes are common in this population. A thorough evaluation to identify the specific cause is essential before initiating targeted therapy.
 **Common Causes and Their Treatments**
@@ -2393,7 +2431,7 @@
 Would you like to explore the approach to anal dysplasia screening and management in HIV-positive patients with HPV-related perianal disease?</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Perianal rash in a person living with HIV can have many causes, so the "recommended treatment" depends heavily on the underlying diagnosis. Because immunosuppression broadens the differential and changes how some conditions present, it's important to identify the cause rather than treat empirically. Here's an overview of the most common causes and their treatments.
 ### Important first step: identify the cause
@@ -2422,51 +2460,51 @@
 This information is educational and not a substitute for professional medical advice.</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr"/>
-      <c r="G14" s="13" t="inlineStr"/>
-      <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="13" t="inlineStr"/>
-      <c r="L14" s="13" t="inlineStr"/>
-      <c r="M14" s="13" t="inlineStr"/>
-      <c r="N14" s="13" t="inlineStr"/>
-      <c r="O14" s="13" t="inlineStr"/>
-      <c r="P14" s="13" t="inlineStr"/>
-      <c r="Q14" s="13" t="inlineStr"/>
-      <c r="R14" s="13" t="inlineStr"/>
-      <c r="S14" s="13" t="inlineStr"/>
-      <c r="T14" s="13" t="inlineStr"/>
-      <c r="U14" s="13" t="inlineStr"/>
-      <c r="V14" s="13" t="inlineStr"/>
-      <c r="W14" s="13" t="inlineStr"/>
-      <c r="X14" s="13" t="inlineStr"/>
-      <c r="Y14" s="13" t="inlineStr"/>
-      <c r="Z14" s="13" t="inlineStr"/>
-      <c r="AA14" s="13" t="inlineStr"/>
-      <c r="AB14" s="13" t="inlineStr"/>
-      <c r="AC14" s="13" t="inlineStr"/>
-      <c r="AD14" s="13" t="inlineStr"/>
-      <c r="AE14" s="13" t="inlineStr"/>
-      <c r="AF14" s="14" t="inlineStr"/>
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr"/>
+      <c r="H14" s="16" t="inlineStr"/>
+      <c r="I14" s="16" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="16" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr"/>
+      <c r="O14" s="16" t="inlineStr"/>
+      <c r="P14" s="16" t="inlineStr"/>
+      <c r="Q14" s="16" t="inlineStr"/>
+      <c r="R14" s="16" t="inlineStr"/>
+      <c r="S14" s="16" t="inlineStr"/>
+      <c r="T14" s="16" t="inlineStr"/>
+      <c r="U14" s="16" t="inlineStr"/>
+      <c r="V14" s="16" t="inlineStr"/>
+      <c r="W14" s="16" t="inlineStr"/>
+      <c r="X14" s="16" t="inlineStr"/>
+      <c r="Y14" s="16" t="inlineStr"/>
+      <c r="Z14" s="16" t="inlineStr"/>
+      <c r="AA14" s="16" t="inlineStr"/>
+      <c r="AB14" s="16" t="inlineStr"/>
+      <c r="AC14" s="16" t="inlineStr"/>
+      <c r="AD14" s="16" t="inlineStr"/>
+      <c r="AE14" s="16" t="inlineStr"/>
+      <c r="AF14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>ITM-013</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Allergy &amp; Immunology</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>What is the recommended treatment for perianal rash in a patient with HIV?</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>A **perianal rash in a patient with HIV should be examined and tested rather than treated blindly**, because common causes include **HSV**, **syphilis**, **HPV/anal warts**, **Candida/intertrigo**, bacterial infection, dermatitis, mpox, and proctitis/STIs.
 **If the rash is painful, vesicular, erosive, or ulcerative**, the most common “treat-now” concern is **perianal/genital herpes simplex virus (HSV)**. Recommended treatment in people with HIV is typically:
@@ -2482,7 +2520,7 @@
 **Bottom line:** In a patient with HIV, a painful perianal ulcerative rash should generally be treated empirically as **HSV with valacyclovir/acyclovir/famciclovir while testing is obtained**, but the exact treatment depends on the rash’s appearance and test results. Urgent evaluation is warranted if there is fever, rapidly spreading redness, severe pain, drainage, rectal pain/discharge, immunosuppression with low CD4 count, or lesions not improving within a few days.</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>The recommended treatment for **perianal rash in HIV depends on the underlying etiology**, as multiple infectious and noninfectious causes are common in this population. A thorough evaluation to identify the specific cause is essential before initiating targeted therapy.
 **Common Causes and Their Treatments**
@@ -2506,51 +2544,51 @@
 Would you like to explore the approach to anal dysplasia screening and management in HIV-positive patients with HPV-related perianal disease?</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr"/>
-      <c r="G15" s="13" t="inlineStr"/>
-      <c r="H15" s="13" t="inlineStr"/>
-      <c r="I15" s="13" t="inlineStr"/>
-      <c r="J15" s="13" t="inlineStr"/>
-      <c r="K15" s="13" t="inlineStr"/>
-      <c r="L15" s="13" t="inlineStr"/>
-      <c r="M15" s="13" t="inlineStr"/>
-      <c r="N15" s="13" t="inlineStr"/>
-      <c r="O15" s="13" t="inlineStr"/>
-      <c r="P15" s="13" t="inlineStr"/>
-      <c r="Q15" s="13" t="inlineStr"/>
-      <c r="R15" s="13" t="inlineStr"/>
-      <c r="S15" s="13" t="inlineStr"/>
-      <c r="T15" s="13" t="inlineStr"/>
-      <c r="U15" s="13" t="inlineStr"/>
-      <c r="V15" s="13" t="inlineStr"/>
-      <c r="W15" s="13" t="inlineStr"/>
-      <c r="X15" s="13" t="inlineStr"/>
-      <c r="Y15" s="13" t="inlineStr"/>
-      <c r="Z15" s="13" t="inlineStr"/>
-      <c r="AA15" s="13" t="inlineStr"/>
-      <c r="AB15" s="13" t="inlineStr"/>
-      <c r="AC15" s="13" t="inlineStr"/>
-      <c r="AD15" s="13" t="inlineStr"/>
-      <c r="AE15" s="13" t="inlineStr"/>
-      <c r="AF15" s="14" t="inlineStr"/>
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr"/>
+      <c r="H15" s="16" t="inlineStr"/>
+      <c r="I15" s="16" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="16" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr"/>
+      <c r="O15" s="16" t="inlineStr"/>
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr"/>
+      <c r="R15" s="16" t="inlineStr"/>
+      <c r="S15" s="16" t="inlineStr"/>
+      <c r="T15" s="16" t="inlineStr"/>
+      <c r="U15" s="16" t="inlineStr"/>
+      <c r="V15" s="16" t="inlineStr"/>
+      <c r="W15" s="16" t="inlineStr"/>
+      <c r="X15" s="16" t="inlineStr"/>
+      <c r="Y15" s="16" t="inlineStr"/>
+      <c r="Z15" s="16" t="inlineStr"/>
+      <c r="AA15" s="16" t="inlineStr"/>
+      <c r="AB15" s="16" t="inlineStr"/>
+      <c r="AC15" s="16" t="inlineStr"/>
+      <c r="AD15" s="16" t="inlineStr"/>
+      <c r="AE15" s="16" t="inlineStr"/>
+      <c r="AF15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>ITM-014</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Rheumatology</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>What is the most likely diagnosis in this patient presenting with recurrent summer burning sensation along the thigh that worsens with heat exposure, without rash, with transiently positive dsDNA and mildly elevated inflammatory markers that normalized on repeat testing?</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>This presentation is most consistent with **meralgia paresthetica** (lateral femoral cutaneous nerve [LFCN] entrapment neuropathy), though focal small-fiber neuropathy should also be considered. The transiently positive dsDNA and mildly elevated inflammatory markers that normalized are likely incidental and do not meet criteria for [systemic lupus erythematosus](https://www.openevidence.com/rare-disease/systemic-lupus-erythematosus).
 **Most Likely Diagnosis**
@@ -2573,7 +2611,7 @@
 Has the burning been specifically over the outer/lateral thigh, and are there any associated autonomic symptoms or other systemic complaints that might broaden the differential?</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Based on the clinical presentation, the most likely diagnosis is **Multiple Sclerosis (MS)**.
 Here is a breakdown of the clinical clues provided in the vignette:
@@ -2585,51 +2623,51 @@
 The patient is experiencing a temperature-dependent sensory symptom (Uhthoff phenomenon) typical of a demyelinating spinal cord lesion, with transient, non-specific serologic abnormalities that rule out a true systemic connective tissue disease like Lupus.</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="inlineStr"/>
-      <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
-      <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr"/>
-      <c r="L16" s="13" t="inlineStr"/>
-      <c r="M16" s="13" t="inlineStr"/>
-      <c r="N16" s="13" t="inlineStr"/>
-      <c r="O16" s="13" t="inlineStr"/>
-      <c r="P16" s="13" t="inlineStr"/>
-      <c r="Q16" s="13" t="inlineStr"/>
-      <c r="R16" s="13" t="inlineStr"/>
-      <c r="S16" s="13" t="inlineStr"/>
-      <c r="T16" s="13" t="inlineStr"/>
-      <c r="U16" s="13" t="inlineStr"/>
-      <c r="V16" s="13" t="inlineStr"/>
-      <c r="W16" s="13" t="inlineStr"/>
-      <c r="X16" s="13" t="inlineStr"/>
-      <c r="Y16" s="13" t="inlineStr"/>
-      <c r="Z16" s="13" t="inlineStr"/>
-      <c r="AA16" s="13" t="inlineStr"/>
-      <c r="AB16" s="13" t="inlineStr"/>
-      <c r="AC16" s="13" t="inlineStr"/>
-      <c r="AD16" s="13" t="inlineStr"/>
-      <c r="AE16" s="13" t="inlineStr"/>
-      <c r="AF16" s="14" t="inlineStr"/>
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="16" t="inlineStr"/>
+      <c r="H16" s="16" t="inlineStr"/>
+      <c r="I16" s="16" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr"/>
+      <c r="O16" s="16" t="inlineStr"/>
+      <c r="P16" s="16" t="inlineStr"/>
+      <c r="Q16" s="16" t="inlineStr"/>
+      <c r="R16" s="16" t="inlineStr"/>
+      <c r="S16" s="16" t="inlineStr"/>
+      <c r="T16" s="16" t="inlineStr"/>
+      <c r="U16" s="16" t="inlineStr"/>
+      <c r="V16" s="16" t="inlineStr"/>
+      <c r="W16" s="16" t="inlineStr"/>
+      <c r="X16" s="16" t="inlineStr"/>
+      <c r="Y16" s="16" t="inlineStr"/>
+      <c r="Z16" s="16" t="inlineStr"/>
+      <c r="AA16" s="16" t="inlineStr"/>
+      <c r="AB16" s="16" t="inlineStr"/>
+      <c r="AC16" s="16" t="inlineStr"/>
+      <c r="AD16" s="16" t="inlineStr"/>
+      <c r="AE16" s="16" t="inlineStr"/>
+      <c r="AF16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>ITM-015</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Surgery</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Have there been any documented case reports of pilonidal disease occurring in a skin fold at the nape of the neck?</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Yes, **pilonidal sinus of the neck has been documented in the medical literature**, though it is a rare ectopic location. Two key reports are relevant:
 **Specific case report of neck pilonidal sinus:** Meher et al. (2006) described a case of **pilonidal sinus of the neck following trauma due to shaving**. The sinus was treated with excision and primary repair, resulting in complete healing with no recurrence. The authors discussed the acquired pathogenesis of the condition, implicating repetitive local trauma (shaving) as the inciting factor.
@@ -2641,7 +2679,7 @@
 Would you like to explore the differential diagnosis of chronic draining sinuses at the posterior neck, including how to distinguish pilonidal disease from other entities such as hidradenitis suppurativa or infected branchial cleft remnants?</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Yes, there are indeed documented case reports of pilonidal disease occurring at the nape of the neck. While pilonidal cysts and sinus tracts overwhelmingly occur in the sacrococcygeal region (the natal cleft), the posterior neck/nuchal region has been recognized as one of several rare, "atypical" locations for the disease.
 ### Why Does It Occur in the Neck?
@@ -2657,51 +2695,51 @@
 Because the pathology is identical to standard pilonidal disease, the treatment protocol remains the same. Broad-spectrum antibiotics or simple drainage usually result in recurrence. Complete surgical excision of the sinus tracts and cysts, followed by primary or secondary closure, is the definitive cure.</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr"/>
-      <c r="G17" s="13" t="inlineStr"/>
-      <c r="H17" s="13" t="inlineStr"/>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr"/>
-      <c r="K17" s="13" t="inlineStr"/>
-      <c r="L17" s="13" t="inlineStr"/>
-      <c r="M17" s="13" t="inlineStr"/>
-      <c r="N17" s="13" t="inlineStr"/>
-      <c r="O17" s="13" t="inlineStr"/>
-      <c r="P17" s="13" t="inlineStr"/>
-      <c r="Q17" s="13" t="inlineStr"/>
-      <c r="R17" s="13" t="inlineStr"/>
-      <c r="S17" s="13" t="inlineStr"/>
-      <c r="T17" s="13" t="inlineStr"/>
-      <c r="U17" s="13" t="inlineStr"/>
-      <c r="V17" s="13" t="inlineStr"/>
-      <c r="W17" s="13" t="inlineStr"/>
-      <c r="X17" s="13" t="inlineStr"/>
-      <c r="Y17" s="13" t="inlineStr"/>
-      <c r="Z17" s="13" t="inlineStr"/>
-      <c r="AA17" s="13" t="inlineStr"/>
-      <c r="AB17" s="13" t="inlineStr"/>
-      <c r="AC17" s="13" t="inlineStr"/>
-      <c r="AD17" s="13" t="inlineStr"/>
-      <c r="AE17" s="13" t="inlineStr"/>
-      <c r="AF17" s="14" t="inlineStr"/>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+      <c r="H17" s="16" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="16" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr"/>
+      <c r="O17" s="16" t="inlineStr"/>
+      <c r="P17" s="16" t="inlineStr"/>
+      <c r="Q17" s="16" t="inlineStr"/>
+      <c r="R17" s="16" t="inlineStr"/>
+      <c r="S17" s="16" t="inlineStr"/>
+      <c r="T17" s="16" t="inlineStr"/>
+      <c r="U17" s="16" t="inlineStr"/>
+      <c r="V17" s="16" t="inlineStr"/>
+      <c r="W17" s="16" t="inlineStr"/>
+      <c r="X17" s="16" t="inlineStr"/>
+      <c r="Y17" s="16" t="inlineStr"/>
+      <c r="Z17" s="16" t="inlineStr"/>
+      <c r="AA17" s="16" t="inlineStr"/>
+      <c r="AB17" s="16" t="inlineStr"/>
+      <c r="AC17" s="16" t="inlineStr"/>
+      <c r="AD17" s="16" t="inlineStr"/>
+      <c r="AE17" s="16" t="inlineStr"/>
+      <c r="AF17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>ITM-016</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Internal Medicine</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>What prophylactic treatment should be given to an 82-year-old woman with a prior history of superficial thrombophlebitis of the leg following prolonged air travel, who completed a 45-day course of rivaroxaban and is now planning another long-distance flight three months later?</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>For this patient with **prior superficial vein thrombosis (SuVT)** and multiple risk factors (advanced age, history of travel-related thrombosis), the recommended prophylactic measures for long-distance air travel are **graduated compression stockings (15–30 mm Hg, below-knee)** combined with **frequent ambulation and calf muscle exercises** during the flight. Pharmacologic prophylaxis with a single dose of **LMWH (e.g., enoxaparin 40 mg subcutaneously)** before departure may also be considered on an individualized basis.
 **Evidence-Based Rationale**
@@ -2730,7 +2768,7 @@
 Rashedi S, Pfeferman M, Pandey A, et al. Extended Low-Dose Apixaban and Superficial Vein Thrombosis: Post Hoc Analysis of the HI-PRO Randomized Clinical Trial. JAMA Cardiology. 2026;:2847054. doi:10.1001/jamacardio.2026.0151.</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>### Prophylactic Approach for Travel-Related VTE in This High-Risk Patient
 This patient has several features that place her in a **higher-risk category** for travel-related venous thromboembolism (VTE): advanced age (82 years), a prior history of superficial thrombophlebitis specifically triggered by prolonged air travel, and a planned long-haul flight. Importantly, she completed her course of rivaroxaban and is no longer on therapeutic anticoagulation. Here's a structured approach:
@@ -2757,51 +2795,51 @@
 Would you like me to search for the most current society guidelines (e.g., the latest CHEST or ESC recommendations) to confirm specific dosing or thresholds?</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr"/>
-      <c r="L18" s="13" t="inlineStr"/>
-      <c r="M18" s="13" t="inlineStr"/>
-      <c r="N18" s="13" t="inlineStr"/>
-      <c r="O18" s="13" t="inlineStr"/>
-      <c r="P18" s="13" t="inlineStr"/>
-      <c r="Q18" s="13" t="inlineStr"/>
-      <c r="R18" s="13" t="inlineStr"/>
-      <c r="S18" s="13" t="inlineStr"/>
-      <c r="T18" s="13" t="inlineStr"/>
-      <c r="U18" s="13" t="inlineStr"/>
-      <c r="V18" s="13" t="inlineStr"/>
-      <c r="W18" s="13" t="inlineStr"/>
-      <c r="X18" s="13" t="inlineStr"/>
-      <c r="Y18" s="13" t="inlineStr"/>
-      <c r="Z18" s="13" t="inlineStr"/>
-      <c r="AA18" s="13" t="inlineStr"/>
-      <c r="AB18" s="13" t="inlineStr"/>
-      <c r="AC18" s="13" t="inlineStr"/>
-      <c r="AD18" s="13" t="inlineStr"/>
-      <c r="AE18" s="13" t="inlineStr"/>
-      <c r="AF18" s="14" t="inlineStr"/>
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="16" t="inlineStr"/>
+      <c r="H18" s="16" t="inlineStr"/>
+      <c r="I18" s="16" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr"/>
+      <c r="O18" s="16" t="inlineStr"/>
+      <c r="P18" s="16" t="inlineStr"/>
+      <c r="Q18" s="16" t="inlineStr"/>
+      <c r="R18" s="16" t="inlineStr"/>
+      <c r="S18" s="16" t="inlineStr"/>
+      <c r="T18" s="16" t="inlineStr"/>
+      <c r="U18" s="16" t="inlineStr"/>
+      <c r="V18" s="16" t="inlineStr"/>
+      <c r="W18" s="16" t="inlineStr"/>
+      <c r="X18" s="16" t="inlineStr"/>
+      <c r="Y18" s="16" t="inlineStr"/>
+      <c r="Z18" s="16" t="inlineStr"/>
+      <c r="AA18" s="16" t="inlineStr"/>
+      <c r="AB18" s="16" t="inlineStr"/>
+      <c r="AC18" s="16" t="inlineStr"/>
+      <c r="AD18" s="16" t="inlineStr"/>
+      <c r="AE18" s="16" t="inlineStr"/>
+      <c r="AF18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>ITM-017</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Urology</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>What is the preferred management for early-stage prostate cancer in a 71-year-old patient?</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>For a **71-year-old with early-stage/localized prostate cancer**, the **preferred management is often _active surveillance_** **if the cancer is very-low-risk or low-risk**—for example, small-volume, confined to the prostate, PSA and biopsy features suggesting slow growth, and Gleason Grade Group 1 / Gleason 3+3. This is especially reasonable when avoiding urinary, sexual, and bowel side effects from surgery or radiation is a priority. Active surveillance means **regular PSA testing, exams, repeat MRI/biopsy as needed, and switching to curative treatment if the cancer shows signs of progression**.
 The decision should **not be based on age alone**. At 71, management depends mainly on **risk category, symptoms, comorbidities, functional status, and estimated life expectancy**. If the patient is healthy with a life expectancy of **&gt;10 years**, curative options—**radiation therapy or radical prostatectomy**—may be discussed, especially for higher-risk disease. If life expectancy is **&lt;10 years** or there are significant competing health problems, **watchful waiting/observation** may be favored over intensive monitoring or curative treatment.
@@ -2815,7 +2853,7 @@
 So, if this 71-year-old has **low-risk early-stage prostate cancer**, the usual preferred management is **active surveillance rather than immediate surgery or radiation**. The key next step is to confirm the **PSA, Gleason/Grade Group, number of positive biopsy cores, MRI findings, clinical stage, and overall health/life expectancy** with a urologist—and often also a radiation oncologist for a balanced discussion.</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>The preferred management of early-stage prostate cancer in a 71-year-old depends critically on the **risk group** (low, favorable intermediate, unfavorable intermediate, or high) and the patient's **estimated life expectancy**, which is driven by comorbidities rather than age alone. Below is a summary organized by risk category per the NCCN Prostate Cancer Guidelines and AUA/ASTRO Guidelines.
 The NCCN risk stratification algorithm is shown below:
@@ -2845,51 +2883,51 @@
 Would you like to explore the specific active surveillance protocols and monitoring schedules recommended for a particular risk group, or the comparative side-effect profiles of radical prostatectomy versus radiation therapy in more detail?</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr"/>
-      <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="13" t="inlineStr"/>
-      <c r="I19" s="13" t="inlineStr"/>
-      <c r="J19" s="13" t="inlineStr"/>
-      <c r="K19" s="13" t="inlineStr"/>
-      <c r="L19" s="13" t="inlineStr"/>
-      <c r="M19" s="13" t="inlineStr"/>
-      <c r="N19" s="13" t="inlineStr"/>
-      <c r="O19" s="13" t="inlineStr"/>
-      <c r="P19" s="13" t="inlineStr"/>
-      <c r="Q19" s="13" t="inlineStr"/>
-      <c r="R19" s="13" t="inlineStr"/>
-      <c r="S19" s="13" t="inlineStr"/>
-      <c r="T19" s="13" t="inlineStr"/>
-      <c r="U19" s="13" t="inlineStr"/>
-      <c r="V19" s="13" t="inlineStr"/>
-      <c r="W19" s="13" t="inlineStr"/>
-      <c r="X19" s="13" t="inlineStr"/>
-      <c r="Y19" s="13" t="inlineStr"/>
-      <c r="Z19" s="13" t="inlineStr"/>
-      <c r="AA19" s="13" t="inlineStr"/>
-      <c r="AB19" s="13" t="inlineStr"/>
-      <c r="AC19" s="13" t="inlineStr"/>
-      <c r="AD19" s="13" t="inlineStr"/>
-      <c r="AE19" s="13" t="inlineStr"/>
-      <c r="AF19" s="14" t="inlineStr"/>
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr"/>
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="16" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr"/>
+      <c r="P19" s="16" t="inlineStr"/>
+      <c r="Q19" s="16" t="inlineStr"/>
+      <c r="R19" s="16" t="inlineStr"/>
+      <c r="S19" s="16" t="inlineStr"/>
+      <c r="T19" s="16" t="inlineStr"/>
+      <c r="U19" s="16" t="inlineStr"/>
+      <c r="V19" s="16" t="inlineStr"/>
+      <c r="W19" s="16" t="inlineStr"/>
+      <c r="X19" s="16" t="inlineStr"/>
+      <c r="Y19" s="16" t="inlineStr"/>
+      <c r="Z19" s="16" t="inlineStr"/>
+      <c r="AA19" s="16" t="inlineStr"/>
+      <c r="AB19" s="16" t="inlineStr"/>
+      <c r="AC19" s="16" t="inlineStr"/>
+      <c r="AD19" s="16" t="inlineStr"/>
+      <c r="AE19" s="16" t="inlineStr"/>
+      <c r="AF19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>ITM-018</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>What is the appropriate next step in the workup for a 76-year-old woman with persistently suppressed renin and mildly elevated aldosterone (ARR suggesting possible primary aldosteronism), who has not yet completed the confirmatory sodium loading test, and whose blood pressure remains largely controlled on her current regimen?</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>The most appropriate next step depends on whether confirmatory testing will change management. For a 76-year-old with persistently suppressed renin and mildly elevated aldosterone, the recommended approach is to either **proceed with a confirmatory aldosterone suppression test** (oral sodium loading, IV saline infusion, or captopril challenge) or, alternatively, **initiate empiric mineralocorticoid receptor antagonist (MRA) therapy without confirmatory testing**, particularly if the patient is unlikely to pursue surgical intervention.
 **Why confirmatory testing may be bypassed in this patient**
@@ -2909,7 +2947,7 @@
 Would you like to explore the specific dosing, monitoring, and side effect profiles of spironolactone versus eplerenone for medical management of primary aldosteronism in older adults?</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>The appropriate next step is to **complete the confirmatory testing** before moving on to subtype classification or treatment decisions. Here's the reasoning:
 ### Why confirmatory testing is the correct next step
@@ -2934,51 +2972,51 @@
 *This is general medical information; specific management should be guided by her treating physician/endocrinologist based on her full clinical picture.*</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
-      <c r="J20" s="13" t="inlineStr"/>
-      <c r="K20" s="13" t="inlineStr"/>
-      <c r="L20" s="13" t="inlineStr"/>
-      <c r="M20" s="13" t="inlineStr"/>
-      <c r="N20" s="13" t="inlineStr"/>
-      <c r="O20" s="13" t="inlineStr"/>
-      <c r="P20" s="13" t="inlineStr"/>
-      <c r="Q20" s="13" t="inlineStr"/>
-      <c r="R20" s="13" t="inlineStr"/>
-      <c r="S20" s="13" t="inlineStr"/>
-      <c r="T20" s="13" t="inlineStr"/>
-      <c r="U20" s="13" t="inlineStr"/>
-      <c r="V20" s="13" t="inlineStr"/>
-      <c r="W20" s="13" t="inlineStr"/>
-      <c r="X20" s="13" t="inlineStr"/>
-      <c r="Y20" s="13" t="inlineStr"/>
-      <c r="Z20" s="13" t="inlineStr"/>
-      <c r="AA20" s="13" t="inlineStr"/>
-      <c r="AB20" s="13" t="inlineStr"/>
-      <c r="AC20" s="13" t="inlineStr"/>
-      <c r="AD20" s="13" t="inlineStr"/>
-      <c r="AE20" s="13" t="inlineStr"/>
-      <c r="AF20" s="14" t="inlineStr"/>
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="16" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="16" t="inlineStr"/>
+      <c r="L20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr"/>
+      <c r="O20" s="16" t="inlineStr"/>
+      <c r="P20" s="16" t="inlineStr"/>
+      <c r="Q20" s="16" t="inlineStr"/>
+      <c r="R20" s="16" t="inlineStr"/>
+      <c r="S20" s="16" t="inlineStr"/>
+      <c r="T20" s="16" t="inlineStr"/>
+      <c r="U20" s="16" t="inlineStr"/>
+      <c r="V20" s="16" t="inlineStr"/>
+      <c r="W20" s="16" t="inlineStr"/>
+      <c r="X20" s="16" t="inlineStr"/>
+      <c r="Y20" s="16" t="inlineStr"/>
+      <c r="Z20" s="16" t="inlineStr"/>
+      <c r="AA20" s="16" t="inlineStr"/>
+      <c r="AB20" s="16" t="inlineStr"/>
+      <c r="AC20" s="16" t="inlineStr"/>
+      <c r="AD20" s="16" t="inlineStr"/>
+      <c r="AE20" s="16" t="inlineStr"/>
+      <c r="AF20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>ITM-019</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>What is the appropriate next step in the workup for a 76-year-old woman with persistently suppressed renin and mildly elevated aldosterone (ARR suggesting possible primary aldosteronism), who has not yet completed the confirmatory sodium loading test, and whose blood pressure remains largely controlled on her current regimen?</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>The **appropriate next step is to finish biochemical confirmation**, not to jump to adrenal CT/AVS or surgery.
 For a 76-year-old with **persistently suppressed renin** and **only mildly elevated aldosterone**, the ARR can suggest possible primary aldosteronism, but it is not by itself definitive—especially if aldosterone is only modestly elevated or if medications could be suppressing renin. Current guidance supports **aldosterone-suppression/confirmatory testing** when the probability is not already overt and the patient might pursue PA-specific treatment decisions.
@@ -2990,7 +3028,7 @@
 Given that her BP is largely controlled, this is generally an **outpatient endocrine/hypertension workup**, not an emergency—complete the confirmatory test and avoid irreversible or invasive steps until the diagnosis and goals of care are clarified.</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>The most appropriate next step depends on whether confirmatory testing will change management. For a 76-year-old with persistently suppressed renin and mildly elevated aldosterone, the recommended approach is to either **proceed with a confirmatory aldosterone suppression test** (oral sodium loading, IV saline infusion, or captopril challenge) or, alternatively, **initiate empiric mineralocorticoid receptor antagonist (MRA) therapy without confirmatory testing**, particularly if the patient is unlikely to pursue surgical intervention.
 **Why confirmatory testing may be bypassed in this patient**
@@ -3010,51 +3048,51 @@
 Would you like to explore the specific dosing, monitoring, and side effect profiles of spironolactone versus eplerenone for medical management of primary aldosteronism in older adults?</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr"/>
-      <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="13" t="inlineStr"/>
-      <c r="K21" s="13" t="inlineStr"/>
-      <c r="L21" s="13" t="inlineStr"/>
-      <c r="M21" s="13" t="inlineStr"/>
-      <c r="N21" s="13" t="inlineStr"/>
-      <c r="O21" s="13" t="inlineStr"/>
-      <c r="P21" s="13" t="inlineStr"/>
-      <c r="Q21" s="13" t="inlineStr"/>
-      <c r="R21" s="13" t="inlineStr"/>
-      <c r="S21" s="13" t="inlineStr"/>
-      <c r="T21" s="13" t="inlineStr"/>
-      <c r="U21" s="13" t="inlineStr"/>
-      <c r="V21" s="13" t="inlineStr"/>
-      <c r="W21" s="13" t="inlineStr"/>
-      <c r="X21" s="13" t="inlineStr"/>
-      <c r="Y21" s="13" t="inlineStr"/>
-      <c r="Z21" s="13" t="inlineStr"/>
-      <c r="AA21" s="13" t="inlineStr"/>
-      <c r="AB21" s="13" t="inlineStr"/>
-      <c r="AC21" s="13" t="inlineStr"/>
-      <c r="AD21" s="13" t="inlineStr"/>
-      <c r="AE21" s="13" t="inlineStr"/>
-      <c r="AF21" s="14" t="inlineStr"/>
+      <c r="F21" s="16" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+      <c r="H21" s="16" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr"/>
+      <c r="K21" s="16" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr"/>
+      <c r="N21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="inlineStr"/>
+      <c r="P21" s="16" t="inlineStr"/>
+      <c r="Q21" s="16" t="inlineStr"/>
+      <c r="R21" s="16" t="inlineStr"/>
+      <c r="S21" s="16" t="inlineStr"/>
+      <c r="T21" s="16" t="inlineStr"/>
+      <c r="U21" s="16" t="inlineStr"/>
+      <c r="V21" s="16" t="inlineStr"/>
+      <c r="W21" s="16" t="inlineStr"/>
+      <c r="X21" s="16" t="inlineStr"/>
+      <c r="Y21" s="16" t="inlineStr"/>
+      <c r="Z21" s="16" t="inlineStr"/>
+      <c r="AA21" s="16" t="inlineStr"/>
+      <c r="AB21" s="16" t="inlineStr"/>
+      <c r="AC21" s="16" t="inlineStr"/>
+      <c r="AD21" s="16" t="inlineStr"/>
+      <c r="AE21" s="16" t="inlineStr"/>
+      <c r="AF21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>ITM-020</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Emergency Medicine</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Is splinting still appropriate for a right hand 5th distal phalanx base fracture if the patient has gone three weeks without immobilization due to being incarcerated?</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Yes—a three-week delay does not automatically rule out splinting, and in fact splinting is often still the appropriate treatment for many fractures at the base of the distal phalanx. Here's what the evidence shows, along with important caveats.
 ### Why this injury matters
@@ -3075,7 +3113,7 @@
 I'd strongly recommend that the patient be evaluated by a hand surgeon or orthopedist with updated imaging before committing to a plan. This information is educational and not a substitute for that individualized assessment.</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>**Yes, splinting is still appropriate** for a 5th distal phalanx base fracture at three weeks post-injury, provided the fracture alignment is acceptable on current radiographs. The decision depends on the fracture pattern, current alignment, and whether early healing is occurring in an acceptable position.
 **Key considerations at three weeks:**
@@ -3088,51 +3126,51 @@
 Would you like to explore the specific indications for hand surgery referral versus continued conservative management in subacute phalangeal fractures?</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr"/>
-      <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
-      <c r="J22" s="13" t="inlineStr"/>
-      <c r="K22" s="13" t="inlineStr"/>
-      <c r="L22" s="13" t="inlineStr"/>
-      <c r="M22" s="13" t="inlineStr"/>
-      <c r="N22" s="13" t="inlineStr"/>
-      <c r="O22" s="13" t="inlineStr"/>
-      <c r="P22" s="13" t="inlineStr"/>
-      <c r="Q22" s="13" t="inlineStr"/>
-      <c r="R22" s="13" t="inlineStr"/>
-      <c r="S22" s="13" t="inlineStr"/>
-      <c r="T22" s="13" t="inlineStr"/>
-      <c r="U22" s="13" t="inlineStr"/>
-      <c r="V22" s="13" t="inlineStr"/>
-      <c r="W22" s="13" t="inlineStr"/>
-      <c r="X22" s="13" t="inlineStr"/>
-      <c r="Y22" s="13" t="inlineStr"/>
-      <c r="Z22" s="13" t="inlineStr"/>
-      <c r="AA22" s="13" t="inlineStr"/>
-      <c r="AB22" s="13" t="inlineStr"/>
-      <c r="AC22" s="13" t="inlineStr"/>
-      <c r="AD22" s="13" t="inlineStr"/>
-      <c r="AE22" s="13" t="inlineStr"/>
-      <c r="AF22" s="14" t="inlineStr"/>
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
+      <c r="H22" s="16" t="inlineStr"/>
+      <c r="I22" s="16" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="16" t="inlineStr"/>
+      <c r="L22" s="16" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr"/>
+      <c r="O22" s="16" t="inlineStr"/>
+      <c r="P22" s="16" t="inlineStr"/>
+      <c r="Q22" s="16" t="inlineStr"/>
+      <c r="R22" s="16" t="inlineStr"/>
+      <c r="S22" s="16" t="inlineStr"/>
+      <c r="T22" s="16" t="inlineStr"/>
+      <c r="U22" s="16" t="inlineStr"/>
+      <c r="V22" s="16" t="inlineStr"/>
+      <c r="W22" s="16" t="inlineStr"/>
+      <c r="X22" s="16" t="inlineStr"/>
+      <c r="Y22" s="16" t="inlineStr"/>
+      <c r="Z22" s="16" t="inlineStr"/>
+      <c r="AA22" s="16" t="inlineStr"/>
+      <c r="AB22" s="16" t="inlineStr"/>
+      <c r="AC22" s="16" t="inlineStr"/>
+      <c r="AD22" s="16" t="inlineStr"/>
+      <c r="AE22" s="16" t="inlineStr"/>
+      <c r="AF22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ITM-021</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>If hematocrit rises to 51% following initiation of testosterone 75mg weekly, what modification to the testosterone regimen should be made, and at what interval should the hematocrit be reassessed?</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>### Background on the Threshold
 Hematocrit elevation (erythrocytosis) is the most common adverse effect requiring monitoring during testosterone therapy. The key clinical reference points are:
@@ -3150,7 +3188,7 @@
 *This reflects general guideline-based practice (Endocrine Society); specific decisions should be individualized to the patient and made by the treating clinician.*</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>The guidelines provide a nuanced, tiered approach depending on the degree of hematocrit elevation. At a hematocrit of 51%, the management differs from the more urgent threshold of &gt;54%.
 **Dose reduction** of testosterone is the recommended modification. Current guidelines advise against androgen replacement when hematocrit exceeds **50%**, and the testosterone dose should be **reduced** with a target hematocrit of **&lt;50%**. At 51%, the hematocrit has not yet reached the critical **&gt;54% threshold** at which the Endocrine Society recommends **withholding testosterone entirely** until hematocrit normalizes. However, a dose reduction is warranted at this level, and switching from injectable to **transdermal testosterone** may also be considered, as the frequency of erythrocytosis is substantially lower with transdermal formulations (15% vs. 44% with injections).
@@ -3162,51 +3200,51 @@
 Would you like to explore the comparative efficacy and erythrocytosis risk profiles of different testosterone formulations (injectable vs. transdermal vs. oral) to guide formulation switching in this patient?</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr"/>
-      <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="13" t="inlineStr"/>
-      <c r="K23" s="13" t="inlineStr"/>
-      <c r="L23" s="13" t="inlineStr"/>
-      <c r="M23" s="13" t="inlineStr"/>
-      <c r="N23" s="13" t="inlineStr"/>
-      <c r="O23" s="13" t="inlineStr"/>
-      <c r="P23" s="13" t="inlineStr"/>
-      <c r="Q23" s="13" t="inlineStr"/>
-      <c r="R23" s="13" t="inlineStr"/>
-      <c r="S23" s="13" t="inlineStr"/>
-      <c r="T23" s="13" t="inlineStr"/>
-      <c r="U23" s="13" t="inlineStr"/>
-      <c r="V23" s="13" t="inlineStr"/>
-      <c r="W23" s="13" t="inlineStr"/>
-      <c r="X23" s="13" t="inlineStr"/>
-      <c r="Y23" s="13" t="inlineStr"/>
-      <c r="Z23" s="13" t="inlineStr"/>
-      <c r="AA23" s="13" t="inlineStr"/>
-      <c r="AB23" s="13" t="inlineStr"/>
-      <c r="AC23" s="13" t="inlineStr"/>
-      <c r="AD23" s="13" t="inlineStr"/>
-      <c r="AE23" s="13" t="inlineStr"/>
-      <c r="AF23" s="14" t="inlineStr"/>
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
+      <c r="H23" s="16" t="inlineStr"/>
+      <c r="I23" s="16" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="16" t="inlineStr"/>
+      <c r="L23" s="16" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr"/>
+      <c r="O23" s="16" t="inlineStr"/>
+      <c r="P23" s="16" t="inlineStr"/>
+      <c r="Q23" s="16" t="inlineStr"/>
+      <c r="R23" s="16" t="inlineStr"/>
+      <c r="S23" s="16" t="inlineStr"/>
+      <c r="T23" s="16" t="inlineStr"/>
+      <c r="U23" s="16" t="inlineStr"/>
+      <c r="V23" s="16" t="inlineStr"/>
+      <c r="W23" s="16" t="inlineStr"/>
+      <c r="X23" s="16" t="inlineStr"/>
+      <c r="Y23" s="16" t="inlineStr"/>
+      <c r="Z23" s="16" t="inlineStr"/>
+      <c r="AA23" s="16" t="inlineStr"/>
+      <c r="AB23" s="16" t="inlineStr"/>
+      <c r="AC23" s="16" t="inlineStr"/>
+      <c r="AD23" s="16" t="inlineStr"/>
+      <c r="AE23" s="16" t="inlineStr"/>
+      <c r="AF23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>ITM-022</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>OB / GYN</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>What is the recommended management for Gardnerella vaginalis infection?</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>### Practice Guideline
 The **CDC recommends treatment for bacterial vaginosis (BV) — the condition caused by Gardnerella vaginalis overgrowth — only in symptomatic women**. The established benefit of therapy is relief of vaginal symptoms and signs of infection, with potential additional benefits including reduced risk of acquiring other STIs.
@@ -3232,7 +3270,7 @@
 Would you like to explore the evidence on management strategies specifically for recurrent bacterial vaginosis, including biofilm-disrupting agents and adjunctive probiotics?</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>### Management of Gardnerella vaginalis / Bacterial Vaginosis
 *Gardnerella vaginalis* is the bacterium most commonly associated with **bacterial vaginosis (BV)**, a condition caused by an imbalance in the normal vaginal flora—where protective lactobacilli are replaced by an overgrowth of anaerobic bacteria including *Gardnerella*. Treatment guidelines (such as those from the CDC) target this overgrowth.
@@ -3260,51 +3298,51 @@
 Would you like me to look up the latest specific guideline recommendations?</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr"/>
-      <c r="K24" s="13" t="inlineStr"/>
-      <c r="L24" s="13" t="inlineStr"/>
-      <c r="M24" s="13" t="inlineStr"/>
-      <c r="N24" s="13" t="inlineStr"/>
-      <c r="O24" s="13" t="inlineStr"/>
-      <c r="P24" s="13" t="inlineStr"/>
-      <c r="Q24" s="13" t="inlineStr"/>
-      <c r="R24" s="13" t="inlineStr"/>
-      <c r="S24" s="13" t="inlineStr"/>
-      <c r="T24" s="13" t="inlineStr"/>
-      <c r="U24" s="13" t="inlineStr"/>
-      <c r="V24" s="13" t="inlineStr"/>
-      <c r="W24" s="13" t="inlineStr"/>
-      <c r="X24" s="13" t="inlineStr"/>
-      <c r="Y24" s="13" t="inlineStr"/>
-      <c r="Z24" s="13" t="inlineStr"/>
-      <c r="AA24" s="13" t="inlineStr"/>
-      <c r="AB24" s="13" t="inlineStr"/>
-      <c r="AC24" s="13" t="inlineStr"/>
-      <c r="AD24" s="13" t="inlineStr"/>
-      <c r="AE24" s="13" t="inlineStr"/>
-      <c r="AF24" s="14" t="inlineStr"/>
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr"/>
+      <c r="H24" s="16" t="inlineStr"/>
+      <c r="I24" s="16" t="inlineStr"/>
+      <c r="J24" s="16" t="inlineStr"/>
+      <c r="K24" s="16" t="inlineStr"/>
+      <c r="L24" s="16" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr"/>
+      <c r="O24" s="16" t="inlineStr"/>
+      <c r="P24" s="16" t="inlineStr"/>
+      <c r="Q24" s="16" t="inlineStr"/>
+      <c r="R24" s="16" t="inlineStr"/>
+      <c r="S24" s="16" t="inlineStr"/>
+      <c r="T24" s="16" t="inlineStr"/>
+      <c r="U24" s="16" t="inlineStr"/>
+      <c r="V24" s="16" t="inlineStr"/>
+      <c r="W24" s="16" t="inlineStr"/>
+      <c r="X24" s="16" t="inlineStr"/>
+      <c r="Y24" s="16" t="inlineStr"/>
+      <c r="Z24" s="16" t="inlineStr"/>
+      <c r="AA24" s="16" t="inlineStr"/>
+      <c r="AB24" s="16" t="inlineStr"/>
+      <c r="AC24" s="16" t="inlineStr"/>
+      <c r="AD24" s="16" t="inlineStr"/>
+      <c r="AE24" s="16" t="inlineStr"/>
+      <c r="AF24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>ITM-023</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Nephrology</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Can patients with active lupus nephritis present with isolated proteinuria in the absence of hematuria?</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>**Yes, patients with active lupus nephritis can present with isolated proteinuria in the absence of hematuria**, and this is a well-recognized clinical scenario with important management implications.
 **Evidence supporting isolated proteinuria as a presentation of active LN**
@@ -3321,7 +3359,7 @@
 Would you like to explore how serologic markers (anti-dsDNA, complement levels, anti-Sm) perform in predicting histologic class in patients with isolated proteinuria and no active sediment?</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>**Yes**, patients with active lupus nephritis (LN) can absolutely present with isolated proteinuria in the absence of hematuria.
 While the "classic" description of active lupus nephritis involves an active urinary sediment (proteinuria combined with microscopic hematuria, and red blood cell casts), relying on the presence of hematuria to suspect kidney involvement can lead to missed diagnoses.
@@ -3341,51 +3379,51 @@
 **Bottom Line:** The absence of hematuria does not rule out active lupus nephritis. Any new, persistent, or worsening proteinuria in a patient with SLE should be treated with high clinical suspicion for active kidney involvement and usually warrants a renal biopsy.</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr"/>
-      <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="13" t="inlineStr"/>
-      <c r="K25" s="13" t="inlineStr"/>
-      <c r="L25" s="13" t="inlineStr"/>
-      <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="13" t="inlineStr"/>
-      <c r="O25" s="13" t="inlineStr"/>
-      <c r="P25" s="13" t="inlineStr"/>
-      <c r="Q25" s="13" t="inlineStr"/>
-      <c r="R25" s="13" t="inlineStr"/>
-      <c r="S25" s="13" t="inlineStr"/>
-      <c r="T25" s="13" t="inlineStr"/>
-      <c r="U25" s="13" t="inlineStr"/>
-      <c r="V25" s="13" t="inlineStr"/>
-      <c r="W25" s="13" t="inlineStr"/>
-      <c r="X25" s="13" t="inlineStr"/>
-      <c r="Y25" s="13" t="inlineStr"/>
-      <c r="Z25" s="13" t="inlineStr"/>
-      <c r="AA25" s="13" t="inlineStr"/>
-      <c r="AB25" s="13" t="inlineStr"/>
-      <c r="AC25" s="13" t="inlineStr"/>
-      <c r="AD25" s="13" t="inlineStr"/>
-      <c r="AE25" s="13" t="inlineStr"/>
-      <c r="AF25" s="14" t="inlineStr"/>
+      <c r="F25" s="16" t="inlineStr"/>
+      <c r="G25" s="16" t="inlineStr"/>
+      <c r="H25" s="16" t="inlineStr"/>
+      <c r="I25" s="16" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr"/>
+      <c r="K25" s="16" t="inlineStr"/>
+      <c r="L25" s="16" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr"/>
+      <c r="N25" s="16" t="inlineStr"/>
+      <c r="O25" s="16" t="inlineStr"/>
+      <c r="P25" s="16" t="inlineStr"/>
+      <c r="Q25" s="16" t="inlineStr"/>
+      <c r="R25" s="16" t="inlineStr"/>
+      <c r="S25" s="16" t="inlineStr"/>
+      <c r="T25" s="16" t="inlineStr"/>
+      <c r="U25" s="16" t="inlineStr"/>
+      <c r="V25" s="16" t="inlineStr"/>
+      <c r="W25" s="16" t="inlineStr"/>
+      <c r="X25" s="16" t="inlineStr"/>
+      <c r="Y25" s="16" t="inlineStr"/>
+      <c r="Z25" s="16" t="inlineStr"/>
+      <c r="AA25" s="16" t="inlineStr"/>
+      <c r="AB25" s="16" t="inlineStr"/>
+      <c r="AC25" s="16" t="inlineStr"/>
+      <c r="AD25" s="16" t="inlineStr"/>
+      <c r="AE25" s="16" t="inlineStr"/>
+      <c r="AF25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>ITM-024</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>What are the secondary effects of escitalopram when used for anxiety?</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>If by “secondary effects” you mean **side effects**, escitalopram (Lexapro) can cause several when used for anxiety. It’s an SSRI used for **generalized anxiety disorder (GAD)** in adults and children age 7+ in U.S. labeling; it’s usually taken once daily, and full benefit may take several weeks.
 ### Common side effects
@@ -3411,7 +3449,7 @@
 If you tell me your **dose**, **how long you’ve been taking it**, and what symptoms you’re noticing, I can help you sort out what’s common vs. what should be checked promptly.</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>### Drug Label
 According to the FDA-approved drug label, the **most commonly observed adverse reactions** of escitalopram in adults with generalized anxiety disorder (GAD) — occurring at ≥5% incidence and approximately twice the placebo rate — are **nausea, ejaculation disorder** (primarily ejaculatory delay), **insomnia, fatigue, decreased libido, and anorgasmia**.
@@ -3440,51 +3478,51 @@
 Would you like to explore strategies for managing specific escitalopram side effects, such as sexual dysfunction or insomnia, in patients being treated for anxiety?</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr"/>
-      <c r="G26" s="13" t="inlineStr"/>
-      <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
-      <c r="J26" s="13" t="inlineStr"/>
-      <c r="K26" s="13" t="inlineStr"/>
-      <c r="L26" s="13" t="inlineStr"/>
-      <c r="M26" s="13" t="inlineStr"/>
-      <c r="N26" s="13" t="inlineStr"/>
-      <c r="O26" s="13" t="inlineStr"/>
-      <c r="P26" s="13" t="inlineStr"/>
-      <c r="Q26" s="13" t="inlineStr"/>
-      <c r="R26" s="13" t="inlineStr"/>
-      <c r="S26" s="13" t="inlineStr"/>
-      <c r="T26" s="13" t="inlineStr"/>
-      <c r="U26" s="13" t="inlineStr"/>
-      <c r="V26" s="13" t="inlineStr"/>
-      <c r="W26" s="13" t="inlineStr"/>
-      <c r="X26" s="13" t="inlineStr"/>
-      <c r="Y26" s="13" t="inlineStr"/>
-      <c r="Z26" s="13" t="inlineStr"/>
-      <c r="AA26" s="13" t="inlineStr"/>
-      <c r="AB26" s="13" t="inlineStr"/>
-      <c r="AC26" s="13" t="inlineStr"/>
-      <c r="AD26" s="13" t="inlineStr"/>
-      <c r="AE26" s="13" t="inlineStr"/>
-      <c r="AF26" s="14" t="inlineStr"/>
+      <c r="F26" s="16" t="inlineStr"/>
+      <c r="G26" s="16" t="inlineStr"/>
+      <c r="H26" s="16" t="inlineStr"/>
+      <c r="I26" s="16" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr"/>
+      <c r="K26" s="16" t="inlineStr"/>
+      <c r="L26" s="16" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr"/>
+      <c r="N26" s="16" t="inlineStr"/>
+      <c r="O26" s="16" t="inlineStr"/>
+      <c r="P26" s="16" t="inlineStr"/>
+      <c r="Q26" s="16" t="inlineStr"/>
+      <c r="R26" s="16" t="inlineStr"/>
+      <c r="S26" s="16" t="inlineStr"/>
+      <c r="T26" s="16" t="inlineStr"/>
+      <c r="U26" s="16" t="inlineStr"/>
+      <c r="V26" s="16" t="inlineStr"/>
+      <c r="W26" s="16" t="inlineStr"/>
+      <c r="X26" s="16" t="inlineStr"/>
+      <c r="Y26" s="16" t="inlineStr"/>
+      <c r="Z26" s="16" t="inlineStr"/>
+      <c r="AA26" s="16" t="inlineStr"/>
+      <c r="AB26" s="16" t="inlineStr"/>
+      <c r="AC26" s="16" t="inlineStr"/>
+      <c r="AD26" s="16" t="inlineStr"/>
+      <c r="AE26" s="16" t="inlineStr"/>
+      <c r="AF26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>ITM-025</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Surgery</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>Is there evidence that restricting oral intake in a patient with a low-output enterocutaneous fistula who is already on TPN would promote faster fistula closure compared to allowing continued oral feeding?</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>Based on current clinical evidence and nutritional guidelines, the short answer is **no**. There is no robust evidence that restricting oral intake (strict bowel rest / *nil per os* [NPO]) promotes faster or more frequent spontaneous closure of a low-output enterocutaneous fistula (ECF) compared to allowing oral or enteral feeding. In fact, modern evidence suggests the opposite.
 Historically, surgical dogma dictated that complete bowel rest combined with Total Parenteral Nutrition (TPN) was necessary to treat ECFs. The rationale was that eliminating oral intake would drastically reduce gastrointestinal secretions and fistula output, thereby "resting" the bowel and allowing the fistula to heal. However, modern clinical studies and nutritional guidelines (such as those from ASPEN and ESPEN) have shifted significantly away from this approach.
@@ -3507,7 +3545,7 @@
 If your patient has a low-output ECF, is already on TPN, and can tolerate food without the fistula output becoming unmanageable or detrimental to skin integrity, **allowing and advancing oral intake (often starting with a low-residue or high-protein diet) is the evidence-based recommendation**. Restricting oral intake simply to "rest the bowel" is an outdated concept that will not speed up the closure of the fistula and deprives the gastrointestinal tract of the direct nutrients it needs to heal.</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>**No robust evidence supports restricting oral intake to promote faster closure** of a low-output enterocutaneous fistula (ECF) in a patient already receiving TPN. The traditional practice of NPO with TPN for "bowel rest" is based largely on historical convention rather than high-quality comparative data, and current guidelines and literature increasingly challenge this dogma — particularly for low-output fistulas.
 **What the guidelines say**
@@ -3525,51 +3563,51 @@
 Would you like to explore the role of somatostatin analogues as adjuncts for reducing fistula output and whether they have a clearer evidence base for accelerating closure?</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr"/>
-      <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr"/>
-      <c r="I27" s="13" t="inlineStr"/>
-      <c r="J27" s="13" t="inlineStr"/>
-      <c r="K27" s="13" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
-      <c r="M27" s="13" t="inlineStr"/>
-      <c r="N27" s="13" t="inlineStr"/>
-      <c r="O27" s="13" t="inlineStr"/>
-      <c r="P27" s="13" t="inlineStr"/>
-      <c r="Q27" s="13" t="inlineStr"/>
-      <c r="R27" s="13" t="inlineStr"/>
-      <c r="S27" s="13" t="inlineStr"/>
-      <c r="T27" s="13" t="inlineStr"/>
-      <c r="U27" s="13" t="inlineStr"/>
-      <c r="V27" s="13" t="inlineStr"/>
-      <c r="W27" s="13" t="inlineStr"/>
-      <c r="X27" s="13" t="inlineStr"/>
-      <c r="Y27" s="13" t="inlineStr"/>
-      <c r="Z27" s="13" t="inlineStr"/>
-      <c r="AA27" s="13" t="inlineStr"/>
-      <c r="AB27" s="13" t="inlineStr"/>
-      <c r="AC27" s="13" t="inlineStr"/>
-      <c r="AD27" s="13" t="inlineStr"/>
-      <c r="AE27" s="13" t="inlineStr"/>
-      <c r="AF27" s="14" t="inlineStr"/>
+      <c r="F27" s="16" t="inlineStr"/>
+      <c r="G27" s="16" t="inlineStr"/>
+      <c r="H27" s="16" t="inlineStr"/>
+      <c r="I27" s="16" t="inlineStr"/>
+      <c r="J27" s="16" t="inlineStr"/>
+      <c r="K27" s="16" t="inlineStr"/>
+      <c r="L27" s="16" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr"/>
+      <c r="N27" s="16" t="inlineStr"/>
+      <c r="O27" s="16" t="inlineStr"/>
+      <c r="P27" s="16" t="inlineStr"/>
+      <c r="Q27" s="16" t="inlineStr"/>
+      <c r="R27" s="16" t="inlineStr"/>
+      <c r="S27" s="16" t="inlineStr"/>
+      <c r="T27" s="16" t="inlineStr"/>
+      <c r="U27" s="16" t="inlineStr"/>
+      <c r="V27" s="16" t="inlineStr"/>
+      <c r="W27" s="16" t="inlineStr"/>
+      <c r="X27" s="16" t="inlineStr"/>
+      <c r="Y27" s="16" t="inlineStr"/>
+      <c r="Z27" s="16" t="inlineStr"/>
+      <c r="AA27" s="16" t="inlineStr"/>
+      <c r="AB27" s="16" t="inlineStr"/>
+      <c r="AC27" s="16" t="inlineStr"/>
+      <c r="AD27" s="16" t="inlineStr"/>
+      <c r="AE27" s="16" t="inlineStr"/>
+      <c r="AF27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>ITM-026</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Pediatrics</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>What are the indications for varicella-zoster immunoglobulin administration in neonates?</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Varicella-zoster immune globulin (VZIG, commercially available as VariZIG in the United States) is indicated for post-exposure prophylaxis in high-risk neonates to prevent or attenuate severe, potentially fatal varicella (chickenpox) infection.
 According to the Centers for Disease Control and Prevention (CDC) and the American Academy of Pediatrics (AAP), the specific indications for VZIG administration in neonates following a significant exposure to the varicella-zoster virus (VZV) are:
@@ -3588,7 +3626,7 @@
 For optimal effectiveness, VZIG should be administered as soon as possible after exposure. It is most effective when given **within 96 hours (4 days)**, but it can still be administered **up to 10 days** post-exposure. If VZIG is unavailable, Intravenous Immune Globulin (IVIG) may be used as an alternative.</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Per CDC/ACIP and AAP guidelines, **varicella-zoster immune globulin (VariZIG) is indicated in three neonatal populations** following exposure to varicella-zoster virus (VZV):
 **Neonatal Indications for VariZIG**
@@ -3604,51 +3642,51 @@
 Would you like to explore the role of acyclovir prophylaxis or treatment in neonates who develop varicella despite VariZIG administration?</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr"/>
-      <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr"/>
-      <c r="I28" s="13" t="inlineStr"/>
-      <c r="J28" s="13" t="inlineStr"/>
-      <c r="K28" s="13" t="inlineStr"/>
-      <c r="L28" s="13" t="inlineStr"/>
-      <c r="M28" s="13" t="inlineStr"/>
-      <c r="N28" s="13" t="inlineStr"/>
-      <c r="O28" s="13" t="inlineStr"/>
-      <c r="P28" s="13" t="inlineStr"/>
-      <c r="Q28" s="13" t="inlineStr"/>
-      <c r="R28" s="13" t="inlineStr"/>
-      <c r="S28" s="13" t="inlineStr"/>
-      <c r="T28" s="13" t="inlineStr"/>
-      <c r="U28" s="13" t="inlineStr"/>
-      <c r="V28" s="13" t="inlineStr"/>
-      <c r="W28" s="13" t="inlineStr"/>
-      <c r="X28" s="13" t="inlineStr"/>
-      <c r="Y28" s="13" t="inlineStr"/>
-      <c r="Z28" s="13" t="inlineStr"/>
-      <c r="AA28" s="13" t="inlineStr"/>
-      <c r="AB28" s="13" t="inlineStr"/>
-      <c r="AC28" s="13" t="inlineStr"/>
-      <c r="AD28" s="13" t="inlineStr"/>
-      <c r="AE28" s="13" t="inlineStr"/>
-      <c r="AF28" s="14" t="inlineStr"/>
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="16" t="inlineStr"/>
+      <c r="H28" s="16" t="inlineStr"/>
+      <c r="I28" s="16" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr"/>
+      <c r="K28" s="16" t="inlineStr"/>
+      <c r="L28" s="16" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr"/>
+      <c r="N28" s="16" t="inlineStr"/>
+      <c r="O28" s="16" t="inlineStr"/>
+      <c r="P28" s="16" t="inlineStr"/>
+      <c r="Q28" s="16" t="inlineStr"/>
+      <c r="R28" s="16" t="inlineStr"/>
+      <c r="S28" s="16" t="inlineStr"/>
+      <c r="T28" s="16" t="inlineStr"/>
+      <c r="U28" s="16" t="inlineStr"/>
+      <c r="V28" s="16" t="inlineStr"/>
+      <c r="W28" s="16" t="inlineStr"/>
+      <c r="X28" s="16" t="inlineStr"/>
+      <c r="Y28" s="16" t="inlineStr"/>
+      <c r="Z28" s="16" t="inlineStr"/>
+      <c r="AA28" s="16" t="inlineStr"/>
+      <c r="AB28" s="16" t="inlineStr"/>
+      <c r="AC28" s="16" t="inlineStr"/>
+      <c r="AD28" s="16" t="inlineStr"/>
+      <c r="AE28" s="16" t="inlineStr"/>
+      <c r="AF28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>ITM-027</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>What is the next step in management for a patient with Stage IIB triple-negative breast cancer (cT2, cN0, cM0, G3) whose chemotherapy was delayed due to ANC of 0.9 during cycle 2, and whose ANC remains low at 0.8 one week later?</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>### Clinical Context
 This patient has **Stage IIB TNBC (cT2N0M0, G3)** receiving curative-intent chemotherapy (most likely neoadjuvant therapy, per the KEYNOTE-522 paradigm with carboplatin/taxane → anthracycline ± pembrolizumab). The key issue is **chemotherapy-induced neutropenia causing a treatment delay**, with persistent Grade 3 neutropenia (ANC 0.8 ×10⁹/L, i.e., 800/µL) one week after the initial hold.
@@ -3671,7 +3709,7 @@
 *This is general educational information and not a substitute for management by the treating oncology team, who can apply the specific protocol, local thresholds, and patient factors.*</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>The immediate next step is to **administer G-CSF (filgrastim) to raise the ANC** so that chemotherapy can resume without further delay. This patient has experienced a **dose-limiting neutropenic event** — persistent ANC &lt;1.0 × 10⁹/L preventing on-schedule chemotherapy — which constitutes a clear indication for secondary prophylaxis with G-CSF per NCCN guidelines.
 **Clinical Reasoning and Guideline-Based Approach**
@@ -3694,51 +3732,51 @@
 Would you like to explore the specific febrile neutropenia risk category for this patient's chemotherapy regimen and whether primary prophylaxis should have been initiated from cycle 1?</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr"/>
-      <c r="G29" s="13" t="inlineStr"/>
-      <c r="H29" s="13" t="inlineStr"/>
-      <c r="I29" s="13" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr"/>
-      <c r="K29" s="13" t="inlineStr"/>
-      <c r="L29" s="13" t="inlineStr"/>
-      <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="13" t="inlineStr"/>
-      <c r="O29" s="13" t="inlineStr"/>
-      <c r="P29" s="13" t="inlineStr"/>
-      <c r="Q29" s="13" t="inlineStr"/>
-      <c r="R29" s="13" t="inlineStr"/>
-      <c r="S29" s="13" t="inlineStr"/>
-      <c r="T29" s="13" t="inlineStr"/>
-      <c r="U29" s="13" t="inlineStr"/>
-      <c r="V29" s="13" t="inlineStr"/>
-      <c r="W29" s="13" t="inlineStr"/>
-      <c r="X29" s="13" t="inlineStr"/>
-      <c r="Y29" s="13" t="inlineStr"/>
-      <c r="Z29" s="13" t="inlineStr"/>
-      <c r="AA29" s="13" t="inlineStr"/>
-      <c r="AB29" s="13" t="inlineStr"/>
-      <c r="AC29" s="13" t="inlineStr"/>
-      <c r="AD29" s="13" t="inlineStr"/>
-      <c r="AE29" s="13" t="inlineStr"/>
-      <c r="AF29" s="14" t="inlineStr"/>
+      <c r="F29" s="16" t="inlineStr"/>
+      <c r="G29" s="16" t="inlineStr"/>
+      <c r="H29" s="16" t="inlineStr"/>
+      <c r="I29" s="16" t="inlineStr"/>
+      <c r="J29" s="16" t="inlineStr"/>
+      <c r="K29" s="16" t="inlineStr"/>
+      <c r="L29" s="16" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr"/>
+      <c r="N29" s="16" t="inlineStr"/>
+      <c r="O29" s="16" t="inlineStr"/>
+      <c r="P29" s="16" t="inlineStr"/>
+      <c r="Q29" s="16" t="inlineStr"/>
+      <c r="R29" s="16" t="inlineStr"/>
+      <c r="S29" s="16" t="inlineStr"/>
+      <c r="T29" s="16" t="inlineStr"/>
+      <c r="U29" s="16" t="inlineStr"/>
+      <c r="V29" s="16" t="inlineStr"/>
+      <c r="W29" s="16" t="inlineStr"/>
+      <c r="X29" s="16" t="inlineStr"/>
+      <c r="Y29" s="16" t="inlineStr"/>
+      <c r="Z29" s="16" t="inlineStr"/>
+      <c r="AA29" s="16" t="inlineStr"/>
+      <c r="AB29" s="16" t="inlineStr"/>
+      <c r="AC29" s="16" t="inlineStr"/>
+      <c r="AD29" s="16" t="inlineStr"/>
+      <c r="AE29" s="16" t="inlineStr"/>
+      <c r="AF29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>ITM-028</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>What is the next step in management for a patient with Stage IIB triple-negative breast cancer (cT2, cN0, cM0, G3) whose chemotherapy was delayed due to ANC of 0.9 during cycle 2, and whose ANC remains low at 0.8 one week later?</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>For a patient with early-stage (Stage IIB) triple-negative breast cancer (TNBC) being treated with curative intent, maintaining the dose intensity of chemotherapy is critical for overall survival and maximizing the chance of a pathologic complete response (pCR).
 The immediate next step in management involves the following approach:
@@ -3754,7 +3792,7 @@
 Hold treatment, recheck the CBC in a few days to a week until ANC &gt; 1.0, give the planned full dose of chemotherapy, and add prophylactic G-CSF 24–72 hours after the infusion for this and all future cycles.</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>The immediate next step is to **administer G-CSF (filgrastim) to raise the ANC** so that chemotherapy can resume without further delay. This patient has experienced a **dose-limiting neutropenic event** — persistent ANC &lt;1.0 × 10⁹/L preventing on-schedule chemotherapy — which constitutes a clear indication for secondary prophylaxis with G-CSF per NCCN guidelines.
 **Clinical Reasoning and Guideline-Based Approach**
@@ -3777,51 +3815,51 @@
 Would you like to explore the specific febrile neutropenia risk category for this patient's chemotherapy regimen and whether primary prophylaxis should have been initiated from cycle 1?</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr"/>
-      <c r="G30" s="13" t="inlineStr"/>
-      <c r="H30" s="13" t="inlineStr"/>
-      <c r="I30" s="13" t="inlineStr"/>
-      <c r="J30" s="13" t="inlineStr"/>
-      <c r="K30" s="13" t="inlineStr"/>
-      <c r="L30" s="13" t="inlineStr"/>
-      <c r="M30" s="13" t="inlineStr"/>
-      <c r="N30" s="13" t="inlineStr"/>
-      <c r="O30" s="13" t="inlineStr"/>
-      <c r="P30" s="13" t="inlineStr"/>
-      <c r="Q30" s="13" t="inlineStr"/>
-      <c r="R30" s="13" t="inlineStr"/>
-      <c r="S30" s="13" t="inlineStr"/>
-      <c r="T30" s="13" t="inlineStr"/>
-      <c r="U30" s="13" t="inlineStr"/>
-      <c r="V30" s="13" t="inlineStr"/>
-      <c r="W30" s="13" t="inlineStr"/>
-      <c r="X30" s="13" t="inlineStr"/>
-      <c r="Y30" s="13" t="inlineStr"/>
-      <c r="Z30" s="13" t="inlineStr"/>
-      <c r="AA30" s="13" t="inlineStr"/>
-      <c r="AB30" s="13" t="inlineStr"/>
-      <c r="AC30" s="13" t="inlineStr"/>
-      <c r="AD30" s="13" t="inlineStr"/>
-      <c r="AE30" s="13" t="inlineStr"/>
-      <c r="AF30" s="14" t="inlineStr"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="16" t="inlineStr"/>
+      <c r="H30" s="16" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr"/>
+      <c r="J30" s="16" t="inlineStr"/>
+      <c r="K30" s="16" t="inlineStr"/>
+      <c r="L30" s="16" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr"/>
+      <c r="N30" s="16" t="inlineStr"/>
+      <c r="O30" s="16" t="inlineStr"/>
+      <c r="P30" s="16" t="inlineStr"/>
+      <c r="Q30" s="16" t="inlineStr"/>
+      <c r="R30" s="16" t="inlineStr"/>
+      <c r="S30" s="16" t="inlineStr"/>
+      <c r="T30" s="16" t="inlineStr"/>
+      <c r="U30" s="16" t="inlineStr"/>
+      <c r="V30" s="16" t="inlineStr"/>
+      <c r="W30" s="16" t="inlineStr"/>
+      <c r="X30" s="16" t="inlineStr"/>
+      <c r="Y30" s="16" t="inlineStr"/>
+      <c r="Z30" s="16" t="inlineStr"/>
+      <c r="AA30" s="16" t="inlineStr"/>
+      <c r="AB30" s="16" t="inlineStr"/>
+      <c r="AC30" s="16" t="inlineStr"/>
+      <c r="AD30" s="16" t="inlineStr"/>
+      <c r="AE30" s="16" t="inlineStr"/>
+      <c r="AF30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>ITM-029</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>What is the next step in management for a patient with Stage IIB triple-negative breast cancer (cT2, cN0, cM0, G3) whose chemotherapy was delayed due to ANC of 0.9 during cycle 2, and whose ANC remains low at 0.8 one week later?</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>Assuming the patient is **afebrile and clinically stable**, the next step is:
 **Continue to hold cytotoxic chemotherapy because the ANC is still 0.8 × 10⁹/L, and arrange short-interval repeat CBC/oncology review; add G-CSF support and resume chemotherapy once ANC recovers, with consideration of dose modification for subsequent cycles.**
@@ -3832,7 +3870,7 @@
 **Do not give the next cytotoxic chemotherapy dose today at ANC 0.8.** If she develops **fever ≥38°C/100.4°F, chills, or signs of infection**, this becomes possible febrile neutropenia and requires urgent evaluation and empiric antibiotics within 1 hour of triage.</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>The immediate next step is to **administer G-CSF (filgrastim) to raise the ANC** so that chemotherapy can resume without further delay. This patient has experienced a **dose-limiting neutropenic event** — persistent ANC &lt;1.0 × 10⁹/L preventing on-schedule chemotherapy — which constitutes a clear indication for secondary prophylaxis with G-CSF per NCCN guidelines.
 **Clinical Reasoning and Guideline-Based Approach**
@@ -3855,51 +3893,51 @@
 Would you like to explore the specific febrile neutropenia risk category for this patient's chemotherapy regimen and whether primary prophylaxis should have been initiated from cycle 1?</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr"/>
-      <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr"/>
-      <c r="I31" s="13" t="inlineStr"/>
-      <c r="J31" s="13" t="inlineStr"/>
-      <c r="K31" s="13" t="inlineStr"/>
-      <c r="L31" s="13" t="inlineStr"/>
-      <c r="M31" s="13" t="inlineStr"/>
-      <c r="N31" s="13" t="inlineStr"/>
-      <c r="O31" s="13" t="inlineStr"/>
-      <c r="P31" s="13" t="inlineStr"/>
-      <c r="Q31" s="13" t="inlineStr"/>
-      <c r="R31" s="13" t="inlineStr"/>
-      <c r="S31" s="13" t="inlineStr"/>
-      <c r="T31" s="13" t="inlineStr"/>
-      <c r="U31" s="13" t="inlineStr"/>
-      <c r="V31" s="13" t="inlineStr"/>
-      <c r="W31" s="13" t="inlineStr"/>
-      <c r="X31" s="13" t="inlineStr"/>
-      <c r="Y31" s="13" t="inlineStr"/>
-      <c r="Z31" s="13" t="inlineStr"/>
-      <c r="AA31" s="13" t="inlineStr"/>
-      <c r="AB31" s="13" t="inlineStr"/>
-      <c r="AC31" s="13" t="inlineStr"/>
-      <c r="AD31" s="13" t="inlineStr"/>
-      <c r="AE31" s="13" t="inlineStr"/>
-      <c r="AF31" s="14" t="inlineStr"/>
+      <c r="F31" s="16" t="inlineStr"/>
+      <c r="G31" s="16" t="inlineStr"/>
+      <c r="H31" s="16" t="inlineStr"/>
+      <c r="I31" s="16" t="inlineStr"/>
+      <c r="J31" s="16" t="inlineStr"/>
+      <c r="K31" s="16" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr"/>
+      <c r="O31" s="16" t="inlineStr"/>
+      <c r="P31" s="16" t="inlineStr"/>
+      <c r="Q31" s="16" t="inlineStr"/>
+      <c r="R31" s="16" t="inlineStr"/>
+      <c r="S31" s="16" t="inlineStr"/>
+      <c r="T31" s="16" t="inlineStr"/>
+      <c r="U31" s="16" t="inlineStr"/>
+      <c r="V31" s="16" t="inlineStr"/>
+      <c r="W31" s="16" t="inlineStr"/>
+      <c r="X31" s="16" t="inlineStr"/>
+      <c r="Y31" s="16" t="inlineStr"/>
+      <c r="Z31" s="16" t="inlineStr"/>
+      <c r="AA31" s="16" t="inlineStr"/>
+      <c r="AB31" s="16" t="inlineStr"/>
+      <c r="AC31" s="16" t="inlineStr"/>
+      <c r="AD31" s="16" t="inlineStr"/>
+      <c r="AE31" s="16" t="inlineStr"/>
+      <c r="AF31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>ITM-030</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Radiology</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>What MRI findings help differentiate infectious discitis from other causes of disc space abnormality?</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>Magnetic Resonance Imaging (MRI) is the gold standard for evaluating spinal infections, boasting a sensitivity and specificity of over 90%. Differentiating infectious discitis (often presenting as spondylodiscitis, which involves both the disc and adjacent vertebrae) from other mimicking pathologies is critical to prevent severe neurological compromise or unnecessary invasive biopsies.
 Here is a breakdown of the hallmark MRI findings of infectious discitis, followed by the specific features that differentiate it from other common causes of disc space and vertebral abnormalities.
@@ -3936,7 +3974,7 @@
 It is worth noting that while pyogenic (bacterial) infections destroy the disc quickly, granulomatous infections like **Tuberculosis** behave atypically. TB often spreads beneath the anterior longitudinal ligament (subligamentous spread), involving multiple contiguous vertebrae while **sparing the intervertebral disc** until very late in the disease process. TB is also distinguished by the presence of massive, often calcified, paraspinal "cold" abscesses that seem disproportionately large compared to the degree of bone destruction.</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Several key MRI findings help distinguish **infectious discitis/spondylodiscitis** from degenerative, neoplastic, and inflammatory mimics. MRI has a reported **sensitivity of 96–97%, specificity of 93–94%, and accuracy of ~94%** for diagnosing vertebral osteomyelitis.
 **Classic MRI Features of Infectious Discitis**
@@ -3964,51 +4002,51 @@
 Would you like to explore the optimal biopsy strategy and timing when MRI findings are equivocal for infection versus degeneration?</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr"/>
-      <c r="G32" s="13" t="inlineStr"/>
-      <c r="H32" s="13" t="inlineStr"/>
-      <c r="I32" s="13" t="inlineStr"/>
-      <c r="J32" s="13" t="inlineStr"/>
-      <c r="K32" s="13" t="inlineStr"/>
-      <c r="L32" s="13" t="inlineStr"/>
-      <c r="M32" s="13" t="inlineStr"/>
-      <c r="N32" s="13" t="inlineStr"/>
-      <c r="O32" s="13" t="inlineStr"/>
-      <c r="P32" s="13" t="inlineStr"/>
-      <c r="Q32" s="13" t="inlineStr"/>
-      <c r="R32" s="13" t="inlineStr"/>
-      <c r="S32" s="13" t="inlineStr"/>
-      <c r="T32" s="13" t="inlineStr"/>
-      <c r="U32" s="13" t="inlineStr"/>
-      <c r="V32" s="13" t="inlineStr"/>
-      <c r="W32" s="13" t="inlineStr"/>
-      <c r="X32" s="13" t="inlineStr"/>
-      <c r="Y32" s="13" t="inlineStr"/>
-      <c r="Z32" s="13" t="inlineStr"/>
-      <c r="AA32" s="13" t="inlineStr"/>
-      <c r="AB32" s="13" t="inlineStr"/>
-      <c r="AC32" s="13" t="inlineStr"/>
-      <c r="AD32" s="13" t="inlineStr"/>
-      <c r="AE32" s="13" t="inlineStr"/>
-      <c r="AF32" s="14" t="inlineStr"/>
+      <c r="F32" s="16" t="inlineStr"/>
+      <c r="G32" s="16" t="inlineStr"/>
+      <c r="H32" s="16" t="inlineStr"/>
+      <c r="I32" s="16" t="inlineStr"/>
+      <c r="J32" s="16" t="inlineStr"/>
+      <c r="K32" s="16" t="inlineStr"/>
+      <c r="L32" s="16" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr"/>
+      <c r="N32" s="16" t="inlineStr"/>
+      <c r="O32" s="16" t="inlineStr"/>
+      <c r="P32" s="16" t="inlineStr"/>
+      <c r="Q32" s="16" t="inlineStr"/>
+      <c r="R32" s="16" t="inlineStr"/>
+      <c r="S32" s="16" t="inlineStr"/>
+      <c r="T32" s="16" t="inlineStr"/>
+      <c r="U32" s="16" t="inlineStr"/>
+      <c r="V32" s="16" t="inlineStr"/>
+      <c r="W32" s="16" t="inlineStr"/>
+      <c r="X32" s="16" t="inlineStr"/>
+      <c r="Y32" s="16" t="inlineStr"/>
+      <c r="Z32" s="16" t="inlineStr"/>
+      <c r="AA32" s="16" t="inlineStr"/>
+      <c r="AB32" s="16" t="inlineStr"/>
+      <c r="AC32" s="16" t="inlineStr"/>
+      <c r="AD32" s="16" t="inlineStr"/>
+      <c r="AE32" s="16" t="inlineStr"/>
+      <c r="AF32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>ITM-031</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Radiology</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>What MRI findings help differentiate infectious discitis from other causes of disc space abnormality?</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>Several key MRI findings help distinguish **infectious discitis/spondylodiscitis** from degenerative, neoplastic, and inflammatory mimics. MRI has a reported **sensitivity of 96–97%, specificity of 93–94%, and accuracy of ~94%** for diagnosing vertebral osteomyelitis.
 **Classic MRI Features of Infectious Discitis**
@@ -4036,7 +4074,7 @@
 Would you like to explore the optimal biopsy strategy and timing when MRI findings are equivocal for infection versus degeneration?</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>MRI findings that **favor infectious discitis / spondylodiscitis** over degenerative, inflammatory, traumatic, or neoplastic causes of disc-space abnormality include:
 - **Abnormal disc signal**, especially **high T2/STIR signal within the disc** — fluid-like disc signal is more suspicious for infection than simple degenerative disc desiccation.
@@ -4050,51 +4088,51 @@
 Findings that make **degenerative disease** more likely include a desiccated low-T2 disc, vacuum phenomenon, preserved endplate cortex, lack of paraspinal/epidural soft-tissue abnormality, and a positive DWI claw sign. Early infection can still be subtle or nonspecific, so MRI findings should be correlated with fever, inflammatory markers, blood cultures, and sometimes biopsy.</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr"/>
-      <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="13" t="inlineStr"/>
-      <c r="I33" s="13" t="inlineStr"/>
-      <c r="J33" s="13" t="inlineStr"/>
-      <c r="K33" s="13" t="inlineStr"/>
-      <c r="L33" s="13" t="inlineStr"/>
-      <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="13" t="inlineStr"/>
-      <c r="O33" s="13" t="inlineStr"/>
-      <c r="P33" s="13" t="inlineStr"/>
-      <c r="Q33" s="13" t="inlineStr"/>
-      <c r="R33" s="13" t="inlineStr"/>
-      <c r="S33" s="13" t="inlineStr"/>
-      <c r="T33" s="13" t="inlineStr"/>
-      <c r="U33" s="13" t="inlineStr"/>
-      <c r="V33" s="13" t="inlineStr"/>
-      <c r="W33" s="13" t="inlineStr"/>
-      <c r="X33" s="13" t="inlineStr"/>
-      <c r="Y33" s="13" t="inlineStr"/>
-      <c r="Z33" s="13" t="inlineStr"/>
-      <c r="AA33" s="13" t="inlineStr"/>
-      <c r="AB33" s="13" t="inlineStr"/>
-      <c r="AC33" s="13" t="inlineStr"/>
-      <c r="AD33" s="13" t="inlineStr"/>
-      <c r="AE33" s="13" t="inlineStr"/>
-      <c r="AF33" s="14" t="inlineStr"/>
+      <c r="F33" s="16" t="inlineStr"/>
+      <c r="G33" s="16" t="inlineStr"/>
+      <c r="H33" s="16" t="inlineStr"/>
+      <c r="I33" s="16" t="inlineStr"/>
+      <c r="J33" s="16" t="inlineStr"/>
+      <c r="K33" s="16" t="inlineStr"/>
+      <c r="L33" s="16" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr"/>
+      <c r="O33" s="16" t="inlineStr"/>
+      <c r="P33" s="16" t="inlineStr"/>
+      <c r="Q33" s="16" t="inlineStr"/>
+      <c r="R33" s="16" t="inlineStr"/>
+      <c r="S33" s="16" t="inlineStr"/>
+      <c r="T33" s="16" t="inlineStr"/>
+      <c r="U33" s="16" t="inlineStr"/>
+      <c r="V33" s="16" t="inlineStr"/>
+      <c r="W33" s="16" t="inlineStr"/>
+      <c r="X33" s="16" t="inlineStr"/>
+      <c r="Y33" s="16" t="inlineStr"/>
+      <c r="Z33" s="16" t="inlineStr"/>
+      <c r="AA33" s="16" t="inlineStr"/>
+      <c r="AB33" s="16" t="inlineStr"/>
+      <c r="AC33" s="16" t="inlineStr"/>
+      <c r="AD33" s="16" t="inlineStr"/>
+      <c r="AE33" s="16" t="inlineStr"/>
+      <c r="AF33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>ITM-032</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Allergy &amp; Immunology</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Management of hypersensitivity reaction</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>### Management of Hypersensitivity Reactions
 Hypersensitivity reactions are exaggerated or inappropriate immune responses that cause tissue damage. Management depends on the **type** of reaction (Gell and Coombs classification I–IV) and its **severity**. Below is a practical overview.
@@ -4160,7 +4198,7 @@
 This information is for educational purposes and is not a substitute for clinical judgment or local protocols.</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Management of hypersensitivity reactions depends on the **severity and type of reaction**, ranging from mild cutaneous symptoms (urticaria) to life-threatening anaphylaxis. The approach is organized below by clinical severity.
 ---
@@ -4199,51 +4237,51 @@
 Would you like to explore the specific desensitization protocols for a particular drug class, such as platinum-based chemotherapeutics or beta-lactam antibiotics?</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr"/>
-      <c r="G34" s="13" t="inlineStr"/>
-      <c r="H34" s="13" t="inlineStr"/>
-      <c r="I34" s="13" t="inlineStr"/>
-      <c r="J34" s="13" t="inlineStr"/>
-      <c r="K34" s="13" t="inlineStr"/>
-      <c r="L34" s="13" t="inlineStr"/>
-      <c r="M34" s="13" t="inlineStr"/>
-      <c r="N34" s="13" t="inlineStr"/>
-      <c r="O34" s="13" t="inlineStr"/>
-      <c r="P34" s="13" t="inlineStr"/>
-      <c r="Q34" s="13" t="inlineStr"/>
-      <c r="R34" s="13" t="inlineStr"/>
-      <c r="S34" s="13" t="inlineStr"/>
-      <c r="T34" s="13" t="inlineStr"/>
-      <c r="U34" s="13" t="inlineStr"/>
-      <c r="V34" s="13" t="inlineStr"/>
-      <c r="W34" s="13" t="inlineStr"/>
-      <c r="X34" s="13" t="inlineStr"/>
-      <c r="Y34" s="13" t="inlineStr"/>
-      <c r="Z34" s="13" t="inlineStr"/>
-      <c r="AA34" s="13" t="inlineStr"/>
-      <c r="AB34" s="13" t="inlineStr"/>
-      <c r="AC34" s="13" t="inlineStr"/>
-      <c r="AD34" s="13" t="inlineStr"/>
-      <c r="AE34" s="13" t="inlineStr"/>
-      <c r="AF34" s="14" t="inlineStr"/>
+      <c r="F34" s="16" t="inlineStr"/>
+      <c r="G34" s="16" t="inlineStr"/>
+      <c r="H34" s="16" t="inlineStr"/>
+      <c r="I34" s="16" t="inlineStr"/>
+      <c r="J34" s="16" t="inlineStr"/>
+      <c r="K34" s="16" t="inlineStr"/>
+      <c r="L34" s="16" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr"/>
+      <c r="N34" s="16" t="inlineStr"/>
+      <c r="O34" s="16" t="inlineStr"/>
+      <c r="P34" s="16" t="inlineStr"/>
+      <c r="Q34" s="16" t="inlineStr"/>
+      <c r="R34" s="16" t="inlineStr"/>
+      <c r="S34" s="16" t="inlineStr"/>
+      <c r="T34" s="16" t="inlineStr"/>
+      <c r="U34" s="16" t="inlineStr"/>
+      <c r="V34" s="16" t="inlineStr"/>
+      <c r="W34" s="16" t="inlineStr"/>
+      <c r="X34" s="16" t="inlineStr"/>
+      <c r="Y34" s="16" t="inlineStr"/>
+      <c r="Z34" s="16" t="inlineStr"/>
+      <c r="AA34" s="16" t="inlineStr"/>
+      <c r="AB34" s="16" t="inlineStr"/>
+      <c r="AC34" s="16" t="inlineStr"/>
+      <c r="AD34" s="16" t="inlineStr"/>
+      <c r="AE34" s="16" t="inlineStr"/>
+      <c r="AF34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>ITM-033</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>Allergy &amp; Immunology</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Management of hypersensitivity reaction</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>If a **hypersensitivity reaction is happening now** and there is **trouble breathing, throat/tongue swelling, dizziness/fainting, low blood pressure, wheeze, repetitive vomiting, or rapidly spreading hives**, treat it as **anaphylaxis**: **give epinephrine immediately and call emergency services (911 in the U.S.)**. Epinephrine is the first and most important treatment, with no absolute contraindication in anaphylaxis.
 ### 1) Stop the trigger and assess ABCs
@@ -4286,7 +4324,7 @@
 If you tell me the context—**drug/infusion reaction, vaccine reaction, food allergy, contrast reaction, or perioperative reaction**—I can tailor the management steps and medication dosing more specifically.</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Management of hypersensitivity reactions depends on the **severity and type of reaction**, ranging from mild cutaneous symptoms (urticaria) to life-threatening anaphylaxis. The approach is organized below by clinical severity.
 ---
@@ -4325,51 +4363,51 @@
 Would you like to explore the specific desensitization protocols for a particular drug class, such as platinum-based chemotherapeutics or beta-lactam antibiotics?</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr"/>
-      <c r="G35" s="13" t="inlineStr"/>
-      <c r="H35" s="13" t="inlineStr"/>
-      <c r="I35" s="13" t="inlineStr"/>
-      <c r="J35" s="13" t="inlineStr"/>
-      <c r="K35" s="13" t="inlineStr"/>
-      <c r="L35" s="13" t="inlineStr"/>
-      <c r="M35" s="13" t="inlineStr"/>
-      <c r="N35" s="13" t="inlineStr"/>
-      <c r="O35" s="13" t="inlineStr"/>
-      <c r="P35" s="13" t="inlineStr"/>
-      <c r="Q35" s="13" t="inlineStr"/>
-      <c r="R35" s="13" t="inlineStr"/>
-      <c r="S35" s="13" t="inlineStr"/>
-      <c r="T35" s="13" t="inlineStr"/>
-      <c r="U35" s="13" t="inlineStr"/>
-      <c r="V35" s="13" t="inlineStr"/>
-      <c r="W35" s="13" t="inlineStr"/>
-      <c r="X35" s="13" t="inlineStr"/>
-      <c r="Y35" s="13" t="inlineStr"/>
-      <c r="Z35" s="13" t="inlineStr"/>
-      <c r="AA35" s="13" t="inlineStr"/>
-      <c r="AB35" s="13" t="inlineStr"/>
-      <c r="AC35" s="13" t="inlineStr"/>
-      <c r="AD35" s="13" t="inlineStr"/>
-      <c r="AE35" s="13" t="inlineStr"/>
-      <c r="AF35" s="14" t="inlineStr"/>
+      <c r="F35" s="16" t="inlineStr"/>
+      <c r="G35" s="16" t="inlineStr"/>
+      <c r="H35" s="16" t="inlineStr"/>
+      <c r="I35" s="16" t="inlineStr"/>
+      <c r="J35" s="16" t="inlineStr"/>
+      <c r="K35" s="16" t="inlineStr"/>
+      <c r="L35" s="16" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr"/>
+      <c r="O35" s="16" t="inlineStr"/>
+      <c r="P35" s="16" t="inlineStr"/>
+      <c r="Q35" s="16" t="inlineStr"/>
+      <c r="R35" s="16" t="inlineStr"/>
+      <c r="S35" s="16" t="inlineStr"/>
+      <c r="T35" s="16" t="inlineStr"/>
+      <c r="U35" s="16" t="inlineStr"/>
+      <c r="V35" s="16" t="inlineStr"/>
+      <c r="W35" s="16" t="inlineStr"/>
+      <c r="X35" s="16" t="inlineStr"/>
+      <c r="Y35" s="16" t="inlineStr"/>
+      <c r="Z35" s="16" t="inlineStr"/>
+      <c r="AA35" s="16" t="inlineStr"/>
+      <c r="AB35" s="16" t="inlineStr"/>
+      <c r="AC35" s="16" t="inlineStr"/>
+      <c r="AD35" s="16" t="inlineStr"/>
+      <c r="AE35" s="16" t="inlineStr"/>
+      <c r="AF35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>ITM-034</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Rheumatology</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>Can beta blockers worsen or trigger Raynaud's phenomenon?</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>**Yes, beta blockers are recognized as a potential trigger or aggravating factor for Raynaud's phenomenon (RP), though the evidence is more nuanced than commonly assumed.** The association is well-established in pharmacology references and drug labeling, but well-designed clinical studies have produced conflicting results.
 **Evidence Supporting the Association**
@@ -4391,7 +4429,7 @@
 Would you like to explore which alternative antihypertensive or rate-control agents are preferred in patients with significant Raynaud's phenomenon?</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>**Yes, beta blockers can both worsen existing Raynaud’s phenomenon and trigger Raynaud's-like symptoms** (such as unusually cold hands and feet) in people who have never had the condition before.
 Here is a breakdown of why this happens, which medications are most likely to cause it, and how it is typically managed:
@@ -4411,51 +4449,51 @@
 *Disclaimer: I am an AI, not a doctor. This information is for educational purposes. Always consult with a healthcare professional before making any changes to your prescription medications.*</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr"/>
-      <c r="G36" s="13" t="inlineStr"/>
-      <c r="H36" s="13" t="inlineStr"/>
-      <c r="I36" s="13" t="inlineStr"/>
-      <c r="J36" s="13" t="inlineStr"/>
-      <c r="K36" s="13" t="inlineStr"/>
-      <c r="L36" s="13" t="inlineStr"/>
-      <c r="M36" s="13" t="inlineStr"/>
-      <c r="N36" s="13" t="inlineStr"/>
-      <c r="O36" s="13" t="inlineStr"/>
-      <c r="P36" s="13" t="inlineStr"/>
-      <c r="Q36" s="13" t="inlineStr"/>
-      <c r="R36" s="13" t="inlineStr"/>
-      <c r="S36" s="13" t="inlineStr"/>
-      <c r="T36" s="13" t="inlineStr"/>
-      <c r="U36" s="13" t="inlineStr"/>
-      <c r="V36" s="13" t="inlineStr"/>
-      <c r="W36" s="13" t="inlineStr"/>
-      <c r="X36" s="13" t="inlineStr"/>
-      <c r="Y36" s="13" t="inlineStr"/>
-      <c r="Z36" s="13" t="inlineStr"/>
-      <c r="AA36" s="13" t="inlineStr"/>
-      <c r="AB36" s="13" t="inlineStr"/>
-      <c r="AC36" s="13" t="inlineStr"/>
-      <c r="AD36" s="13" t="inlineStr"/>
-      <c r="AE36" s="13" t="inlineStr"/>
-      <c r="AF36" s="14" t="inlineStr"/>
+      <c r="F36" s="16" t="inlineStr"/>
+      <c r="G36" s="16" t="inlineStr"/>
+      <c r="H36" s="16" t="inlineStr"/>
+      <c r="I36" s="16" t="inlineStr"/>
+      <c r="J36" s="16" t="inlineStr"/>
+      <c r="K36" s="16" t="inlineStr"/>
+      <c r="L36" s="16" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr"/>
+      <c r="N36" s="16" t="inlineStr"/>
+      <c r="O36" s="16" t="inlineStr"/>
+      <c r="P36" s="16" t="inlineStr"/>
+      <c r="Q36" s="16" t="inlineStr"/>
+      <c r="R36" s="16" t="inlineStr"/>
+      <c r="S36" s="16" t="inlineStr"/>
+      <c r="T36" s="16" t="inlineStr"/>
+      <c r="U36" s="16" t="inlineStr"/>
+      <c r="V36" s="16" t="inlineStr"/>
+      <c r="W36" s="16" t="inlineStr"/>
+      <c r="X36" s="16" t="inlineStr"/>
+      <c r="Y36" s="16" t="inlineStr"/>
+      <c r="Z36" s="16" t="inlineStr"/>
+      <c r="AA36" s="16" t="inlineStr"/>
+      <c r="AB36" s="16" t="inlineStr"/>
+      <c r="AC36" s="16" t="inlineStr"/>
+      <c r="AD36" s="16" t="inlineStr"/>
+      <c r="AE36" s="16" t="inlineStr"/>
+      <c r="AF36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>ITM-035</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>Is the somatic mutational burden of differentiated thyroid cancer comparably low to that seen in pediatric malignancies, and if so, what is the supporting reference?</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>Yes, **papillary thyroid carcinoma (PTC) has one of the lowest somatic mutation densities among all cancers studied by whole-exome sequencing**, and this low mutational burden is indeed comparable to that seen in pediatric malignancies. The key supporting reference is the landmark NEJM review by **Fagin and Wells (2016)**, which states:
 “Papillary thyroid carcinoma has one of the lowest mutation densities of cancers that have been studied by means of whole-exome sequencing.”
@@ -4470,7 +4508,7 @@
 Would you like to explore how the low mutational burden of [differentiated thyroid cancer](https://www.openevidence.com/rare-disease/differentiated-thyroid-carcinoma) affects treatment selection for radioiodine-refractory disease, particularly regarding immunotherapy eligibility?</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Yes. Differentiated thyroid cancer (DTC) is well established as having one of the lowest somatic mutational burdens of any human malignancy, placing it in the same low-mutation category as many pediatric cancers.
 The supporting data and most commonly cited reference:
@@ -4483,51 +4521,51 @@
 If you are citing this point in a manuscript, the canonical reference to use is **Lawrence MS, Stojanov P, Polak P, et al. Mutational heterogeneity in cancer and the search for new cancer-associated genes. *Nature*. 2013;499(7457):214–218. doi:10.1038/nature12213**, often supplemented by the TCGA thyroid carcinoma paper (Cancer Genome Atlas Research Network, *Cell* 2014) for thyroid-specific genomic detail.</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr"/>
-      <c r="G37" s="13" t="inlineStr"/>
-      <c r="H37" s="13" t="inlineStr"/>
-      <c r="I37" s="13" t="inlineStr"/>
-      <c r="J37" s="13" t="inlineStr"/>
-      <c r="K37" s="13" t="inlineStr"/>
-      <c r="L37" s="13" t="inlineStr"/>
-      <c r="M37" s="13" t="inlineStr"/>
-      <c r="N37" s="13" t="inlineStr"/>
-      <c r="O37" s="13" t="inlineStr"/>
-      <c r="P37" s="13" t="inlineStr"/>
-      <c r="Q37" s="13" t="inlineStr"/>
-      <c r="R37" s="13" t="inlineStr"/>
-      <c r="S37" s="13" t="inlineStr"/>
-      <c r="T37" s="13" t="inlineStr"/>
-      <c r="U37" s="13" t="inlineStr"/>
-      <c r="V37" s="13" t="inlineStr"/>
-      <c r="W37" s="13" t="inlineStr"/>
-      <c r="X37" s="13" t="inlineStr"/>
-      <c r="Y37" s="13" t="inlineStr"/>
-      <c r="Z37" s="13" t="inlineStr"/>
-      <c r="AA37" s="13" t="inlineStr"/>
-      <c r="AB37" s="13" t="inlineStr"/>
-      <c r="AC37" s="13" t="inlineStr"/>
-      <c r="AD37" s="13" t="inlineStr"/>
-      <c r="AE37" s="13" t="inlineStr"/>
-      <c r="AF37" s="14" t="inlineStr"/>
+      <c r="F37" s="16" t="inlineStr"/>
+      <c r="G37" s="16" t="inlineStr"/>
+      <c r="H37" s="16" t="inlineStr"/>
+      <c r="I37" s="16" t="inlineStr"/>
+      <c r="J37" s="16" t="inlineStr"/>
+      <c r="K37" s="16" t="inlineStr"/>
+      <c r="L37" s="16" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr"/>
+      <c r="N37" s="16" t="inlineStr"/>
+      <c r="O37" s="16" t="inlineStr"/>
+      <c r="P37" s="16" t="inlineStr"/>
+      <c r="Q37" s="16" t="inlineStr"/>
+      <c r="R37" s="16" t="inlineStr"/>
+      <c r="S37" s="16" t="inlineStr"/>
+      <c r="T37" s="16" t="inlineStr"/>
+      <c r="U37" s="16" t="inlineStr"/>
+      <c r="V37" s="16" t="inlineStr"/>
+      <c r="W37" s="16" t="inlineStr"/>
+      <c r="X37" s="16" t="inlineStr"/>
+      <c r="Y37" s="16" t="inlineStr"/>
+      <c r="Z37" s="16" t="inlineStr"/>
+      <c r="AA37" s="16" t="inlineStr"/>
+      <c r="AB37" s="16" t="inlineStr"/>
+      <c r="AC37" s="16" t="inlineStr"/>
+      <c r="AD37" s="16" t="inlineStr"/>
+      <c r="AE37" s="16" t="inlineStr"/>
+      <c r="AF37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>ITM-036</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Dermatology</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>What is the dosing of N-acetylcysteine for the treatment of neurotic excoriations?</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>N-acetylcysteine (NAC) is used off-label to treat neurotic excoriation (also called excoriation/skin-picking disorder). Here is a summary of the dosing based on the available evidence:
 ### Standard Dosing Range
@@ -4544,7 +4582,7 @@
 **Bottom line:** The evidence-based dosing range is **1200–3000 mg/day**, typically started at 1200 mg/day (600 mg twice daily) and titrated upward to a target of 2400–3000 mg/day, with patients counseled that benefit may take 9–12 weeks to appear. As always, clinical decisions should be individualized and made in consultation with a prescribing clinician.</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>The best-studied dosing regimen for **N-acetylcysteine (NAC) in excoriation disorder (neurotic excoriations)** is a gradual titration to a target dose of **3000 mg/day**, based on the pivotal randomized controlled trial by Grant et al. (2016):
 - **Weeks 1–2:** 1200 mg/day
@@ -4556,51 +4594,51 @@
 Would you like to explore the comparative evidence for NAC versus SSRIs or cognitive behavioral therapy for excoriation disorder?</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr"/>
-      <c r="G38" s="13" t="inlineStr"/>
-      <c r="H38" s="13" t="inlineStr"/>
-      <c r="I38" s="13" t="inlineStr"/>
-      <c r="J38" s="13" t="inlineStr"/>
-      <c r="K38" s="13" t="inlineStr"/>
-      <c r="L38" s="13" t="inlineStr"/>
-      <c r="M38" s="13" t="inlineStr"/>
-      <c r="N38" s="13" t="inlineStr"/>
-      <c r="O38" s="13" t="inlineStr"/>
-      <c r="P38" s="13" t="inlineStr"/>
-      <c r="Q38" s="13" t="inlineStr"/>
-      <c r="R38" s="13" t="inlineStr"/>
-      <c r="S38" s="13" t="inlineStr"/>
-      <c r="T38" s="13" t="inlineStr"/>
-      <c r="U38" s="13" t="inlineStr"/>
-      <c r="V38" s="13" t="inlineStr"/>
-      <c r="W38" s="13" t="inlineStr"/>
-      <c r="X38" s="13" t="inlineStr"/>
-      <c r="Y38" s="13" t="inlineStr"/>
-      <c r="Z38" s="13" t="inlineStr"/>
-      <c r="AA38" s="13" t="inlineStr"/>
-      <c r="AB38" s="13" t="inlineStr"/>
-      <c r="AC38" s="13" t="inlineStr"/>
-      <c r="AD38" s="13" t="inlineStr"/>
-      <c r="AE38" s="13" t="inlineStr"/>
-      <c r="AF38" s="14" t="inlineStr"/>
+      <c r="F38" s="16" t="inlineStr"/>
+      <c r="G38" s="16" t="inlineStr"/>
+      <c r="H38" s="16" t="inlineStr"/>
+      <c r="I38" s="16" t="inlineStr"/>
+      <c r="J38" s="16" t="inlineStr"/>
+      <c r="K38" s="16" t="inlineStr"/>
+      <c r="L38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr"/>
+      <c r="N38" s="16" t="inlineStr"/>
+      <c r="O38" s="16" t="inlineStr"/>
+      <c r="P38" s="16" t="inlineStr"/>
+      <c r="Q38" s="16" t="inlineStr"/>
+      <c r="R38" s="16" t="inlineStr"/>
+      <c r="S38" s="16" t="inlineStr"/>
+      <c r="T38" s="16" t="inlineStr"/>
+      <c r="U38" s="16" t="inlineStr"/>
+      <c r="V38" s="16" t="inlineStr"/>
+      <c r="W38" s="16" t="inlineStr"/>
+      <c r="X38" s="16" t="inlineStr"/>
+      <c r="Y38" s="16" t="inlineStr"/>
+      <c r="Z38" s="16" t="inlineStr"/>
+      <c r="AA38" s="16" t="inlineStr"/>
+      <c r="AB38" s="16" t="inlineStr"/>
+      <c r="AC38" s="16" t="inlineStr"/>
+      <c r="AD38" s="16" t="inlineStr"/>
+      <c r="AE38" s="16" t="inlineStr"/>
+      <c r="AF38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>ITM-037</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Neurology</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>How can steroid-induced myopathy be distinguished from immune-mediated myopathy using EMG findings?</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>Distinguishing steroid-induced myopathy from immune-mediated (inflammatory) myopathy is a common clinical challenge, particularly in patients with inflammatory myopathy who are being treated with corticosteroids and develop worsening or persistent weakness. EMG can be a helpful discriminator, though it has important limitations. Here are the key findings:
 ### Steroid-Induced Myopathy
@@ -4628,7 +4666,7 @@
 Would you like me to search for the most recent literature or guidelines on this distinction, as some newer studies address additional electrodiagnostic and biomarker approaches?</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>The **key distinguishing EMG feature** is that **steroid-induced myopathy typically produces a normal or near-normal EMG**, whereas **immune-mediated necrotizing myopathy (IMNM) shows active myopathic changes with prominent spontaneous activity**. This distinction makes EMG particularly useful when differentiating a disease flare from steroid myopathy in patients on glucocorticoid therapy.
 **Steroid-Induced Myopathy — EMG Findings**
@@ -4663,51 +4701,51 @@
 Mongiovi PC, Elsheikh B, Lawson VH, Kissel JT, Arnold WD. Neuromuscular Junction Disorders Mimicking Myopathy. Muscle &amp; Nerve. 2014;50(5):854-6. doi:10.1002/mus.24300.</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr"/>
-      <c r="G39" s="13" t="inlineStr"/>
-      <c r="H39" s="13" t="inlineStr"/>
-      <c r="I39" s="13" t="inlineStr"/>
-      <c r="J39" s="13" t="inlineStr"/>
-      <c r="K39" s="13" t="inlineStr"/>
-      <c r="L39" s="13" t="inlineStr"/>
-      <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="13" t="inlineStr"/>
-      <c r="O39" s="13" t="inlineStr"/>
-      <c r="P39" s="13" t="inlineStr"/>
-      <c r="Q39" s="13" t="inlineStr"/>
-      <c r="R39" s="13" t="inlineStr"/>
-      <c r="S39" s="13" t="inlineStr"/>
-      <c r="T39" s="13" t="inlineStr"/>
-      <c r="U39" s="13" t="inlineStr"/>
-      <c r="V39" s="13" t="inlineStr"/>
-      <c r="W39" s="13" t="inlineStr"/>
-      <c r="X39" s="13" t="inlineStr"/>
-      <c r="Y39" s="13" t="inlineStr"/>
-      <c r="Z39" s="13" t="inlineStr"/>
-      <c r="AA39" s="13" t="inlineStr"/>
-      <c r="AB39" s="13" t="inlineStr"/>
-      <c r="AC39" s="13" t="inlineStr"/>
-      <c r="AD39" s="13" t="inlineStr"/>
-      <c r="AE39" s="13" t="inlineStr"/>
-      <c r="AF39" s="14" t="inlineStr"/>
+      <c r="F39" s="16" t="inlineStr"/>
+      <c r="G39" s="16" t="inlineStr"/>
+      <c r="H39" s="16" t="inlineStr"/>
+      <c r="I39" s="16" t="inlineStr"/>
+      <c r="J39" s="16" t="inlineStr"/>
+      <c r="K39" s="16" t="inlineStr"/>
+      <c r="L39" s="16" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr"/>
+      <c r="N39" s="16" t="inlineStr"/>
+      <c r="O39" s="16" t="inlineStr"/>
+      <c r="P39" s="16" t="inlineStr"/>
+      <c r="Q39" s="16" t="inlineStr"/>
+      <c r="R39" s="16" t="inlineStr"/>
+      <c r="S39" s="16" t="inlineStr"/>
+      <c r="T39" s="16" t="inlineStr"/>
+      <c r="U39" s="16" t="inlineStr"/>
+      <c r="V39" s="16" t="inlineStr"/>
+      <c r="W39" s="16" t="inlineStr"/>
+      <c r="X39" s="16" t="inlineStr"/>
+      <c r="Y39" s="16" t="inlineStr"/>
+      <c r="Z39" s="16" t="inlineStr"/>
+      <c r="AA39" s="16" t="inlineStr"/>
+      <c r="AB39" s="16" t="inlineStr"/>
+      <c r="AC39" s="16" t="inlineStr"/>
+      <c r="AD39" s="16" t="inlineStr"/>
+      <c r="AE39" s="16" t="inlineStr"/>
+      <c r="AF39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>ITM-038</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>What is the evidence supporting the use of GLP-1 receptor agonists in the management of post-bariatric surgery hypoglycemia?</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>The evidence supporting GLP-1 receptor agonists (GLP-1 RAs) for post-bariatric surgery hypoglycemia (PBH) is **limited, mixed, and classified as "uncertain"** in current treatment recommendations, despite a plausible mechanistic rationale.
 **Pathophysiologic Rationale**
@@ -4733,7 +4771,7 @@
 Would you like to explore the emerging evidence on GLP-1 receptor antagonists (such as exendin 9-39) or novel agents like dasiglucagon for post-bariatric hypoglycemia?</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>### Evidence for GLP-1 Receptor Agonists in Post-Bariatric Surgery Hypoglycemia
 The use of GLP-1 receptor agonists (GLP-1RAs) for post-bariatric hypoglycemia (PBH) is somewhat paradoxical, and the supporting evidence remains limited and of low quality. Here's a summary of what's known.
@@ -4756,51 +4794,51 @@
 The evidence supporting GLP-1RAs for PBH consists almost entirely of case reports, small case series, and isolated patients within trials—not robust randomized controlled trials. The signal is encouraging in refractory patients (those who fail dietary measures, acarbose, diazoxide, octreotide, etc.), and reassuringly the agonists do not appear to worsen hypoglycemia. However, as the systematic reviews emphasize, more studies need to be conducted to assess whether GLP-1 receptor agonists can reduce postprandial hypoglycemia after bariatric surgery. At present this remains an off-label, evidence-limited option best reserved for difficult cases, and the mechanism by which it works (when it does) is still not understood.</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr"/>
-      <c r="G40" s="13" t="inlineStr"/>
-      <c r="H40" s="13" t="inlineStr"/>
-      <c r="I40" s="13" t="inlineStr"/>
-      <c r="J40" s="13" t="inlineStr"/>
-      <c r="K40" s="13" t="inlineStr"/>
-      <c r="L40" s="13" t="inlineStr"/>
-      <c r="M40" s="13" t="inlineStr"/>
-      <c r="N40" s="13" t="inlineStr"/>
-      <c r="O40" s="13" t="inlineStr"/>
-      <c r="P40" s="13" t="inlineStr"/>
-      <c r="Q40" s="13" t="inlineStr"/>
-      <c r="R40" s="13" t="inlineStr"/>
-      <c r="S40" s="13" t="inlineStr"/>
-      <c r="T40" s="13" t="inlineStr"/>
-      <c r="U40" s="13" t="inlineStr"/>
-      <c r="V40" s="13" t="inlineStr"/>
-      <c r="W40" s="13" t="inlineStr"/>
-      <c r="X40" s="13" t="inlineStr"/>
-      <c r="Y40" s="13" t="inlineStr"/>
-      <c r="Z40" s="13" t="inlineStr"/>
-      <c r="AA40" s="13" t="inlineStr"/>
-      <c r="AB40" s="13" t="inlineStr"/>
-      <c r="AC40" s="13" t="inlineStr"/>
-      <c r="AD40" s="13" t="inlineStr"/>
-      <c r="AE40" s="13" t="inlineStr"/>
-      <c r="AF40" s="14" t="inlineStr"/>
+      <c r="F40" s="16" t="inlineStr"/>
+      <c r="G40" s="16" t="inlineStr"/>
+      <c r="H40" s="16" t="inlineStr"/>
+      <c r="I40" s="16" t="inlineStr"/>
+      <c r="J40" s="16" t="inlineStr"/>
+      <c r="K40" s="16" t="inlineStr"/>
+      <c r="L40" s="16" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr"/>
+      <c r="N40" s="16" t="inlineStr"/>
+      <c r="O40" s="16" t="inlineStr"/>
+      <c r="P40" s="16" t="inlineStr"/>
+      <c r="Q40" s="16" t="inlineStr"/>
+      <c r="R40" s="16" t="inlineStr"/>
+      <c r="S40" s="16" t="inlineStr"/>
+      <c r="T40" s="16" t="inlineStr"/>
+      <c r="U40" s="16" t="inlineStr"/>
+      <c r="V40" s="16" t="inlineStr"/>
+      <c r="W40" s="16" t="inlineStr"/>
+      <c r="X40" s="16" t="inlineStr"/>
+      <c r="Y40" s="16" t="inlineStr"/>
+      <c r="Z40" s="16" t="inlineStr"/>
+      <c r="AA40" s="16" t="inlineStr"/>
+      <c r="AB40" s="16" t="inlineStr"/>
+      <c r="AC40" s="16" t="inlineStr"/>
+      <c r="AD40" s="16" t="inlineStr"/>
+      <c r="AE40" s="16" t="inlineStr"/>
+      <c r="AF40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>ITM-039</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>What is the appropriate next step in monitoring a 55-year-old female with a 1 cm pituitary adenoma and prolactin level of 129.4 who has been on cabergoline 0.25 mg twice weekly for 6 weeks?</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>The appropriate next step is to **recheck the serum prolactin level and consider dose titration**, as this patient has been on cabergoline 0.25 mg twice weekly (0.5 mg/week) for 6 weeks with a prolactin that remains elevated at 129.4 ng/mL. A 1 cm adenoma is at the threshold between micro- and macroprolactinoma.
 **Prolactin monitoring and dose adjustment:**
@@ -4817,7 +4855,7 @@
 Would you like to explore the criteria and timing for assessing dopamine agonist resistance versus expected treatment response in prolactinomas?</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>The appropriate next step is to **recheck the serum prolactin level** to assess the biochemical response to cabergoline, which then guides whether the dose should be maintained, titrated up, or held.
 Here's the reasoning and the broader monitoring framework for this patient:
@@ -4838,51 +4876,51 @@
 This is general educational information based on standard endocrine practice—the managing endocrinologist should individualize the plan. Would you like me to look up the most current Endocrine Society or Pituitary Society guideline specifics on titration intervals and MRI timing?</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr"/>
-      <c r="G41" s="13" t="inlineStr"/>
-      <c r="H41" s="13" t="inlineStr"/>
-      <c r="I41" s="13" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr"/>
-      <c r="K41" s="13" t="inlineStr"/>
-      <c r="L41" s="13" t="inlineStr"/>
-      <c r="M41" s="13" t="inlineStr"/>
-      <c r="N41" s="13" t="inlineStr"/>
-      <c r="O41" s="13" t="inlineStr"/>
-      <c r="P41" s="13" t="inlineStr"/>
-      <c r="Q41" s="13" t="inlineStr"/>
-      <c r="R41" s="13" t="inlineStr"/>
-      <c r="S41" s="13" t="inlineStr"/>
-      <c r="T41" s="13" t="inlineStr"/>
-      <c r="U41" s="13" t="inlineStr"/>
-      <c r="V41" s="13" t="inlineStr"/>
-      <c r="W41" s="13" t="inlineStr"/>
-      <c r="X41" s="13" t="inlineStr"/>
-      <c r="Y41" s="13" t="inlineStr"/>
-      <c r="Z41" s="13" t="inlineStr"/>
-      <c r="AA41" s="13" t="inlineStr"/>
-      <c r="AB41" s="13" t="inlineStr"/>
-      <c r="AC41" s="13" t="inlineStr"/>
-      <c r="AD41" s="13" t="inlineStr"/>
-      <c r="AE41" s="13" t="inlineStr"/>
-      <c r="AF41" s="14" t="inlineStr"/>
+      <c r="F41" s="16" t="inlineStr"/>
+      <c r="G41" s="16" t="inlineStr"/>
+      <c r="H41" s="16" t="inlineStr"/>
+      <c r="I41" s="16" t="inlineStr"/>
+      <c r="J41" s="16" t="inlineStr"/>
+      <c r="K41" s="16" t="inlineStr"/>
+      <c r="L41" s="16" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr"/>
+      <c r="N41" s="16" t="inlineStr"/>
+      <c r="O41" s="16" t="inlineStr"/>
+      <c r="P41" s="16" t="inlineStr"/>
+      <c r="Q41" s="16" t="inlineStr"/>
+      <c r="R41" s="16" t="inlineStr"/>
+      <c r="S41" s="16" t="inlineStr"/>
+      <c r="T41" s="16" t="inlineStr"/>
+      <c r="U41" s="16" t="inlineStr"/>
+      <c r="V41" s="16" t="inlineStr"/>
+      <c r="W41" s="16" t="inlineStr"/>
+      <c r="X41" s="16" t="inlineStr"/>
+      <c r="Y41" s="16" t="inlineStr"/>
+      <c r="Z41" s="16" t="inlineStr"/>
+      <c r="AA41" s="16" t="inlineStr"/>
+      <c r="AB41" s="16" t="inlineStr"/>
+      <c r="AC41" s="16" t="inlineStr"/>
+      <c r="AD41" s="16" t="inlineStr"/>
+      <c r="AE41" s="16" t="inlineStr"/>
+      <c r="AF41" s="17" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>ITM-040</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Elevated lipoprotein(a) levels in East Asian populations.</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>**East Asian populations have the lowest median Lp(a) levels among all major ethnic groups**, with a mean population level of approximately **15 nmol/L** and a median of **7.8 mg/dL** in Chinese cohorts, compared to 25 nmol/L in Whites, 30 nmol/L in South Asians, and 75 nmol/L in Blacks. Despite these lower population-level concentrations, elevated Lp(a) remains a clinically significant and causal risk factor for ASCVD in East Asians, with proportional risk effects comparable to those in European populations.
 **Epidemiology and Genetic Basis**
@@ -4903,7 +4941,7 @@
 Would you like to explore the emerging Lp(a)-lowering therapies (e.g., pelacarsen, olpasiran, lepodisiran) and their potential implications for East Asian patients specifically?</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>I'll search for current information on this topic.Here's an overview of what current research says about elevated lipoprotein(a) levels in East Asian populations:
 ### What Is Lp(a) and Why It Matters
@@ -4927,51 +4965,51 @@
 Would you like me to dig deeper into any specific aspect—such as the genetics, specific country-level data (Japan, Korea, China), or the emerging Lp(a)-lowering therapies?</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr"/>
-      <c r="G42" s="13" t="inlineStr"/>
-      <c r="H42" s="13" t="inlineStr"/>
-      <c r="I42" s="13" t="inlineStr"/>
-      <c r="J42" s="13" t="inlineStr"/>
-      <c r="K42" s="13" t="inlineStr"/>
-      <c r="L42" s="13" t="inlineStr"/>
-      <c r="M42" s="13" t="inlineStr"/>
-      <c r="N42" s="13" t="inlineStr"/>
-      <c r="O42" s="13" t="inlineStr"/>
-      <c r="P42" s="13" t="inlineStr"/>
-      <c r="Q42" s="13" t="inlineStr"/>
-      <c r="R42" s="13" t="inlineStr"/>
-      <c r="S42" s="13" t="inlineStr"/>
-      <c r="T42" s="13" t="inlineStr"/>
-      <c r="U42" s="13" t="inlineStr"/>
-      <c r="V42" s="13" t="inlineStr"/>
-      <c r="W42" s="13" t="inlineStr"/>
-      <c r="X42" s="13" t="inlineStr"/>
-      <c r="Y42" s="13" t="inlineStr"/>
-      <c r="Z42" s="13" t="inlineStr"/>
-      <c r="AA42" s="13" t="inlineStr"/>
-      <c r="AB42" s="13" t="inlineStr"/>
-      <c r="AC42" s="13" t="inlineStr"/>
-      <c r="AD42" s="13" t="inlineStr"/>
-      <c r="AE42" s="13" t="inlineStr"/>
-      <c r="AF42" s="14" t="inlineStr"/>
+      <c r="F42" s="16" t="inlineStr"/>
+      <c r="G42" s="16" t="inlineStr"/>
+      <c r="H42" s="16" t="inlineStr"/>
+      <c r="I42" s="16" t="inlineStr"/>
+      <c r="J42" s="16" t="inlineStr"/>
+      <c r="K42" s="16" t="inlineStr"/>
+      <c r="L42" s="16" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr"/>
+      <c r="N42" s="16" t="inlineStr"/>
+      <c r="O42" s="16" t="inlineStr"/>
+      <c r="P42" s="16" t="inlineStr"/>
+      <c r="Q42" s="16" t="inlineStr"/>
+      <c r="R42" s="16" t="inlineStr"/>
+      <c r="S42" s="16" t="inlineStr"/>
+      <c r="T42" s="16" t="inlineStr"/>
+      <c r="U42" s="16" t="inlineStr"/>
+      <c r="V42" s="16" t="inlineStr"/>
+      <c r="W42" s="16" t="inlineStr"/>
+      <c r="X42" s="16" t="inlineStr"/>
+      <c r="Y42" s="16" t="inlineStr"/>
+      <c r="Z42" s="16" t="inlineStr"/>
+      <c r="AA42" s="16" t="inlineStr"/>
+      <c r="AB42" s="16" t="inlineStr"/>
+      <c r="AC42" s="16" t="inlineStr"/>
+      <c r="AD42" s="16" t="inlineStr"/>
+      <c r="AE42" s="16" t="inlineStr"/>
+      <c r="AF42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>ITM-041</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>Elevated lipoprotein(a) levels in East Asian populations.</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>**Lipoprotein(a) [Lp(a)]** is a genetically determined, low-density lipoprotein (LDL)-like particle that is well-established as an independent and causal risk factor for atherosclerotic cardiovascular disease (ASCVD), myocardial infarction (MI), ischemic stroke, and calcific aortic valve stenosis.
 While much of the early research on Lp(a) focused on Western populations, recent genomic and epidemiological studies have shed significant light on how Lp(a) presents in and affects **East Asian populations** (e.g., Chinese, Japanese, Korean descents).
@@ -4997,7 +5035,7 @@
 * **Future Therapies:** Groundbreaking RNA-targeted therapies—such as antisense oligonucleotides (e.g., pelacarsen) and small interfering RNAs (e.g., olpasiran, lepodisiran)—which lower Lp(a) by 80% to 95+%, are currently in Phase 3 cardiovascular outcome trials. Importantly, these global trials feature designated Asian subgroups to ensure efficacy and safety profiles are established for East Asian patients.</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>**East Asian populations have the lowest median Lp(a) levels among all major ethnic groups**, with a mean population level of approximately **15 nmol/L** and a median of **7.8 mg/dL** in Chinese cohorts, compared to 25 nmol/L in Whites, 30 nmol/L in South Asians, and 75 nmol/L in Blacks. Despite these lower population-level concentrations, elevated Lp(a) remains a clinically significant and causal risk factor for ASCVD in East Asians, with proportional risk effects comparable to those in European populations.
 **Epidemiology and Genetic Basis**
@@ -5018,51 +5056,51 @@
 Would you like to explore the emerging Lp(a)-lowering therapies (e.g., pelacarsen, olpasiran, lepodisiran) and their potential implications for East Asian patients specifically?</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr"/>
-      <c r="G43" s="13" t="inlineStr"/>
-      <c r="H43" s="13" t="inlineStr"/>
-      <c r="I43" s="13" t="inlineStr"/>
-      <c r="J43" s="13" t="inlineStr"/>
-      <c r="K43" s="13" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
-      <c r="N43" s="13" t="inlineStr"/>
-      <c r="O43" s="13" t="inlineStr"/>
-      <c r="P43" s="13" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
-      <c r="R43" s="13" t="inlineStr"/>
-      <c r="S43" s="13" t="inlineStr"/>
-      <c r="T43" s="13" t="inlineStr"/>
-      <c r="U43" s="13" t="inlineStr"/>
-      <c r="V43" s="13" t="inlineStr"/>
-      <c r="W43" s="13" t="inlineStr"/>
-      <c r="X43" s="13" t="inlineStr"/>
-      <c r="Y43" s="13" t="inlineStr"/>
-      <c r="Z43" s="13" t="inlineStr"/>
-      <c r="AA43" s="13" t="inlineStr"/>
-      <c r="AB43" s="13" t="inlineStr"/>
-      <c r="AC43" s="13" t="inlineStr"/>
-      <c r="AD43" s="13" t="inlineStr"/>
-      <c r="AE43" s="13" t="inlineStr"/>
-      <c r="AF43" s="14" t="inlineStr"/>
+      <c r="F43" s="16" t="inlineStr"/>
+      <c r="G43" s="16" t="inlineStr"/>
+      <c r="H43" s="16" t="inlineStr"/>
+      <c r="I43" s="16" t="inlineStr"/>
+      <c r="J43" s="16" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr"/>
+      <c r="L43" s="16" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr"/>
+      <c r="N43" s="16" t="inlineStr"/>
+      <c r="O43" s="16" t="inlineStr"/>
+      <c r="P43" s="16" t="inlineStr"/>
+      <c r="Q43" s="16" t="inlineStr"/>
+      <c r="R43" s="16" t="inlineStr"/>
+      <c r="S43" s="16" t="inlineStr"/>
+      <c r="T43" s="16" t="inlineStr"/>
+      <c r="U43" s="16" t="inlineStr"/>
+      <c r="V43" s="16" t="inlineStr"/>
+      <c r="W43" s="16" t="inlineStr"/>
+      <c r="X43" s="16" t="inlineStr"/>
+      <c r="Y43" s="16" t="inlineStr"/>
+      <c r="Z43" s="16" t="inlineStr"/>
+      <c r="AA43" s="16" t="inlineStr"/>
+      <c r="AB43" s="16" t="inlineStr"/>
+      <c r="AC43" s="16" t="inlineStr"/>
+      <c r="AD43" s="16" t="inlineStr"/>
+      <c r="AE43" s="16" t="inlineStr"/>
+      <c r="AF43" s="17" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>ITM-042</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>What is the diagnostic evaluation for postprandial hypoglycemia?</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>The diagnostic evaluation for postprandial hypoglycemia centers on **confirming Whipple's triad** (symptoms of hypoglycemia, documented low plasma glucose, and symptom resolution with glucose correction), followed by a **mixed meal tolerance test (MMTT)** as the preferred provocative test, with concurrent biochemical profiling to identify the underlying etiology.
 **Step 1: Confirm Whipple's Triad**
@@ -5094,7 +5132,7 @@
 Would you like to explore the specific management strategies for postprandial hypoglycemia based on etiology, such as dietary modifications, pharmacotherapy (e.g., acarbose, diazoxide), or surgical options?</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>**Postprandial hypoglycemia should be evaluated only after confirming that the symptoms are truly due to low plasma glucose**—i.e., **Whipple’s triad**: 1) symptoms/signs compatible with hypoglycemia, 2) **low laboratory plasma glucose** during symptoms, and 3) symptom relief when glucose is corrected. Fingerstick meters and CGMs can be useful for pattern recognition, but in people without diabetes, the diagnostic glucose should be confirmed with a reliable lab plasma glucose because artifacts and meter inaccuracies are common.
 ### Diagnostic evaluation
@@ -5130,51 +5168,51 @@
 **Bottom line:** The core diagnostic evaluation is **document Whipple’s triad**, obtain a **critical blood sample during hypoglycemia**, and if needed perform a **supervised mixed-meal test**. A standard OGTT is generally **not recommended** for suspected postprandial hypoglycemia.</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr"/>
-      <c r="G44" s="13" t="inlineStr"/>
-      <c r="H44" s="13" t="inlineStr"/>
-      <c r="I44" s="13" t="inlineStr"/>
-      <c r="J44" s="13" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
-      <c r="L44" s="13" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
-      <c r="N44" s="13" t="inlineStr"/>
-      <c r="O44" s="13" t="inlineStr"/>
-      <c r="P44" s="13" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
-      <c r="R44" s="13" t="inlineStr"/>
-      <c r="S44" s="13" t="inlineStr"/>
-      <c r="T44" s="13" t="inlineStr"/>
-      <c r="U44" s="13" t="inlineStr"/>
-      <c r="V44" s="13" t="inlineStr"/>
-      <c r="W44" s="13" t="inlineStr"/>
-      <c r="X44" s="13" t="inlineStr"/>
-      <c r="Y44" s="13" t="inlineStr"/>
-      <c r="Z44" s="13" t="inlineStr"/>
-      <c r="AA44" s="13" t="inlineStr"/>
-      <c r="AB44" s="13" t="inlineStr"/>
-      <c r="AC44" s="13" t="inlineStr"/>
-      <c r="AD44" s="13" t="inlineStr"/>
-      <c r="AE44" s="13" t="inlineStr"/>
-      <c r="AF44" s="14" t="inlineStr"/>
+      <c r="F44" s="16" t="inlineStr"/>
+      <c r="G44" s="16" t="inlineStr"/>
+      <c r="H44" s="16" t="inlineStr"/>
+      <c r="I44" s="16" t="inlineStr"/>
+      <c r="J44" s="16" t="inlineStr"/>
+      <c r="K44" s="16" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr"/>
+      <c r="N44" s="16" t="inlineStr"/>
+      <c r="O44" s="16" t="inlineStr"/>
+      <c r="P44" s="16" t="inlineStr"/>
+      <c r="Q44" s="16" t="inlineStr"/>
+      <c r="R44" s="16" t="inlineStr"/>
+      <c r="S44" s="16" t="inlineStr"/>
+      <c r="T44" s="16" t="inlineStr"/>
+      <c r="U44" s="16" t="inlineStr"/>
+      <c r="V44" s="16" t="inlineStr"/>
+      <c r="W44" s="16" t="inlineStr"/>
+      <c r="X44" s="16" t="inlineStr"/>
+      <c r="Y44" s="16" t="inlineStr"/>
+      <c r="Z44" s="16" t="inlineStr"/>
+      <c r="AA44" s="16" t="inlineStr"/>
+      <c r="AB44" s="16" t="inlineStr"/>
+      <c r="AC44" s="16" t="inlineStr"/>
+      <c r="AD44" s="16" t="inlineStr"/>
+      <c r="AE44" s="16" t="inlineStr"/>
+      <c r="AF44" s="17" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>ITM-043</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>Infectious Disease</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>Should a patient with recently diagnosed pyelonephritis who has been on ceftriaxone and one day of cefpodoxime but is now presenting with worsening symptoms be continued on ceftriaxone or should antibiotic coverage be escalated?</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>In a patient with pyelonephritis whose symptoms are **worsening despite ceftriaxone and oral cefpodoxime**, antibiotic coverage should be **escalated rather than simply continuing ceftriaxone**, and the workup should be broadened to identify the cause of treatment failure.
 **Key Considerations in This Scenario**
@@ -5193,7 +5231,7 @@
 Would you like to explore the specific risk factors and clinical decision-making framework for determining when to suspect ESBL-producing organisms in community-acquired pyelonephritis?</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>This is an important clinical scenario. Let me search for current evidence-based guidance to supplement my response.This is fundamentally a clinical judgment call that needs to be made by the treating team with the full clinical picture, but the evidence strongly suggests that simply "staying the course" on ceftriaxone is **not** the right approach when a patient is actively worsening. Here's what the literature supports:
 ### The clinical worsening itself is a red flag
@@ -5211,51 +5249,51 @@
 **Important caveat:** This is general information drawn from published guidelines and references, not a substitute for bedside clinical judgment. The right decision depends on details I don't have—the patient's hemodynamic status, comorbidities, allergy profile, local resistance patterns, prior culture data, pregnancy status, and whether this is complicated vs. uncomplicated pyelonephritis. An infectious disease and/or urology consultation is warranted for a patient failing first-line therapy.</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr"/>
-      <c r="G45" s="13" t="inlineStr"/>
-      <c r="H45" s="13" t="inlineStr"/>
-      <c r="I45" s="13" t="inlineStr"/>
-      <c r="J45" s="13" t="inlineStr"/>
-      <c r="K45" s="13" t="inlineStr"/>
-      <c r="L45" s="13" t="inlineStr"/>
-      <c r="M45" s="13" t="inlineStr"/>
-      <c r="N45" s="13" t="inlineStr"/>
-      <c r="O45" s="13" t="inlineStr"/>
-      <c r="P45" s="13" t="inlineStr"/>
-      <c r="Q45" s="13" t="inlineStr"/>
-      <c r="R45" s="13" t="inlineStr"/>
-      <c r="S45" s="13" t="inlineStr"/>
-      <c r="T45" s="13" t="inlineStr"/>
-      <c r="U45" s="13" t="inlineStr"/>
-      <c r="V45" s="13" t="inlineStr"/>
-      <c r="W45" s="13" t="inlineStr"/>
-      <c r="X45" s="13" t="inlineStr"/>
-      <c r="Y45" s="13" t="inlineStr"/>
-      <c r="Z45" s="13" t="inlineStr"/>
-      <c r="AA45" s="13" t="inlineStr"/>
-      <c r="AB45" s="13" t="inlineStr"/>
-      <c r="AC45" s="13" t="inlineStr"/>
-      <c r="AD45" s="13" t="inlineStr"/>
-      <c r="AE45" s="13" t="inlineStr"/>
-      <c r="AF45" s="14" t="inlineStr"/>
+      <c r="F45" s="16" t="inlineStr"/>
+      <c r="G45" s="16" t="inlineStr"/>
+      <c r="H45" s="16" t="inlineStr"/>
+      <c r="I45" s="16" t="inlineStr"/>
+      <c r="J45" s="16" t="inlineStr"/>
+      <c r="K45" s="16" t="inlineStr"/>
+      <c r="L45" s="16" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr"/>
+      <c r="N45" s="16" t="inlineStr"/>
+      <c r="O45" s="16" t="inlineStr"/>
+      <c r="P45" s="16" t="inlineStr"/>
+      <c r="Q45" s="16" t="inlineStr"/>
+      <c r="R45" s="16" t="inlineStr"/>
+      <c r="S45" s="16" t="inlineStr"/>
+      <c r="T45" s="16" t="inlineStr"/>
+      <c r="U45" s="16" t="inlineStr"/>
+      <c r="V45" s="16" t="inlineStr"/>
+      <c r="W45" s="16" t="inlineStr"/>
+      <c r="X45" s="16" t="inlineStr"/>
+      <c r="Y45" s="16" t="inlineStr"/>
+      <c r="Z45" s="16" t="inlineStr"/>
+      <c r="AA45" s="16" t="inlineStr"/>
+      <c r="AB45" s="16" t="inlineStr"/>
+      <c r="AC45" s="16" t="inlineStr"/>
+      <c r="AD45" s="16" t="inlineStr"/>
+      <c r="AE45" s="16" t="inlineStr"/>
+      <c r="AF45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>ITM-044</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>Infectious Disease</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>Should a patient with recently diagnosed pyelonephritis who has been on ceftriaxone and one day of cefpodoxime but is now presenting with worsening symptoms be continued on ceftriaxone or should antibiotic coverage be escalated?</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>**Short answer:** A patient with pyelonephritis who is **clinically worsening** after ceftriaxone and a step-down to cefpodoxime should **not simply be managed as “continue the same outpatient plan.”** They need **urgent reassessment**—vitals/sepsis evaluation, labs, urine culture/susceptibilities, often blood cultures, and consideration of imaging. Whether to continue ceftriaxone vs broaden depends on severity and resistance risk.
 **Practical decision frame:**
@@ -5273,7 +5311,7 @@
 If they are **worsening clinically**, they should be treated as possible **treatment failure or complicated pyelonephritis**. **Escalate coverage** if they are ill/septic or have MDR/ESBL risk factors; otherwise, **IV ceftriaxone may be acceptable only if stable and susceptibility supports it**, but they still need close reassessment, cultures, and possibly imaging. This is an ED/inpatient-level decision, not a “just continue cefpodoxime” situation.</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>In a patient with pyelonephritis whose symptoms are **worsening despite ceftriaxone and oral cefpodoxime**, antibiotic coverage should be **escalated rather than simply continuing ceftriaxone**, and the workup should be broadened to identify the cause of treatment failure.
 **Key Considerations in This Scenario**
@@ -5292,51 +5330,51 @@
 Would you like to explore the specific risk factors and clinical decision-making framework for determining when to suspect ESBL-producing organisms in community-acquired pyelonephritis?</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr"/>
-      <c r="G46" s="13" t="inlineStr"/>
-      <c r="H46" s="13" t="inlineStr"/>
-      <c r="I46" s="13" t="inlineStr"/>
-      <c r="J46" s="13" t="inlineStr"/>
-      <c r="K46" s="13" t="inlineStr"/>
-      <c r="L46" s="13" t="inlineStr"/>
-      <c r="M46" s="13" t="inlineStr"/>
-      <c r="N46" s="13" t="inlineStr"/>
-      <c r="O46" s="13" t="inlineStr"/>
-      <c r="P46" s="13" t="inlineStr"/>
-      <c r="Q46" s="13" t="inlineStr"/>
-      <c r="R46" s="13" t="inlineStr"/>
-      <c r="S46" s="13" t="inlineStr"/>
-      <c r="T46" s="13" t="inlineStr"/>
-      <c r="U46" s="13" t="inlineStr"/>
-      <c r="V46" s="13" t="inlineStr"/>
-      <c r="W46" s="13" t="inlineStr"/>
-      <c r="X46" s="13" t="inlineStr"/>
-      <c r="Y46" s="13" t="inlineStr"/>
-      <c r="Z46" s="13" t="inlineStr"/>
-      <c r="AA46" s="13" t="inlineStr"/>
-      <c r="AB46" s="13" t="inlineStr"/>
-      <c r="AC46" s="13" t="inlineStr"/>
-      <c r="AD46" s="13" t="inlineStr"/>
-      <c r="AE46" s="13" t="inlineStr"/>
-      <c r="AF46" s="14" t="inlineStr"/>
+      <c r="F46" s="16" t="inlineStr"/>
+      <c r="G46" s="16" t="inlineStr"/>
+      <c r="H46" s="16" t="inlineStr"/>
+      <c r="I46" s="16" t="inlineStr"/>
+      <c r="J46" s="16" t="inlineStr"/>
+      <c r="K46" s="16" t="inlineStr"/>
+      <c r="L46" s="16" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr"/>
+      <c r="N46" s="16" t="inlineStr"/>
+      <c r="O46" s="16" t="inlineStr"/>
+      <c r="P46" s="16" t="inlineStr"/>
+      <c r="Q46" s="16" t="inlineStr"/>
+      <c r="R46" s="16" t="inlineStr"/>
+      <c r="S46" s="16" t="inlineStr"/>
+      <c r="T46" s="16" t="inlineStr"/>
+      <c r="U46" s="16" t="inlineStr"/>
+      <c r="V46" s="16" t="inlineStr"/>
+      <c r="W46" s="16" t="inlineStr"/>
+      <c r="X46" s="16" t="inlineStr"/>
+      <c r="Y46" s="16" t="inlineStr"/>
+      <c r="Z46" s="16" t="inlineStr"/>
+      <c r="AA46" s="16" t="inlineStr"/>
+      <c r="AB46" s="16" t="inlineStr"/>
+      <c r="AC46" s="16" t="inlineStr"/>
+      <c r="AD46" s="16" t="inlineStr"/>
+      <c r="AE46" s="16" t="inlineStr"/>
+      <c r="AF46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>ITM-045</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Rheumatology</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>When can a patient with rheumatoid arthritis on tocilizumab resume the medication following a bone marrow biopsy done as part of a multiple myeloma workup?</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>From a strictly procedural standpoint, a patient with rheumatoid arthritis (RA) can generally resume or continue tocilizumab (Actemra) **immediately or within 24 hours** following a bone marrow biopsy, provided they are clinically stable and show no signs of infection.
 However, because this biopsy is being done as part of a **multiple myeloma workup**, there are critical hematologic and clinical caveats that must be considered before administering the next dose.
@@ -5359,7 +5397,7 @@
 *Disclaimer: This information is for educational purposes based on current clinical guidelines. The patient should always rely on the explicit instructions of their consulting rheumatologist and hematologist/oncologist regarding medication schedules.*</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>A bone marrow biopsy is a **minor, minimally invasive procedure** with a small puncture wound, and tocilizumab can generally be **resumed at the next regularly scheduled dose** provided the biopsy site shows no signs of infection or complications. There is typically no need to delay resumption beyond the normal dosing schedule.
 **Key considerations:**
@@ -5375,51 +5413,51 @@
 Would you like to explore the implications of a potential myeloma diagnosis on continued tocilizumab use and RA management?</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr"/>
-      <c r="G47" s="13" t="inlineStr"/>
-      <c r="H47" s="13" t="inlineStr"/>
-      <c r="I47" s="13" t="inlineStr"/>
-      <c r="J47" s="13" t="inlineStr"/>
-      <c r="K47" s="13" t="inlineStr"/>
-      <c r="L47" s="13" t="inlineStr"/>
-      <c r="M47" s="13" t="inlineStr"/>
-      <c r="N47" s="13" t="inlineStr"/>
-      <c r="O47" s="13" t="inlineStr"/>
-      <c r="P47" s="13" t="inlineStr"/>
-      <c r="Q47" s="13" t="inlineStr"/>
-      <c r="R47" s="13" t="inlineStr"/>
-      <c r="S47" s="13" t="inlineStr"/>
-      <c r="T47" s="13" t="inlineStr"/>
-      <c r="U47" s="13" t="inlineStr"/>
-      <c r="V47" s="13" t="inlineStr"/>
-      <c r="W47" s="13" t="inlineStr"/>
-      <c r="X47" s="13" t="inlineStr"/>
-      <c r="Y47" s="13" t="inlineStr"/>
-      <c r="Z47" s="13" t="inlineStr"/>
-      <c r="AA47" s="13" t="inlineStr"/>
-      <c r="AB47" s="13" t="inlineStr"/>
-      <c r="AC47" s="13" t="inlineStr"/>
-      <c r="AD47" s="13" t="inlineStr"/>
-      <c r="AE47" s="13" t="inlineStr"/>
-      <c r="AF47" s="14" t="inlineStr"/>
+      <c r="F47" s="16" t="inlineStr"/>
+      <c r="G47" s="16" t="inlineStr"/>
+      <c r="H47" s="16" t="inlineStr"/>
+      <c r="I47" s="16" t="inlineStr"/>
+      <c r="J47" s="16" t="inlineStr"/>
+      <c r="K47" s="16" t="inlineStr"/>
+      <c r="L47" s="16" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr"/>
+      <c r="N47" s="16" t="inlineStr"/>
+      <c r="O47" s="16" t="inlineStr"/>
+      <c r="P47" s="16" t="inlineStr"/>
+      <c r="Q47" s="16" t="inlineStr"/>
+      <c r="R47" s="16" t="inlineStr"/>
+      <c r="S47" s="16" t="inlineStr"/>
+      <c r="T47" s="16" t="inlineStr"/>
+      <c r="U47" s="16" t="inlineStr"/>
+      <c r="V47" s="16" t="inlineStr"/>
+      <c r="W47" s="16" t="inlineStr"/>
+      <c r="X47" s="16" t="inlineStr"/>
+      <c r="Y47" s="16" t="inlineStr"/>
+      <c r="Z47" s="16" t="inlineStr"/>
+      <c r="AA47" s="16" t="inlineStr"/>
+      <c r="AB47" s="16" t="inlineStr"/>
+      <c r="AC47" s="16" t="inlineStr"/>
+      <c r="AD47" s="16" t="inlineStr"/>
+      <c r="AE47" s="16" t="inlineStr"/>
+      <c r="AF47" s="17" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>ITM-046</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>What are the potential hazards and drawbacks of elevated coronary thrombus burden and its percutaneous removal via thrombectomy, including technical limitations of existing devices and the adverse outcomes that may paradoxically result from the procedure?</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>**Elevated coronary thrombus burden** is an independent predictor of adverse outcomes including cardiovascular death, cardiogenic shock, heart failure, and no-reflow phenomenon during primary PCI for STEMI. Despite the intuitive rationale for removing thrombus before stenting, **routine aspiration thrombectomy has not demonstrated clinical benefit** and carries a paradoxical risk of **increased stroke**, creating a challenging clinical dilemma.
 **Hazards of High Thrombus Burden**
@@ -5448,7 +5486,7 @@
 Would you like to explore the emerging data on newer thrombus removal technologies or pharmacologic adjuncts (e.g., glycoprotein IIb/IIIa inhibitors, prolonged antithrombotic infusions) that may address the limitations of current mechanical approaches in high thrombus burden STEMI?</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>An elevated coronary thrombus (blood clot) burden is a high-risk scenario typically encountered during an acute myocardial infarction (AMI), particularly ST-segment elevation myocardial infarction (STEMI). While percutaneous coronary intervention (PCI) is the gold standard for restoring blood flow, the presence of a massive clot poses significant challenges.
 Historically, physicians routinely used percutaneous thrombectomy (manual aspiration or mechanical removal of the clot) prior to placing a stent. However, large-scale clinical trials (such as the TOTAL and TASTE trials) revealed significant device limitations and paradoxical risks, shifting modern guidelines away from the routine use of thrombectomy.
@@ -5476,51 +5514,51 @@
 Because of the mechanical limitations of the devices and the paradoxical increased risk of stroke and distal embolization, the routine use of percutaneous aspiration thrombectomy has been downgraded to a **Class III (harmful/not recommended)** indication in modern cardiology guidelines. Today, it is generally reserved strictly as a "bailout" strategy for highly selected patients where massive thrombus burden completely precludes the safe placement of a stent. Future advancements, such as continuous computer-assisted vacuum thrombectomy (CAVT), are currently being investigated to overcome the historic limitations of manual syringe-based aspiration.</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr"/>
-      <c r="G48" s="13" t="inlineStr"/>
-      <c r="H48" s="13" t="inlineStr"/>
-      <c r="I48" s="13" t="inlineStr"/>
-      <c r="J48" s="13" t="inlineStr"/>
-      <c r="K48" s="13" t="inlineStr"/>
-      <c r="L48" s="13" t="inlineStr"/>
-      <c r="M48" s="13" t="inlineStr"/>
-      <c r="N48" s="13" t="inlineStr"/>
-      <c r="O48" s="13" t="inlineStr"/>
-      <c r="P48" s="13" t="inlineStr"/>
-      <c r="Q48" s="13" t="inlineStr"/>
-      <c r="R48" s="13" t="inlineStr"/>
-      <c r="S48" s="13" t="inlineStr"/>
-      <c r="T48" s="13" t="inlineStr"/>
-      <c r="U48" s="13" t="inlineStr"/>
-      <c r="V48" s="13" t="inlineStr"/>
-      <c r="W48" s="13" t="inlineStr"/>
-      <c r="X48" s="13" t="inlineStr"/>
-      <c r="Y48" s="13" t="inlineStr"/>
-      <c r="Z48" s="13" t="inlineStr"/>
-      <c r="AA48" s="13" t="inlineStr"/>
-      <c r="AB48" s="13" t="inlineStr"/>
-      <c r="AC48" s="13" t="inlineStr"/>
-      <c r="AD48" s="13" t="inlineStr"/>
-      <c r="AE48" s="13" t="inlineStr"/>
-      <c r="AF48" s="14" t="inlineStr"/>
+      <c r="F48" s="16" t="inlineStr"/>
+      <c r="G48" s="16" t="inlineStr"/>
+      <c r="H48" s="16" t="inlineStr"/>
+      <c r="I48" s="16" t="inlineStr"/>
+      <c r="J48" s="16" t="inlineStr"/>
+      <c r="K48" s="16" t="inlineStr"/>
+      <c r="L48" s="16" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr"/>
+      <c r="N48" s="16" t="inlineStr"/>
+      <c r="O48" s="16" t="inlineStr"/>
+      <c r="P48" s="16" t="inlineStr"/>
+      <c r="Q48" s="16" t="inlineStr"/>
+      <c r="R48" s="16" t="inlineStr"/>
+      <c r="S48" s="16" t="inlineStr"/>
+      <c r="T48" s="16" t="inlineStr"/>
+      <c r="U48" s="16" t="inlineStr"/>
+      <c r="V48" s="16" t="inlineStr"/>
+      <c r="W48" s="16" t="inlineStr"/>
+      <c r="X48" s="16" t="inlineStr"/>
+      <c r="Y48" s="16" t="inlineStr"/>
+      <c r="Z48" s="16" t="inlineStr"/>
+      <c r="AA48" s="16" t="inlineStr"/>
+      <c r="AB48" s="16" t="inlineStr"/>
+      <c r="AC48" s="16" t="inlineStr"/>
+      <c r="AD48" s="16" t="inlineStr"/>
+      <c r="AE48" s="16" t="inlineStr"/>
+      <c r="AF48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>ITM-047</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>Allergy &amp; Immunology</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>What is the allergic cross-reactivity profile among aspirin, ibuprofen, and acetaminophen?</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>The cross-reactivity among aspirin, ibuprofen, and acetaminophen depends critically on the **type of hypersensitivity reaction** involved — specifically whether it is a **COX-1-mediated (cross-reactive) reaction** or an **immunologically mediated (selective) reaction**.
 **Aspirin ↔ Ibuprofen: High Cross-Reactivity in COX-1-Mediated Reactions**
@@ -5540,7 +5578,7 @@
 Would you like to explore the specific aspirin desensitization protocols used for patients with AERD who require aspirin for cardiovascular indications?</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>To understand the allergic cross-reactivity profile among **aspirin, ibuprofen, and acetaminophen**, it is necessary to differentiate between the two distinct types of "drug allergies" that occur with these medications: **COX-1-mediated hypersensitivity** (which is a pseudoallergy based on the drug's mechanism) and **true immunologic allergy** (which is an IgE-mediated response to the drug's chemical structure).
 Here is the cross-reactivity profile broken down by the type of allergy a patient has:
@@ -5567,51 +5605,51 @@
  * Highly selective COX-2 inhibitors (like **celecoxib**) are also widely used as safe alternatives, as they do not inhibit COX-1 and are well tolerated by the vast majority of NSAID-hypersensitive patients.</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr"/>
-      <c r="G49" s="13" t="inlineStr"/>
-      <c r="H49" s="13" t="inlineStr"/>
-      <c r="I49" s="13" t="inlineStr"/>
-      <c r="J49" s="13" t="inlineStr"/>
-      <c r="K49" s="13" t="inlineStr"/>
-      <c r="L49" s="13" t="inlineStr"/>
-      <c r="M49" s="13" t="inlineStr"/>
-      <c r="N49" s="13" t="inlineStr"/>
-      <c r="O49" s="13" t="inlineStr"/>
-      <c r="P49" s="13" t="inlineStr"/>
-      <c r="Q49" s="13" t="inlineStr"/>
-      <c r="R49" s="13" t="inlineStr"/>
-      <c r="S49" s="13" t="inlineStr"/>
-      <c r="T49" s="13" t="inlineStr"/>
-      <c r="U49" s="13" t="inlineStr"/>
-      <c r="V49" s="13" t="inlineStr"/>
-      <c r="W49" s="13" t="inlineStr"/>
-      <c r="X49" s="13" t="inlineStr"/>
-      <c r="Y49" s="13" t="inlineStr"/>
-      <c r="Z49" s="13" t="inlineStr"/>
-      <c r="AA49" s="13" t="inlineStr"/>
-      <c r="AB49" s="13" t="inlineStr"/>
-      <c r="AC49" s="13" t="inlineStr"/>
-      <c r="AD49" s="13" t="inlineStr"/>
-      <c r="AE49" s="13" t="inlineStr"/>
-      <c r="AF49" s="14" t="inlineStr"/>
+      <c r="F49" s="16" t="inlineStr"/>
+      <c r="G49" s="16" t="inlineStr"/>
+      <c r="H49" s="16" t="inlineStr"/>
+      <c r="I49" s="16" t="inlineStr"/>
+      <c r="J49" s="16" t="inlineStr"/>
+      <c r="K49" s="16" t="inlineStr"/>
+      <c r="L49" s="16" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr"/>
+      <c r="N49" s="16" t="inlineStr"/>
+      <c r="O49" s="16" t="inlineStr"/>
+      <c r="P49" s="16" t="inlineStr"/>
+      <c r="Q49" s="16" t="inlineStr"/>
+      <c r="R49" s="16" t="inlineStr"/>
+      <c r="S49" s="16" t="inlineStr"/>
+      <c r="T49" s="16" t="inlineStr"/>
+      <c r="U49" s="16" t="inlineStr"/>
+      <c r="V49" s="16" t="inlineStr"/>
+      <c r="W49" s="16" t="inlineStr"/>
+      <c r="X49" s="16" t="inlineStr"/>
+      <c r="Y49" s="16" t="inlineStr"/>
+      <c r="Z49" s="16" t="inlineStr"/>
+      <c r="AA49" s="16" t="inlineStr"/>
+      <c r="AB49" s="16" t="inlineStr"/>
+      <c r="AC49" s="16" t="inlineStr"/>
+      <c r="AD49" s="16" t="inlineStr"/>
+      <c r="AE49" s="16" t="inlineStr"/>
+      <c r="AF49" s="17" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>ITM-048</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>Infectious Disease</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>At what threshold of alkaline phosphatase elevation would posaconazole-induced hepatotoxicity warrant close monitoring versus requiring intervention or discontinuation of the drug?</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>### Short Answer
 There is **no specific alkaline phosphatase (ALP) numeric cutoff** unique to posaconazole that automatically triggers monitoring versus discontinuation in the official prescribing information. The regulatory labeling and most clinical literature instead rely on **general drug-induced liver injury (DILI) grading frameworks** and clinical judgment rather than a single ALP value. Below is what the available evidence supports.
@@ -5633,7 +5671,7 @@
 There is no posaconazole-specific ALP number that dictates action. In practice, **isolated ALP elevations up to ~3× ULN (CTCAE Grade 1–2) generally warrant close monitoring with continued therapy**, while **ALP &gt;5× ULN (Grade 3+), a worsening trend, a cholestatic pattern with rising bilirubin, or any elevation with clinical symptoms warrants intervention** (TDM, dose adjustment, or discontinuation). Crucially, the label emphasizes acting on the *clinical picture and overall LFT/bilirubin trend* rather than any single ALP threshold—so the decision should integrate the magnitude, trajectory, accompanying bilirubin, symptoms, dose, and concomitant hepatotoxic drugs. This is general clinical information; management of an individual patient should be guided by the treating clinician.</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>### Drug Label
 According to the FDA-approved drug label, **posaconazole does not specify a discrete alkaline phosphatase (ALP) threshold** that differentiates close monitoring from intervention or discontinuation. The label states that hepatic reactions — including mild to moderate elevations in ALT, AST, ALP, total bilirubin, and clinical hepatitis — have been reported, and that these elevations were generally reversible on discontinuation, with some normalizing without drug interruption. Severe hepatic reactions, including cholestasis and hepatic failure (with fatalities), have occurred primarily in patients with serious underlying conditions (e.g., hematologic malignancy) receiving the oral suspension at 800 mg daily.
@@ -5667,51 +5705,51 @@
 National Comprehensive Cancer Network. Management of Immune Checkpoint Inhibitor-Related Toxicities.</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr"/>
-      <c r="G50" s="13" t="inlineStr"/>
-      <c r="H50" s="13" t="inlineStr"/>
-      <c r="I50" s="13" t="inlineStr"/>
-      <c r="J50" s="13" t="inlineStr"/>
-      <c r="K50" s="13" t="inlineStr"/>
-      <c r="L50" s="13" t="inlineStr"/>
-      <c r="M50" s="13" t="inlineStr"/>
-      <c r="N50" s="13" t="inlineStr"/>
-      <c r="O50" s="13" t="inlineStr"/>
-      <c r="P50" s="13" t="inlineStr"/>
-      <c r="Q50" s="13" t="inlineStr"/>
-      <c r="R50" s="13" t="inlineStr"/>
-      <c r="S50" s="13" t="inlineStr"/>
-      <c r="T50" s="13" t="inlineStr"/>
-      <c r="U50" s="13" t="inlineStr"/>
-      <c r="V50" s="13" t="inlineStr"/>
-      <c r="W50" s="13" t="inlineStr"/>
-      <c r="X50" s="13" t="inlineStr"/>
-      <c r="Y50" s="13" t="inlineStr"/>
-      <c r="Z50" s="13" t="inlineStr"/>
-      <c r="AA50" s="13" t="inlineStr"/>
-      <c r="AB50" s="13" t="inlineStr"/>
-      <c r="AC50" s="13" t="inlineStr"/>
-      <c r="AD50" s="13" t="inlineStr"/>
-      <c r="AE50" s="13" t="inlineStr"/>
-      <c r="AF50" s="14" t="inlineStr"/>
+      <c r="F50" s="16" t="inlineStr"/>
+      <c r="G50" s="16" t="inlineStr"/>
+      <c r="H50" s="16" t="inlineStr"/>
+      <c r="I50" s="16" t="inlineStr"/>
+      <c r="J50" s="16" t="inlineStr"/>
+      <c r="K50" s="16" t="inlineStr"/>
+      <c r="L50" s="16" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr"/>
+      <c r="N50" s="16" t="inlineStr"/>
+      <c r="O50" s="16" t="inlineStr"/>
+      <c r="P50" s="16" t="inlineStr"/>
+      <c r="Q50" s="16" t="inlineStr"/>
+      <c r="R50" s="16" t="inlineStr"/>
+      <c r="S50" s="16" t="inlineStr"/>
+      <c r="T50" s="16" t="inlineStr"/>
+      <c r="U50" s="16" t="inlineStr"/>
+      <c r="V50" s="16" t="inlineStr"/>
+      <c r="W50" s="16" t="inlineStr"/>
+      <c r="X50" s="16" t="inlineStr"/>
+      <c r="Y50" s="16" t="inlineStr"/>
+      <c r="Z50" s="16" t="inlineStr"/>
+      <c r="AA50" s="16" t="inlineStr"/>
+      <c r="AB50" s="16" t="inlineStr"/>
+      <c r="AC50" s="16" t="inlineStr"/>
+      <c r="AD50" s="16" t="inlineStr"/>
+      <c r="AE50" s="16" t="inlineStr"/>
+      <c r="AF50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>ITM-049</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>Infectious Disease</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>At what threshold of alkaline phosphatase elevation would posaconazole-induced hepatotoxicity warrant close monitoring versus requiring intervention or discontinuation of the drug?</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>### Drug Label
 According to the FDA-approved drug label, **posaconazole does not specify a discrete alkaline phosphatase (ALP) threshold** that differentiates close monitoring from intervention or discontinuation. The label states that hepatic reactions — including mild to moderate elevations in ALT, AST, ALP, total bilirubin, and clinical hepatitis — have been reported, and that these elevations were generally reversible on discontinuation, with some normalizing without drug interruption. Severe hepatic reactions, including cholestasis and hepatic failure (with fatalities), have occurred primarily in patients with serious underlying conditions (e.g., hematologic malignancy) receiving the oral suspension at 800 mg daily.
@@ -5745,7 +5783,7 @@
 National Comprehensive Cancer Network. Management of Immune Checkpoint Inhibitor-Related Toxicities.</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>There is **no posaconazole-specific alkaline phosphatase (ALP) cutoff** in the label that automatically mandates stopping. The posaconazole label says to check liver tests at baseline and during therapy; if abnormalities develop, monitor for worsening injury, and **consider discontinuation if clinical signs/symptoms of liver disease occur** and are attributable to posaconazole.
 A practical way to handle **suspected posaconazole-related ALP elevation** is:
@@ -5759,51 +5797,51 @@
 For an **isolated, asymptomatic ALP elevation**, close monitoring is generally reasonable for **mild elevations up to ~2.5× ULN** and sometimes grade 2 (**2.5–5× ULN**) if stable and bilirubin/INR are normal. **ALP &gt;2× ULN** should trigger a DILI evaluation, and **ALP &gt;5× ULN**, a rising trend, or any bilirubin/jaundice/symptoms should generally prompt **intervention—holding, switching, or discontinuing posaconazole depending on infection risk and alternatives**.</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr"/>
-      <c r="G51" s="13" t="inlineStr"/>
-      <c r="H51" s="13" t="inlineStr"/>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr"/>
-      <c r="K51" s="13" t="inlineStr"/>
-      <c r="L51" s="13" t="inlineStr"/>
-      <c r="M51" s="13" t="inlineStr"/>
-      <c r="N51" s="13" t="inlineStr"/>
-      <c r="O51" s="13" t="inlineStr"/>
-      <c r="P51" s="13" t="inlineStr"/>
-      <c r="Q51" s="13" t="inlineStr"/>
-      <c r="R51" s="13" t="inlineStr"/>
-      <c r="S51" s="13" t="inlineStr"/>
-      <c r="T51" s="13" t="inlineStr"/>
-      <c r="U51" s="13" t="inlineStr"/>
-      <c r="V51" s="13" t="inlineStr"/>
-      <c r="W51" s="13" t="inlineStr"/>
-      <c r="X51" s="13" t="inlineStr"/>
-      <c r="Y51" s="13" t="inlineStr"/>
-      <c r="Z51" s="13" t="inlineStr"/>
-      <c r="AA51" s="13" t="inlineStr"/>
-      <c r="AB51" s="13" t="inlineStr"/>
-      <c r="AC51" s="13" t="inlineStr"/>
-      <c r="AD51" s="13" t="inlineStr"/>
-      <c r="AE51" s="13" t="inlineStr"/>
-      <c r="AF51" s="14" t="inlineStr"/>
+      <c r="F51" s="16" t="inlineStr"/>
+      <c r="G51" s="16" t="inlineStr"/>
+      <c r="H51" s="16" t="inlineStr"/>
+      <c r="I51" s="16" t="inlineStr"/>
+      <c r="J51" s="16" t="inlineStr"/>
+      <c r="K51" s="16" t="inlineStr"/>
+      <c r="L51" s="16" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr"/>
+      <c r="N51" s="16" t="inlineStr"/>
+      <c r="O51" s="16" t="inlineStr"/>
+      <c r="P51" s="16" t="inlineStr"/>
+      <c r="Q51" s="16" t="inlineStr"/>
+      <c r="R51" s="16" t="inlineStr"/>
+      <c r="S51" s="16" t="inlineStr"/>
+      <c r="T51" s="16" t="inlineStr"/>
+      <c r="U51" s="16" t="inlineStr"/>
+      <c r="V51" s="16" t="inlineStr"/>
+      <c r="W51" s="16" t="inlineStr"/>
+      <c r="X51" s="16" t="inlineStr"/>
+      <c r="Y51" s="16" t="inlineStr"/>
+      <c r="Z51" s="16" t="inlineStr"/>
+      <c r="AA51" s="16" t="inlineStr"/>
+      <c r="AB51" s="16" t="inlineStr"/>
+      <c r="AC51" s="16" t="inlineStr"/>
+      <c r="AD51" s="16" t="inlineStr"/>
+      <c r="AE51" s="16" t="inlineStr"/>
+      <c r="AF51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>ITM-050</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>Family Medicine</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>How long should antibiotics be continued for an infected ingrown toenail that is resolving following nail avulsion, given that the patient has already completed 5 days of amoxicillin-clavulanate followed by 7 days of cephalexin with no wound cultures obtained?</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>In general, **if the ingrown toenail infection is clearly resolving after nail avulsion and there are no signs of spreading cellulitis or systemic infection, antibiotics usually should not be continued further**—especially after **12 total days** already completed: **5 days of amoxicillin-clavulanate + 7 days of cephalexin**.
 Why:
@@ -5815,7 +5853,7 @@
 **Seek reassessment promptly** if there is increasing redness or swelling, spreading redness up the foot, worsening pain, pus/abscess, fever, red streaks, foul odor, delayed healing, or if the patient has diabetes, peripheral vascular disease, significant immunosuppression, or poor circulation. In those cases, a clinician may consider culture, imaging, drainage/debridement, or different antibiotic coverage.</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>Given that the infection is **resolving** after nail avulsion and a total of **12 days** of oral antibiotics, it is reasonable to **discontinue antibiotics now** rather than extending the course further. The clinical response — not a predetermined duration — should guide the decision to stop.
 **Key principles supporting discontinuation:**
@@ -5836,51 +5874,51 @@
 Gariani K, Lebowitz D, von Dach E, et al. Remission in Diabetic Foot Infections: Duration of Antibiotic Therapy and Other Possible Associated Factors. Diabetes, Obesity &amp; Metabolism. 2019;21(2):244-251. doi:10.1111/dom.13507.</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr"/>
-      <c r="G52" s="13" t="inlineStr"/>
-      <c r="H52" s="13" t="inlineStr"/>
-      <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr"/>
-      <c r="K52" s="13" t="inlineStr"/>
-      <c r="L52" s="13" t="inlineStr"/>
-      <c r="M52" s="13" t="inlineStr"/>
-      <c r="N52" s="13" t="inlineStr"/>
-      <c r="O52" s="13" t="inlineStr"/>
-      <c r="P52" s="13" t="inlineStr"/>
-      <c r="Q52" s="13" t="inlineStr"/>
-      <c r="R52" s="13" t="inlineStr"/>
-      <c r="S52" s="13" t="inlineStr"/>
-      <c r="T52" s="13" t="inlineStr"/>
-      <c r="U52" s="13" t="inlineStr"/>
-      <c r="V52" s="13" t="inlineStr"/>
-      <c r="W52" s="13" t="inlineStr"/>
-      <c r="X52" s="13" t="inlineStr"/>
-      <c r="Y52" s="13" t="inlineStr"/>
-      <c r="Z52" s="13" t="inlineStr"/>
-      <c r="AA52" s="13" t="inlineStr"/>
-      <c r="AB52" s="13" t="inlineStr"/>
-      <c r="AC52" s="13" t="inlineStr"/>
-      <c r="AD52" s="13" t="inlineStr"/>
-      <c r="AE52" s="13" t="inlineStr"/>
-      <c r="AF52" s="14" t="inlineStr"/>
+      <c r="F52" s="16" t="inlineStr"/>
+      <c r="G52" s="16" t="inlineStr"/>
+      <c r="H52" s="16" t="inlineStr"/>
+      <c r="I52" s="16" t="inlineStr"/>
+      <c r="J52" s="16" t="inlineStr"/>
+      <c r="K52" s="16" t="inlineStr"/>
+      <c r="L52" s="16" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr"/>
+      <c r="N52" s="16" t="inlineStr"/>
+      <c r="O52" s="16" t="inlineStr"/>
+      <c r="P52" s="16" t="inlineStr"/>
+      <c r="Q52" s="16" t="inlineStr"/>
+      <c r="R52" s="16" t="inlineStr"/>
+      <c r="S52" s="16" t="inlineStr"/>
+      <c r="T52" s="16" t="inlineStr"/>
+      <c r="U52" s="16" t="inlineStr"/>
+      <c r="V52" s="16" t="inlineStr"/>
+      <c r="W52" s="16" t="inlineStr"/>
+      <c r="X52" s="16" t="inlineStr"/>
+      <c r="Y52" s="16" t="inlineStr"/>
+      <c r="Z52" s="16" t="inlineStr"/>
+      <c r="AA52" s="16" t="inlineStr"/>
+      <c r="AB52" s="16" t="inlineStr"/>
+      <c r="AC52" s="16" t="inlineStr"/>
+      <c r="AD52" s="16" t="inlineStr"/>
+      <c r="AE52" s="16" t="inlineStr"/>
+      <c r="AF52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>ITM-051</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>Transplantation</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>Is transjugular liver biopsy with hepatic venous pressure gradient measurement necessary in a patient with a history of alcohol use, mildly elevated liver enzymes, ZZ alpha-1 antitrypsin deficiency, normal MR elastography, normal platelet count, and normal liver ultrasound who is undergoing evaluation for lung transplantation?</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>**Short answer:** Based on the facts you listed, a **transjugular liver biopsy with hepatic venous pressure gradient (HVPG) measurement is not obviously “necessary” as a routine next step**—*if* liver synthetic function is normal too (INR, bilirubin, albumin), there are no imaging signs of portal hypertension, and noninvasive fibrosis scores are low. However, a lung-transplant program may still request it because transplant listing decisions often require a very high level of certainty that there is **no cirrhosis with portal hypertension or synthetic dysfunction**, which is an ISHLT-listed contraindication to isolated lung transplant unless multi-organ transplant is being considered.
 Why it may **not** be needed from a liver standpoint: in alpha-1 antitrypsin deficiency (especially PiZZ/ZZ), expert guidance supports **regular liver monitoring** with focused exam, liver ultrasound, and labs including AST/ALT/GGT, albumin, bilirubin, INR, and platelets; it does not imply that every ZZ patient with mild enzyme elevation needs biopsy. More recent AGA/AASLD/EASL/Alpha-1 Foundation consensus emphasizes **noninvasive elastography as a preferred staging method** for AATD-associated liver disease. If MR elastography is normal, platelets are normal, ultrasound is normal, and there is no splenomegaly/ascites/varices/collaterals, the pre-test probability of clinically significant portal hypertension is generally low.
@@ -5889,7 +5927,7 @@
 So: **not inherently necessary from the information provided, but it may be a center-specific requirement or a risk-stratification step before lung transplant.** A second hepatology/transplant-hepatology opinion is reasonable if the indication is unclear.</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>In this clinical scenario, **transjugular liver biopsy with HVPG measurement is likely not necessary** given the reassuring constellation of a **normal MR elastography, normal platelet count, and normal liver ultrasound**. The available noninvasive data effectively exclude clinically significant fibrosis and portal hypertension, which are the primary concerns driving invasive liver evaluation in lung transplant candidates with PiZZ [alpha-1 antitrypsin deficiency](https://www.openevidence.com/rare-disease/alpha-1-antitrypsin-deficiency) (AATD).
 **Rationale for Deferring Invasive Testing**
@@ -5908,51 +5946,51 @@
 Would you like to explore the specific FIB-4 and APRI thresholds validated for risk stratification in PiZZ AATD, or the criteria for when combined liver-lung transplantation should be considered?</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr"/>
-      <c r="G53" s="13" t="inlineStr"/>
-      <c r="H53" s="13" t="inlineStr"/>
-      <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="13" t="inlineStr"/>
-      <c r="K53" s="13" t="inlineStr"/>
-      <c r="L53" s="13" t="inlineStr"/>
-      <c r="M53" s="13" t="inlineStr"/>
-      <c r="N53" s="13" t="inlineStr"/>
-      <c r="O53" s="13" t="inlineStr"/>
-      <c r="P53" s="13" t="inlineStr"/>
-      <c r="Q53" s="13" t="inlineStr"/>
-      <c r="R53" s="13" t="inlineStr"/>
-      <c r="S53" s="13" t="inlineStr"/>
-      <c r="T53" s="13" t="inlineStr"/>
-      <c r="U53" s="13" t="inlineStr"/>
-      <c r="V53" s="13" t="inlineStr"/>
-      <c r="W53" s="13" t="inlineStr"/>
-      <c r="X53" s="13" t="inlineStr"/>
-      <c r="Y53" s="13" t="inlineStr"/>
-      <c r="Z53" s="13" t="inlineStr"/>
-      <c r="AA53" s="13" t="inlineStr"/>
-      <c r="AB53" s="13" t="inlineStr"/>
-      <c r="AC53" s="13" t="inlineStr"/>
-      <c r="AD53" s="13" t="inlineStr"/>
-      <c r="AE53" s="13" t="inlineStr"/>
-      <c r="AF53" s="14" t="inlineStr"/>
+      <c r="F53" s="16" t="inlineStr"/>
+      <c r="G53" s="16" t="inlineStr"/>
+      <c r="H53" s="16" t="inlineStr"/>
+      <c r="I53" s="16" t="inlineStr"/>
+      <c r="J53" s="16" t="inlineStr"/>
+      <c r="K53" s="16" t="inlineStr"/>
+      <c r="L53" s="16" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr"/>
+      <c r="N53" s="16" t="inlineStr"/>
+      <c r="O53" s="16" t="inlineStr"/>
+      <c r="P53" s="16" t="inlineStr"/>
+      <c r="Q53" s="16" t="inlineStr"/>
+      <c r="R53" s="16" t="inlineStr"/>
+      <c r="S53" s="16" t="inlineStr"/>
+      <c r="T53" s="16" t="inlineStr"/>
+      <c r="U53" s="16" t="inlineStr"/>
+      <c r="V53" s="16" t="inlineStr"/>
+      <c r="W53" s="16" t="inlineStr"/>
+      <c r="X53" s="16" t="inlineStr"/>
+      <c r="Y53" s="16" t="inlineStr"/>
+      <c r="Z53" s="16" t="inlineStr"/>
+      <c r="AA53" s="16" t="inlineStr"/>
+      <c r="AB53" s="16" t="inlineStr"/>
+      <c r="AC53" s="16" t="inlineStr"/>
+      <c r="AD53" s="16" t="inlineStr"/>
+      <c r="AE53" s="16" t="inlineStr"/>
+      <c r="AF53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>ITM-052</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>Dermatology</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>Are there any reported cases of urticarial vasculitis following rilonacept administration for chronic spontaneous urticaria?</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>Based on a thorough search of the available medical literature, **no reported cases of urticarial vasculitis developing as an adverse effect following rilonacept administration** have been identified, whether in the context of chronic spontaneous urticaria (CSU) or any other indication.
 Several important points provide context:
@@ -5963,7 +6001,7 @@
 Would you like to explore the evidence for IL-1-targeted therapies in the treatment of refractory urticarial vasculitis, including comparative efficacy of anakinra, canakinumab, and rilonacept?</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>Based on my searches, let me look more specifically for any case reports of this adverse event.Based on my searches, I could not find any reported cases of urticarial vasculitis (UV) occurring after rilonacept administration for chronic spontaneous urticaria (CSU). Here's the relevant context:
 **Rilonacept is not an established treatment for CSU.** Rilonacept (Arcalyst), an IL-1 "trap" inhibitor, is FDA-approved for cryopyrin-associated periodic syndromes (CAPS), deficiency of IL-1 receptor antagonist (DIRA), and recurrent pericarditis—not CSU. Arcalyst (rilonacept) is a prescription medication that's used to treat adults and children with certain rare inflammatory conditions, including cryopyrin-associated periodic syndromes (CAPS), deficiency of interleukin-1 receptor antagonist (DIRA), and recurrent pericarditis (RP).
@@ -5973,51 +6011,51 @@
 **Bottom line:** I found no published case reports of rilonacept-induced urticarial vasculitis in any indication, and certainly none in the context of CSU—a condition for which rilonacept is neither approved nor shown to be effective. If you are researching a specific case or suspected reaction, I'd recommend checking the FDA Adverse Event Reporting System (FAERS) database and a targeted PubMed/Embase search, as a rare or very recent individual case report could exist that isn't surfacing in general web results. Would you like me to search any of those specific databases or look into a related agent (e.g., anakinra or canakinumab)?</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr"/>
-      <c r="G54" s="13" t="inlineStr"/>
-      <c r="H54" s="13" t="inlineStr"/>
-      <c r="I54" s="13" t="inlineStr"/>
-      <c r="J54" s="13" t="inlineStr"/>
-      <c r="K54" s="13" t="inlineStr"/>
-      <c r="L54" s="13" t="inlineStr"/>
-      <c r="M54" s="13" t="inlineStr"/>
-      <c r="N54" s="13" t="inlineStr"/>
-      <c r="O54" s="13" t="inlineStr"/>
-      <c r="P54" s="13" t="inlineStr"/>
-      <c r="Q54" s="13" t="inlineStr"/>
-      <c r="R54" s="13" t="inlineStr"/>
-      <c r="S54" s="13" t="inlineStr"/>
-      <c r="T54" s="13" t="inlineStr"/>
-      <c r="U54" s="13" t="inlineStr"/>
-      <c r="V54" s="13" t="inlineStr"/>
-      <c r="W54" s="13" t="inlineStr"/>
-      <c r="X54" s="13" t="inlineStr"/>
-      <c r="Y54" s="13" t="inlineStr"/>
-      <c r="Z54" s="13" t="inlineStr"/>
-      <c r="AA54" s="13" t="inlineStr"/>
-      <c r="AB54" s="13" t="inlineStr"/>
-      <c r="AC54" s="13" t="inlineStr"/>
-      <c r="AD54" s="13" t="inlineStr"/>
-      <c r="AE54" s="13" t="inlineStr"/>
-      <c r="AF54" s="14" t="inlineStr"/>
+      <c r="F54" s="16" t="inlineStr"/>
+      <c r="G54" s="16" t="inlineStr"/>
+      <c r="H54" s="16" t="inlineStr"/>
+      <c r="I54" s="16" t="inlineStr"/>
+      <c r="J54" s="16" t="inlineStr"/>
+      <c r="K54" s="16" t="inlineStr"/>
+      <c r="L54" s="16" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr"/>
+      <c r="N54" s="16" t="inlineStr"/>
+      <c r="O54" s="16" t="inlineStr"/>
+      <c r="P54" s="16" t="inlineStr"/>
+      <c r="Q54" s="16" t="inlineStr"/>
+      <c r="R54" s="16" t="inlineStr"/>
+      <c r="S54" s="16" t="inlineStr"/>
+      <c r="T54" s="16" t="inlineStr"/>
+      <c r="U54" s="16" t="inlineStr"/>
+      <c r="V54" s="16" t="inlineStr"/>
+      <c r="W54" s="16" t="inlineStr"/>
+      <c r="X54" s="16" t="inlineStr"/>
+      <c r="Y54" s="16" t="inlineStr"/>
+      <c r="Z54" s="16" t="inlineStr"/>
+      <c r="AA54" s="16" t="inlineStr"/>
+      <c r="AB54" s="16" t="inlineStr"/>
+      <c r="AC54" s="16" t="inlineStr"/>
+      <c r="AD54" s="16" t="inlineStr"/>
+      <c r="AE54" s="16" t="inlineStr"/>
+      <c r="AF54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>ITM-053</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Dermatology</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>Are there any reported cases of urticarial vasculitis following rilonacept administration for chronic spontaneous urticaria?</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>Based on a thorough search of the available medical literature, **no reported cases of urticarial vasculitis developing as an adverse effect following rilonacept administration** have been identified, whether in the context of chronic spontaneous urticaria (CSU) or any other indication.
 Several important points provide context:
@@ -6028,7 +6066,7 @@
 Would you like to explore the evidence for IL-1-targeted therapies in the treatment of refractory urticarial vasculitis, including comparative efficacy of anakinra, canakinumab, and rilonacept?</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
         <is>
           <t>**Short answer: I did not find any published reported cases of urticarial vasculitis occurring after rilonacept given for chronic spontaneous urticaria (CSU).** More importantly, rilonacept does **not** appear to be an approved or standard CSU therapy: the current ARCALYST/rilonacept prescribing information lists indications for CAPS, DIRA, and recurrent pericarditis—not CSU.
 What I found:
@@ -6038,51 +6076,51 @@
 **Bottom line:** As of the sources I could verify, there are **no reported published cases specifically describing urticarial vasculitis following rilonacept administration for CSU**. If this is a real patient scenario, it would be worth considering whether the initial diagnosis was CSU vs. pre-existing/overlapping urticarial vasculitis, and confirming with lesion duration, residual bruising/hyperpigmentation, complement testing, and skin biopsy. Also, double-check the drug name—**rilonacept** is easily confused with CSU agents in development/approved in some settings such as **rilzabrutinib/remibrutinib**.</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr"/>
-      <c r="G55" s="13" t="inlineStr"/>
-      <c r="H55" s="13" t="inlineStr"/>
-      <c r="I55" s="13" t="inlineStr"/>
-      <c r="J55" s="13" t="inlineStr"/>
-      <c r="K55" s="13" t="inlineStr"/>
-      <c r="L55" s="13" t="inlineStr"/>
-      <c r="M55" s="13" t="inlineStr"/>
-      <c r="N55" s="13" t="inlineStr"/>
-      <c r="O55" s="13" t="inlineStr"/>
-      <c r="P55" s="13" t="inlineStr"/>
-      <c r="Q55" s="13" t="inlineStr"/>
-      <c r="R55" s="13" t="inlineStr"/>
-      <c r="S55" s="13" t="inlineStr"/>
-      <c r="T55" s="13" t="inlineStr"/>
-      <c r="U55" s="13" t="inlineStr"/>
-      <c r="V55" s="13" t="inlineStr"/>
-      <c r="W55" s="13" t="inlineStr"/>
-      <c r="X55" s="13" t="inlineStr"/>
-      <c r="Y55" s="13" t="inlineStr"/>
-      <c r="Z55" s="13" t="inlineStr"/>
-      <c r="AA55" s="13" t="inlineStr"/>
-      <c r="AB55" s="13" t="inlineStr"/>
-      <c r="AC55" s="13" t="inlineStr"/>
-      <c r="AD55" s="13" t="inlineStr"/>
-      <c r="AE55" s="13" t="inlineStr"/>
-      <c r="AF55" s="14" t="inlineStr"/>
+      <c r="F55" s="16" t="inlineStr"/>
+      <c r="G55" s="16" t="inlineStr"/>
+      <c r="H55" s="16" t="inlineStr"/>
+      <c r="I55" s="16" t="inlineStr"/>
+      <c r="J55" s="16" t="inlineStr"/>
+      <c r="K55" s="16" t="inlineStr"/>
+      <c r="L55" s="16" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr"/>
+      <c r="N55" s="16" t="inlineStr"/>
+      <c r="O55" s="16" t="inlineStr"/>
+      <c r="P55" s="16" t="inlineStr"/>
+      <c r="Q55" s="16" t="inlineStr"/>
+      <c r="R55" s="16" t="inlineStr"/>
+      <c r="S55" s="16" t="inlineStr"/>
+      <c r="T55" s="16" t="inlineStr"/>
+      <c r="U55" s="16" t="inlineStr"/>
+      <c r="V55" s="16" t="inlineStr"/>
+      <c r="W55" s="16" t="inlineStr"/>
+      <c r="X55" s="16" t="inlineStr"/>
+      <c r="Y55" s="16" t="inlineStr"/>
+      <c r="Z55" s="16" t="inlineStr"/>
+      <c r="AA55" s="16" t="inlineStr"/>
+      <c r="AB55" s="16" t="inlineStr"/>
+      <c r="AC55" s="16" t="inlineStr"/>
+      <c r="AD55" s="16" t="inlineStr"/>
+      <c r="AE55" s="16" t="inlineStr"/>
+      <c r="AF55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>ITM-054</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
         <is>
           <t>How can panic attacks be managed at home?</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>Panic attacks can be effectively managed at home through a combination of **breathing retraining, relaxation techniques, cognitive strategies, exercise, and mindfulness-based practices**, all of which have evidence supporting their use in reducing panic symptoms. For subthreshold or mild symptoms, self-management alone may be adequate; however, severe or recurrent panic attacks warrant professional evaluation and formal treatment.
 **Acute Panic Attack Management**
@@ -6103,7 +6141,7 @@
 Would you like to explore the evidence for pharmacologic options (e.g., SSRIs, benzodiazepines) as adjuncts to these self-management strategies for panic disorder?</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>Panic attacks can be frightening, but there are several effective techniques you can use at home to manage them. Here are some evidence-based strategies:
 ### During a Panic Attack
@@ -6139,51 +6177,51 @@
 Would you like me to go deeper into any of these techniques?</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr"/>
-      <c r="G56" s="13" t="inlineStr"/>
-      <c r="H56" s="13" t="inlineStr"/>
-      <c r="I56" s="13" t="inlineStr"/>
-      <c r="J56" s="13" t="inlineStr"/>
-      <c r="K56" s="13" t="inlineStr"/>
-      <c r="L56" s="13" t="inlineStr"/>
-      <c r="M56" s="13" t="inlineStr"/>
-      <c r="N56" s="13" t="inlineStr"/>
-      <c r="O56" s="13" t="inlineStr"/>
-      <c r="P56" s="13" t="inlineStr"/>
-      <c r="Q56" s="13" t="inlineStr"/>
-      <c r="R56" s="13" t="inlineStr"/>
-      <c r="S56" s="13" t="inlineStr"/>
-      <c r="T56" s="13" t="inlineStr"/>
-      <c r="U56" s="13" t="inlineStr"/>
-      <c r="V56" s="13" t="inlineStr"/>
-      <c r="W56" s="13" t="inlineStr"/>
-      <c r="X56" s="13" t="inlineStr"/>
-      <c r="Y56" s="13" t="inlineStr"/>
-      <c r="Z56" s="13" t="inlineStr"/>
-      <c r="AA56" s="13" t="inlineStr"/>
-      <c r="AB56" s="13" t="inlineStr"/>
-      <c r="AC56" s="13" t="inlineStr"/>
-      <c r="AD56" s="13" t="inlineStr"/>
-      <c r="AE56" s="13" t="inlineStr"/>
-      <c r="AF56" s="14" t="inlineStr"/>
+      <c r="F56" s="16" t="inlineStr"/>
+      <c r="G56" s="16" t="inlineStr"/>
+      <c r="H56" s="16" t="inlineStr"/>
+      <c r="I56" s="16" t="inlineStr"/>
+      <c r="J56" s="16" t="inlineStr"/>
+      <c r="K56" s="16" t="inlineStr"/>
+      <c r="L56" s="16" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr"/>
+      <c r="N56" s="16" t="inlineStr"/>
+      <c r="O56" s="16" t="inlineStr"/>
+      <c r="P56" s="16" t="inlineStr"/>
+      <c r="Q56" s="16" t="inlineStr"/>
+      <c r="R56" s="16" t="inlineStr"/>
+      <c r="S56" s="16" t="inlineStr"/>
+      <c r="T56" s="16" t="inlineStr"/>
+      <c r="U56" s="16" t="inlineStr"/>
+      <c r="V56" s="16" t="inlineStr"/>
+      <c r="W56" s="16" t="inlineStr"/>
+      <c r="X56" s="16" t="inlineStr"/>
+      <c r="Y56" s="16" t="inlineStr"/>
+      <c r="Z56" s="16" t="inlineStr"/>
+      <c r="AA56" s="16" t="inlineStr"/>
+      <c r="AB56" s="16" t="inlineStr"/>
+      <c r="AC56" s="16" t="inlineStr"/>
+      <c r="AD56" s="16" t="inlineStr"/>
+      <c r="AE56" s="16" t="inlineStr"/>
+      <c r="AF56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>ITM-055</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>Family Medicine</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="15" t="inlineStr">
         <is>
           <t>Should a 20-year-old presenting with new stretch marks on the legs but no change in body weight undergo further evaluation?</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>In most cases, **new stretch marks on the legs in a 20-year-old without weight change are likely physiologic striae distensae** related to the tail end of the adolescent growth spurt or localized mechanical stretching (e.g., exercise-related muscle hypertrophy), and **routine laboratory workup is not required** if the history and exam are otherwise unremarkable. However, a focused clinical assessment is warranted to exclude important secondary causes before reassuring the patient.
 **Most Likely Diagnosis: Physiologic Striae Distensae**
@@ -6200,7 +6238,7 @@
 Would it be helpful to know the patient's sex, exercise habits, any medication/supplement use, or whether there are any associated symptoms such as joint pain or easy bruising?</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>**Yes, a 20-year-old presenting with new stretch marks (striae) and no change in body weight should undergo further medical evaluation.**
 While stretch marks are incredibly common and usually harmless, they are most often associated with rapid skin stretching from weight gain, obesity, pregnancy, or adolescent growth spurts. When new stretch marks appear without any obvious fluctuation in body weight or size, it is a medical standard to investigate underlying causes.
@@ -6221,51 +6259,51 @@
 The healthcare provider will take a detailed medical history (asking about current and past medications, supplements, and exercise habits) and perform a physical exam. Depending on the appearance of the stretch marks and whether the patient has other symptoms (like joint hypermobility or easily bruised skin), the doctor may order blood or urine tests to check hormone levels.</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr"/>
-      <c r="G57" s="13" t="inlineStr"/>
-      <c r="H57" s="13" t="inlineStr"/>
-      <c r="I57" s="13" t="inlineStr"/>
-      <c r="J57" s="13" t="inlineStr"/>
-      <c r="K57" s="13" t="inlineStr"/>
-      <c r="L57" s="13" t="inlineStr"/>
-      <c r="M57" s="13" t="inlineStr"/>
-      <c r="N57" s="13" t="inlineStr"/>
-      <c r="O57" s="13" t="inlineStr"/>
-      <c r="P57" s="13" t="inlineStr"/>
-      <c r="Q57" s="13" t="inlineStr"/>
-      <c r="R57" s="13" t="inlineStr"/>
-      <c r="S57" s="13" t="inlineStr"/>
-      <c r="T57" s="13" t="inlineStr"/>
-      <c r="U57" s="13" t="inlineStr"/>
-      <c r="V57" s="13" t="inlineStr"/>
-      <c r="W57" s="13" t="inlineStr"/>
-      <c r="X57" s="13" t="inlineStr"/>
-      <c r="Y57" s="13" t="inlineStr"/>
-      <c r="Z57" s="13" t="inlineStr"/>
-      <c r="AA57" s="13" t="inlineStr"/>
-      <c r="AB57" s="13" t="inlineStr"/>
-      <c r="AC57" s="13" t="inlineStr"/>
-      <c r="AD57" s="13" t="inlineStr"/>
-      <c r="AE57" s="13" t="inlineStr"/>
-      <c r="AF57" s="14" t="inlineStr"/>
+      <c r="F57" s="16" t="inlineStr"/>
+      <c r="G57" s="16" t="inlineStr"/>
+      <c r="H57" s="16" t="inlineStr"/>
+      <c r="I57" s="16" t="inlineStr"/>
+      <c r="J57" s="16" t="inlineStr"/>
+      <c r="K57" s="16" t="inlineStr"/>
+      <c r="L57" s="16" t="inlineStr"/>
+      <c r="M57" s="16" t="inlineStr"/>
+      <c r="N57" s="16" t="inlineStr"/>
+      <c r="O57" s="16" t="inlineStr"/>
+      <c r="P57" s="16" t="inlineStr"/>
+      <c r="Q57" s="16" t="inlineStr"/>
+      <c r="R57" s="16" t="inlineStr"/>
+      <c r="S57" s="16" t="inlineStr"/>
+      <c r="T57" s="16" t="inlineStr"/>
+      <c r="U57" s="16" t="inlineStr"/>
+      <c r="V57" s="16" t="inlineStr"/>
+      <c r="W57" s="16" t="inlineStr"/>
+      <c r="X57" s="16" t="inlineStr"/>
+      <c r="Y57" s="16" t="inlineStr"/>
+      <c r="Z57" s="16" t="inlineStr"/>
+      <c r="AA57" s="16" t="inlineStr"/>
+      <c r="AB57" s="16" t="inlineStr"/>
+      <c r="AC57" s="16" t="inlineStr"/>
+      <c r="AD57" s="16" t="inlineStr"/>
+      <c r="AE57" s="16" t="inlineStr"/>
+      <c r="AF57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>ITM-056</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>Allergy &amp; Immunology</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>What laboratory test is used to evaluate for specific antibody deficiency?</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>The key test is a **vaccine antibody response test**, most commonly:
 **Serotype-specific pneumococcal IgG antibody titers measured before and ~4–8 weeks after immunization with the 23-valent pneumococcal polysaccharide vaccine — PPSV23/Pneumovax 23.**
@@ -6273,7 +6311,7 @@
 In lab-order terms, this may appear as **“Streptococcus pneumoniae IgG antibodies, 23 serotypes”** or **“pneumococcal serotype-specific antibody titers,”** with pre- and post-vaccine specimens. Mayo Clinic Laboratories notes this testing is used for evaluating possible immunodeficiency and pneumococcal vaccine response.</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
         <is>
           <t>The key laboratory test used to evaluate for **specific antibody deficiency (SAD)** is the measurement of **antigen-specific antibody titers before and after vaccination**, most commonly using the **23-valent unconjugated pneumococcal polysaccharide vaccine (PPSV23)**.
 **How the test works:**
@@ -6287,51 +6325,51 @@
 Would you like to explore the current management strategies for specific antibody deficiency, including indications for immunoglobulin replacement therapy versus antibiotic prophylaxis?</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr"/>
-      <c r="G58" s="13" t="inlineStr"/>
-      <c r="H58" s="13" t="inlineStr"/>
-      <c r="I58" s="13" t="inlineStr"/>
-      <c r="J58" s="13" t="inlineStr"/>
-      <c r="K58" s="13" t="inlineStr"/>
-      <c r="L58" s="13" t="inlineStr"/>
-      <c r="M58" s="13" t="inlineStr"/>
-      <c r="N58" s="13" t="inlineStr"/>
-      <c r="O58" s="13" t="inlineStr"/>
-      <c r="P58" s="13" t="inlineStr"/>
-      <c r="Q58" s="13" t="inlineStr"/>
-      <c r="R58" s="13" t="inlineStr"/>
-      <c r="S58" s="13" t="inlineStr"/>
-      <c r="T58" s="13" t="inlineStr"/>
-      <c r="U58" s="13" t="inlineStr"/>
-      <c r="V58" s="13" t="inlineStr"/>
-      <c r="W58" s="13" t="inlineStr"/>
-      <c r="X58" s="13" t="inlineStr"/>
-      <c r="Y58" s="13" t="inlineStr"/>
-      <c r="Z58" s="13" t="inlineStr"/>
-      <c r="AA58" s="13" t="inlineStr"/>
-      <c r="AB58" s="13" t="inlineStr"/>
-      <c r="AC58" s="13" t="inlineStr"/>
-      <c r="AD58" s="13" t="inlineStr"/>
-      <c r="AE58" s="13" t="inlineStr"/>
-      <c r="AF58" s="14" t="inlineStr"/>
+      <c r="F58" s="16" t="inlineStr"/>
+      <c r="G58" s="16" t="inlineStr"/>
+      <c r="H58" s="16" t="inlineStr"/>
+      <c r="I58" s="16" t="inlineStr"/>
+      <c r="J58" s="16" t="inlineStr"/>
+      <c r="K58" s="16" t="inlineStr"/>
+      <c r="L58" s="16" t="inlineStr"/>
+      <c r="M58" s="16" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr"/>
+      <c r="O58" s="16" t="inlineStr"/>
+      <c r="P58" s="16" t="inlineStr"/>
+      <c r="Q58" s="16" t="inlineStr"/>
+      <c r="R58" s="16" t="inlineStr"/>
+      <c r="S58" s="16" t="inlineStr"/>
+      <c r="T58" s="16" t="inlineStr"/>
+      <c r="U58" s="16" t="inlineStr"/>
+      <c r="V58" s="16" t="inlineStr"/>
+      <c r="W58" s="16" t="inlineStr"/>
+      <c r="X58" s="16" t="inlineStr"/>
+      <c r="Y58" s="16" t="inlineStr"/>
+      <c r="Z58" s="16" t="inlineStr"/>
+      <c r="AA58" s="16" t="inlineStr"/>
+      <c r="AB58" s="16" t="inlineStr"/>
+      <c r="AC58" s="16" t="inlineStr"/>
+      <c r="AD58" s="16" t="inlineStr"/>
+      <c r="AE58" s="16" t="inlineStr"/>
+      <c r="AF58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>ITM-057</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>Surgery</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>What is the management of atypical ductal hyperplasia of the breast?</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>The management of atypical ductal hyperplasia (ADH) involves three key pillars: **surgical excision** (standard of care when diagnosed on core needle biopsy, with emerging data supporting observation in select low-risk cases), **risk-reducing endocrine therapy** (strongly recommended), and **enhanced surveillance**.
 **1. Surgical Excision After Core Needle Biopsy**
@@ -6369,7 +6407,7 @@
 Would you like to explore the specific criteria used to identify low-risk ADH patients who may safely forgo surgical excision?</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="15" t="inlineStr">
         <is>
           <t>### Management of Atypical Ductal Hyperplasia (ADH) of the Breast
 Atypical ductal hyperplasia is a high-risk proliferative breast lesion that serves dual roles: it is both a **risk marker** for future breast cancer and a **non-obligate precursor** lesion. ADH is considered a non-obligate precursor and a risk factor for invasive cancer. Its management is shaped largely by its close relationship with ductal carcinoma in situ (DCIS). Atypical ductal hyperplasia is a non-malignant proliferative lesion that shares a number of features with ductal carcinoma in situ and is recognized as a risk marker for developing breast cancer, even in the contralateral breast.
@@ -6406,51 +6444,51 @@
 This information is educational and not a substitute for individualized advice from a treating physician or breast specialist.</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr"/>
-      <c r="G59" s="13" t="inlineStr"/>
-      <c r="H59" s="13" t="inlineStr"/>
-      <c r="I59" s="13" t="inlineStr"/>
-      <c r="J59" s="13" t="inlineStr"/>
-      <c r="K59" s="13" t="inlineStr"/>
-      <c r="L59" s="13" t="inlineStr"/>
-      <c r="M59" s="13" t="inlineStr"/>
-      <c r="N59" s="13" t="inlineStr"/>
-      <c r="O59" s="13" t="inlineStr"/>
-      <c r="P59" s="13" t="inlineStr"/>
-      <c r="Q59" s="13" t="inlineStr"/>
-      <c r="R59" s="13" t="inlineStr"/>
-      <c r="S59" s="13" t="inlineStr"/>
-      <c r="T59" s="13" t="inlineStr"/>
-      <c r="U59" s="13" t="inlineStr"/>
-      <c r="V59" s="13" t="inlineStr"/>
-      <c r="W59" s="13" t="inlineStr"/>
-      <c r="X59" s="13" t="inlineStr"/>
-      <c r="Y59" s="13" t="inlineStr"/>
-      <c r="Z59" s="13" t="inlineStr"/>
-      <c r="AA59" s="13" t="inlineStr"/>
-      <c r="AB59" s="13" t="inlineStr"/>
-      <c r="AC59" s="13" t="inlineStr"/>
-      <c r="AD59" s="13" t="inlineStr"/>
-      <c r="AE59" s="13" t="inlineStr"/>
-      <c r="AF59" s="14" t="inlineStr"/>
+      <c r="F59" s="16" t="inlineStr"/>
+      <c r="G59" s="16" t="inlineStr"/>
+      <c r="H59" s="16" t="inlineStr"/>
+      <c r="I59" s="16" t="inlineStr"/>
+      <c r="J59" s="16" t="inlineStr"/>
+      <c r="K59" s="16" t="inlineStr"/>
+      <c r="L59" s="16" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr"/>
+      <c r="O59" s="16" t="inlineStr"/>
+      <c r="P59" s="16" t="inlineStr"/>
+      <c r="Q59" s="16" t="inlineStr"/>
+      <c r="R59" s="16" t="inlineStr"/>
+      <c r="S59" s="16" t="inlineStr"/>
+      <c r="T59" s="16" t="inlineStr"/>
+      <c r="U59" s="16" t="inlineStr"/>
+      <c r="V59" s="16" t="inlineStr"/>
+      <c r="W59" s="16" t="inlineStr"/>
+      <c r="X59" s="16" t="inlineStr"/>
+      <c r="Y59" s="16" t="inlineStr"/>
+      <c r="Z59" s="16" t="inlineStr"/>
+      <c r="AA59" s="16" t="inlineStr"/>
+      <c r="AB59" s="16" t="inlineStr"/>
+      <c r="AC59" s="16" t="inlineStr"/>
+      <c r="AD59" s="16" t="inlineStr"/>
+      <c r="AE59" s="16" t="inlineStr"/>
+      <c r="AF59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>ITM-058</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>What is the clinical significance of a stable 5 mm arterially enhancing hepatic lesion in a patient with a history of metastatic pancreatic neuroendocrine tumor?</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>A **stable 5 mm arterially enhancing liver lesion** in someone with a history of **metastatic pancreatic neuroendocrine tumor (pNET)** is usually considered **clinically important but not automatically alarming**.
 **What it may mean:**
@@ -6464,7 +6502,7 @@
 So, in plain terms: **it is worth following because of the pNET history, but if it has remained stable, especially over serial scans, it is less likely to represent aggressive or clinically meaningful progression.**</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
         <is>
           <t>A **stable 5 mm arterially enhancing hepatic lesion** in a patient with known metastatic pancreatic neuroendocrine tumor (pNET) is **highly suspicious for a small hepatic metastasis**, though it falls below the threshold for reliable characterization by most imaging modalities and cannot be definitively confirmed as metastatic disease on imaging alone.
 **Why metastasis is the leading concern**
@@ -6487,51 +6525,51 @@
 Would you like to explore the role of SSTR-PET/CT versus hepatobiliary-phase MRI in detecting sub-centimeter neuroendocrine liver metastases and how each modality might influence treatment decisions?</t>
         </is>
       </c>
-      <c r="F60" s="13" t="inlineStr"/>
-      <c r="G60" s="13" t="inlineStr"/>
-      <c r="H60" s="13" t="inlineStr"/>
-      <c r="I60" s="13" t="inlineStr"/>
-      <c r="J60" s="13" t="inlineStr"/>
-      <c r="K60" s="13" t="inlineStr"/>
-      <c r="L60" s="13" t="inlineStr"/>
-      <c r="M60" s="13" t="inlineStr"/>
-      <c r="N60" s="13" t="inlineStr"/>
-      <c r="O60" s="13" t="inlineStr"/>
-      <c r="P60" s="13" t="inlineStr"/>
-      <c r="Q60" s="13" t="inlineStr"/>
-      <c r="R60" s="13" t="inlineStr"/>
-      <c r="S60" s="13" t="inlineStr"/>
-      <c r="T60" s="13" t="inlineStr"/>
-      <c r="U60" s="13" t="inlineStr"/>
-      <c r="V60" s="13" t="inlineStr"/>
-      <c r="W60" s="13" t="inlineStr"/>
-      <c r="X60" s="13" t="inlineStr"/>
-      <c r="Y60" s="13" t="inlineStr"/>
-      <c r="Z60" s="13" t="inlineStr"/>
-      <c r="AA60" s="13" t="inlineStr"/>
-      <c r="AB60" s="13" t="inlineStr"/>
-      <c r="AC60" s="13" t="inlineStr"/>
-      <c r="AD60" s="13" t="inlineStr"/>
-      <c r="AE60" s="13" t="inlineStr"/>
-      <c r="AF60" s="14" t="inlineStr"/>
+      <c r="F60" s="16" t="inlineStr"/>
+      <c r="G60" s="16" t="inlineStr"/>
+      <c r="H60" s="16" t="inlineStr"/>
+      <c r="I60" s="16" t="inlineStr"/>
+      <c r="J60" s="16" t="inlineStr"/>
+      <c r="K60" s="16" t="inlineStr"/>
+      <c r="L60" s="16" t="inlineStr"/>
+      <c r="M60" s="16" t="inlineStr"/>
+      <c r="N60" s="16" t="inlineStr"/>
+      <c r="O60" s="16" t="inlineStr"/>
+      <c r="P60" s="16" t="inlineStr"/>
+      <c r="Q60" s="16" t="inlineStr"/>
+      <c r="R60" s="16" t="inlineStr"/>
+      <c r="S60" s="16" t="inlineStr"/>
+      <c r="T60" s="16" t="inlineStr"/>
+      <c r="U60" s="16" t="inlineStr"/>
+      <c r="V60" s="16" t="inlineStr"/>
+      <c r="W60" s="16" t="inlineStr"/>
+      <c r="X60" s="16" t="inlineStr"/>
+      <c r="Y60" s="16" t="inlineStr"/>
+      <c r="Z60" s="16" t="inlineStr"/>
+      <c r="AA60" s="16" t="inlineStr"/>
+      <c r="AB60" s="16" t="inlineStr"/>
+      <c r="AC60" s="16" t="inlineStr"/>
+      <c r="AD60" s="16" t="inlineStr"/>
+      <c r="AE60" s="16" t="inlineStr"/>
+      <c r="AF60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>ITM-059</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>Family Medicine</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>Should you take magnesium daily or only as needed for muscle cramps?</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>**Short answer:** For typical muscle cramps, magnesium is usually **not something to take “as needed” for immediate relief**—it doesn’t work like a fast-acting cramp medicine. If you’re low in magnesium or your diet is low, it’s more logical to improve intake **daily** through food, or use a **daily low-dose supplement** after checking safety. But evidence that magnesium supplements prevent ordinary leg cramps is **weak**, especially in older adults. A Cochrane review found magnesium is unlikely to meaningfully reduce cramp frequency or severity in older adults, and evidence is uncertain in pregnancy and exercise-related cramps.
 **A practical approach:**
@@ -6542,7 +6580,7 @@
 Also, recurrent cramps often have non-magnesium causes: dehydration, overuse, electrolyte issues, nerve problems, poor circulation, medication side effects, or low potassium/calcium. Seek medical advice promptly if cramps are severe, frequent, one-sided with swelling/redness, associated with weakness/numbness, or started after a new medication.</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>The best available evidence indicates that **magnesium supplementation is unlikely to provide clinically meaningful prophylaxis for idiopathic muscle cramps in older adults**, regardless of whether it is taken daily or as needed. Neither daily dosing nor PRN use has strong support for this indication.
 **What the evidence shows:**
@@ -6557,51 +6595,51 @@
 Would you like to explore evidence-based alternatives for nocturnal leg cramp management, including stretching protocols and other pharmacologic options?</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr"/>
-      <c r="G61" s="13" t="inlineStr"/>
-      <c r="H61" s="13" t="inlineStr"/>
-      <c r="I61" s="13" t="inlineStr"/>
-      <c r="J61" s="13" t="inlineStr"/>
-      <c r="K61" s="13" t="inlineStr"/>
-      <c r="L61" s="13" t="inlineStr"/>
-      <c r="M61" s="13" t="inlineStr"/>
-      <c r="N61" s="13" t="inlineStr"/>
-      <c r="O61" s="13" t="inlineStr"/>
-      <c r="P61" s="13" t="inlineStr"/>
-      <c r="Q61" s="13" t="inlineStr"/>
-      <c r="R61" s="13" t="inlineStr"/>
-      <c r="S61" s="13" t="inlineStr"/>
-      <c r="T61" s="13" t="inlineStr"/>
-      <c r="U61" s="13" t="inlineStr"/>
-      <c r="V61" s="13" t="inlineStr"/>
-      <c r="W61" s="13" t="inlineStr"/>
-      <c r="X61" s="13" t="inlineStr"/>
-      <c r="Y61" s="13" t="inlineStr"/>
-      <c r="Z61" s="13" t="inlineStr"/>
-      <c r="AA61" s="13" t="inlineStr"/>
-      <c r="AB61" s="13" t="inlineStr"/>
-      <c r="AC61" s="13" t="inlineStr"/>
-      <c r="AD61" s="13" t="inlineStr"/>
-      <c r="AE61" s="13" t="inlineStr"/>
-      <c r="AF61" s="14" t="inlineStr"/>
+      <c r="F61" s="16" t="inlineStr"/>
+      <c r="G61" s="16" t="inlineStr"/>
+      <c r="H61" s="16" t="inlineStr"/>
+      <c r="I61" s="16" t="inlineStr"/>
+      <c r="J61" s="16" t="inlineStr"/>
+      <c r="K61" s="16" t="inlineStr"/>
+      <c r="L61" s="16" t="inlineStr"/>
+      <c r="M61" s="16" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr"/>
+      <c r="O61" s="16" t="inlineStr"/>
+      <c r="P61" s="16" t="inlineStr"/>
+      <c r="Q61" s="16" t="inlineStr"/>
+      <c r="R61" s="16" t="inlineStr"/>
+      <c r="S61" s="16" t="inlineStr"/>
+      <c r="T61" s="16" t="inlineStr"/>
+      <c r="U61" s="16" t="inlineStr"/>
+      <c r="V61" s="16" t="inlineStr"/>
+      <c r="W61" s="16" t="inlineStr"/>
+      <c r="X61" s="16" t="inlineStr"/>
+      <c r="Y61" s="16" t="inlineStr"/>
+      <c r="Z61" s="16" t="inlineStr"/>
+      <c r="AA61" s="16" t="inlineStr"/>
+      <c r="AB61" s="16" t="inlineStr"/>
+      <c r="AC61" s="16" t="inlineStr"/>
+      <c r="AD61" s="16" t="inlineStr"/>
+      <c r="AE61" s="16" t="inlineStr"/>
+      <c r="AF61" s="17" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>ITM-060</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>Endocrinology</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>Should Strensiq be considered appropriate therapy in a postmenopausal woman diagnosed with hypophosphatasia who also has concurrent osteoporosis?</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>Strensiq (asfotase alfa) may be considered appropriate therapy in this patient, but several important nuances must be addressed. The **FDA-approved indication for asfotase alfa is limited to perinatal/infantile- and juvenile-onset [HPP](https://www.openevidence.com/rare-disease/hypophosphatasia)** — it is not approved for adult-onset HPP. However, growing real-world evidence and observational data support its efficacy in adults regardless of age of onset, and it is used off-label in adult-onset HPP in clinical practice. The concurrent diagnosis of osteoporosis also raises critical treatment considerations, as **bisphosphonates and denosumab are contraindicated in HPP**.
 **Regulatory and Labeling Considerations**
@@ -6619,7 +6657,7 @@
 Would you like to explore the evidence for teriparatide as an adjunctive therapy for osteomalacia and fracture management in [adult hypophosphatasia](https://www.openevidence.com/rare-disease/adult-hypophosphatasia)?</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr">
         <is>
           <t>**Short answer:** **Strensiq (asfotase alfa) can be considered in a postmenopausal woman with hypophosphatasia (HPP), but only if the HPP itself is an appropriate indication—especially perinatal/infantile- or juvenile-onset HPP with clinically meaningful disease.** It should **not** be viewed as standard therapy for ordinary postmenopausal osteoporosis or for a low DXA T-score alone.
 In the U.S., Strensiq is FDA-indicated for **perinatal/infantile- and juvenile-onset HPP**, not simply “adult-onset HPP” or postmenopausal osteoporosis. The label’s mechanism also frames HPP as a mineralization disorder causing osteomalacia after growth plates close, which is different from typical postmenopausal osteoporosis.
@@ -6635,51 +6673,51 @@
 **Bottom line:** In a postmenopausal woman with confirmed HPP and concurrent osteoporosis, Strensiq should be **considered as HPP-directed enzyme replacement therapy**, not as routine osteoporosis treatment. The decision should be individualized by a metabolic bone expert, with careful confirmation of HPP severity/onset, fracture pattern, and avoidance of therapies—especially bisphosphonates/denosumab—that may be harmful in HPP.</t>
         </is>
       </c>
-      <c r="F62" s="13" t="inlineStr"/>
-      <c r="G62" s="13" t="inlineStr"/>
-      <c r="H62" s="13" t="inlineStr"/>
-      <c r="I62" s="13" t="inlineStr"/>
-      <c r="J62" s="13" t="inlineStr"/>
-      <c r="K62" s="13" t="inlineStr"/>
-      <c r="L62" s="13" t="inlineStr"/>
-      <c r="M62" s="13" t="inlineStr"/>
-      <c r="N62" s="13" t="inlineStr"/>
-      <c r="O62" s="13" t="inlineStr"/>
-      <c r="P62" s="13" t="inlineStr"/>
-      <c r="Q62" s="13" t="inlineStr"/>
-      <c r="R62" s="13" t="inlineStr"/>
-      <c r="S62" s="13" t="inlineStr"/>
-      <c r="T62" s="13" t="inlineStr"/>
-      <c r="U62" s="13" t="inlineStr"/>
-      <c r="V62" s="13" t="inlineStr"/>
-      <c r="W62" s="13" t="inlineStr"/>
-      <c r="X62" s="13" t="inlineStr"/>
-      <c r="Y62" s="13" t="inlineStr"/>
-      <c r="Z62" s="13" t="inlineStr"/>
-      <c r="AA62" s="13" t="inlineStr"/>
-      <c r="AB62" s="13" t="inlineStr"/>
-      <c r="AC62" s="13" t="inlineStr"/>
-      <c r="AD62" s="13" t="inlineStr"/>
-      <c r="AE62" s="13" t="inlineStr"/>
-      <c r="AF62" s="14" t="inlineStr"/>
+      <c r="F62" s="16" t="inlineStr"/>
+      <c r="G62" s="16" t="inlineStr"/>
+      <c r="H62" s="16" t="inlineStr"/>
+      <c r="I62" s="16" t="inlineStr"/>
+      <c r="J62" s="16" t="inlineStr"/>
+      <c r="K62" s="16" t="inlineStr"/>
+      <c r="L62" s="16" t="inlineStr"/>
+      <c r="M62" s="16" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr"/>
+      <c r="O62" s="16" t="inlineStr"/>
+      <c r="P62" s="16" t="inlineStr"/>
+      <c r="Q62" s="16" t="inlineStr"/>
+      <c r="R62" s="16" t="inlineStr"/>
+      <c r="S62" s="16" t="inlineStr"/>
+      <c r="T62" s="16" t="inlineStr"/>
+      <c r="U62" s="16" t="inlineStr"/>
+      <c r="V62" s="16" t="inlineStr"/>
+      <c r="W62" s="16" t="inlineStr"/>
+      <c r="X62" s="16" t="inlineStr"/>
+      <c r="Y62" s="16" t="inlineStr"/>
+      <c r="Z62" s="16" t="inlineStr"/>
+      <c r="AA62" s="16" t="inlineStr"/>
+      <c r="AB62" s="16" t="inlineStr"/>
+      <c r="AC62" s="16" t="inlineStr"/>
+      <c r="AD62" s="16" t="inlineStr"/>
+      <c r="AE62" s="16" t="inlineStr"/>
+      <c r="AF62" s="17" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>ITM-061</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>What is the most likely diagnosis in a 17-year-old male presenting with pallor, fatigue, 11-pound weight loss, hemoglobin of 9, elevated bilirubin of 1.7, and LDH of 264 with an otherwise normal metabolic panel?</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>The combination of **pallor, fatigue, weight loss, anemia (Hb 9), elevated bilirubin (1.7), and elevated LDH (264)** in a 17-year-old male is most consistent with a **hemolytic anemia**, as the elevated unconjugated bilirubin and LDH are hallmark markers of red blood cell destruction. However, **hematologic malignancy (particularly [acute lymphoblastic leukemia](https://www.openevidence.com/rare-disease/acute-lymphoblastic-leukemia))** must be excluded given the significant weight loss and age group.
 **Most Likely: Hemolytic Anemia**
@@ -6707,7 +6745,7 @@
 Do you have the MCV, WBC with differential, platelet count, or reticulocyte count for this patient? That information would significantly narrow the differential.</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
         <is>
           <t>This clinical picture most strongly suggests **hemolytic anemia**, with **autoimmune hemolytic anemia (AIHA)** being the most likely specific diagnosis to consider first.
 ### Why hemolysis?
@@ -6731,51 +6769,51 @@
 *This is general medical information and not a substitute for evaluation by a physician. A real patient with these findings needs prompt clinical workup.*</t>
         </is>
       </c>
-      <c r="F63" s="13" t="inlineStr"/>
-      <c r="G63" s="13" t="inlineStr"/>
-      <c r="H63" s="13" t="inlineStr"/>
-      <c r="I63" s="13" t="inlineStr"/>
-      <c r="J63" s="13" t="inlineStr"/>
-      <c r="K63" s="13" t="inlineStr"/>
-      <c r="L63" s="13" t="inlineStr"/>
-      <c r="M63" s="13" t="inlineStr"/>
-      <c r="N63" s="13" t="inlineStr"/>
-      <c r="O63" s="13" t="inlineStr"/>
-      <c r="P63" s="13" t="inlineStr"/>
-      <c r="Q63" s="13" t="inlineStr"/>
-      <c r="R63" s="13" t="inlineStr"/>
-      <c r="S63" s="13" t="inlineStr"/>
-      <c r="T63" s="13" t="inlineStr"/>
-      <c r="U63" s="13" t="inlineStr"/>
-      <c r="V63" s="13" t="inlineStr"/>
-      <c r="W63" s="13" t="inlineStr"/>
-      <c r="X63" s="13" t="inlineStr"/>
-      <c r="Y63" s="13" t="inlineStr"/>
-      <c r="Z63" s="13" t="inlineStr"/>
-      <c r="AA63" s="13" t="inlineStr"/>
-      <c r="AB63" s="13" t="inlineStr"/>
-      <c r="AC63" s="13" t="inlineStr"/>
-      <c r="AD63" s="13" t="inlineStr"/>
-      <c r="AE63" s="13" t="inlineStr"/>
-      <c r="AF63" s="14" t="inlineStr"/>
+      <c r="F63" s="16" t="inlineStr"/>
+      <c r="G63" s="16" t="inlineStr"/>
+      <c r="H63" s="16" t="inlineStr"/>
+      <c r="I63" s="16" t="inlineStr"/>
+      <c r="J63" s="16" t="inlineStr"/>
+      <c r="K63" s="16" t="inlineStr"/>
+      <c r="L63" s="16" t="inlineStr"/>
+      <c r="M63" s="16" t="inlineStr"/>
+      <c r="N63" s="16" t="inlineStr"/>
+      <c r="O63" s="16" t="inlineStr"/>
+      <c r="P63" s="16" t="inlineStr"/>
+      <c r="Q63" s="16" t="inlineStr"/>
+      <c r="R63" s="16" t="inlineStr"/>
+      <c r="S63" s="16" t="inlineStr"/>
+      <c r="T63" s="16" t="inlineStr"/>
+      <c r="U63" s="16" t="inlineStr"/>
+      <c r="V63" s="16" t="inlineStr"/>
+      <c r="W63" s="16" t="inlineStr"/>
+      <c r="X63" s="16" t="inlineStr"/>
+      <c r="Y63" s="16" t="inlineStr"/>
+      <c r="Z63" s="16" t="inlineStr"/>
+      <c r="AA63" s="16" t="inlineStr"/>
+      <c r="AB63" s="16" t="inlineStr"/>
+      <c r="AC63" s="16" t="inlineStr"/>
+      <c r="AD63" s="16" t="inlineStr"/>
+      <c r="AE63" s="16" t="inlineStr"/>
+      <c r="AF63" s="17" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>ITM-062</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>Does right bundle branch block render an ECG non-diagnostic for myocardial ischemia?</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>### Practice Guideline
 The **ACC/AHA Fourth Universal Definition of Myocardial Infarction (2018)** and the **AHA/ACCF/HRS scientific statement** both affirm that **standard ST-segment criteria for diagnosing acute ischemia/infarction are not significantly affected by RBBB**, in contrast to LBBB, which produces more pronounced secondary ST-T wave changes that obscure ischemic findings.
@@ -6800,7 +6838,7 @@
 Writing Committee, Kontos MC, de Lemos JA, et al. 2022 ACC Expert Consensus Decision Pathway on the Evaluation and Disposition of Acute Chest Pain In the Emergency Department: A Report of the American College of Cardiology Solution Set Oversight Committee. Journal of the American College of Cardiology. 2022;80(20):1925-1960. doi:10.1016/j.jacc.2022.08.750.</t>
         </is>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>**No, a right bundle branch block (RBBB) does not render an electrocardiogram (ECG) non-diagnostic for myocardial ischemia or infarction.**
 While a left bundle branch block (LBBB) heavily distorts both the early depolarization and the repolarization phases of the heart—traditionally making the ECG non-diagnostic for acute ischemia without special rules like the Sgarbossa criteria—an RBBB behaves differently.
@@ -6817,51 +6855,51 @@
 Historically, only new LBBB was treated as a STEMI equivalent. However, modern cardiology guidelines (such as those from the AHA/ACC and ESC) emphasize that a **new or presumed-new RBBB** in a patient with acute chest pain is a very high-risk finding. It often indicates a massive acute myocardial infarction (such as a proximal LAD occlusion shutting off blood supply to the right bundle branch) and is frequently associated with cardiogenic shock and higher mortality rates. Patients presenting with ischemic symptoms and a new RBBB are often rushed directly to the cardiac catheterization lab.</t>
         </is>
       </c>
-      <c r="F64" s="13" t="inlineStr"/>
-      <c r="G64" s="13" t="inlineStr"/>
-      <c r="H64" s="13" t="inlineStr"/>
-      <c r="I64" s="13" t="inlineStr"/>
-      <c r="J64" s="13" t="inlineStr"/>
-      <c r="K64" s="13" t="inlineStr"/>
-      <c r="L64" s="13" t="inlineStr"/>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="13" t="inlineStr"/>
-      <c r="O64" s="13" t="inlineStr"/>
-      <c r="P64" s="13" t="inlineStr"/>
-      <c r="Q64" s="13" t="inlineStr"/>
-      <c r="R64" s="13" t="inlineStr"/>
-      <c r="S64" s="13" t="inlineStr"/>
-      <c r="T64" s="13" t="inlineStr"/>
-      <c r="U64" s="13" t="inlineStr"/>
-      <c r="V64" s="13" t="inlineStr"/>
-      <c r="W64" s="13" t="inlineStr"/>
-      <c r="X64" s="13" t="inlineStr"/>
-      <c r="Y64" s="13" t="inlineStr"/>
-      <c r="Z64" s="13" t="inlineStr"/>
-      <c r="AA64" s="13" t="inlineStr"/>
-      <c r="AB64" s="13" t="inlineStr"/>
-      <c r="AC64" s="13" t="inlineStr"/>
-      <c r="AD64" s="13" t="inlineStr"/>
-      <c r="AE64" s="13" t="inlineStr"/>
-      <c r="AF64" s="14" t="inlineStr"/>
+      <c r="F64" s="16" t="inlineStr"/>
+      <c r="G64" s="16" t="inlineStr"/>
+      <c r="H64" s="16" t="inlineStr"/>
+      <c r="I64" s="16" t="inlineStr"/>
+      <c r="J64" s="16" t="inlineStr"/>
+      <c r="K64" s="16" t="inlineStr"/>
+      <c r="L64" s="16" t="inlineStr"/>
+      <c r="M64" s="16" t="inlineStr"/>
+      <c r="N64" s="16" t="inlineStr"/>
+      <c r="O64" s="16" t="inlineStr"/>
+      <c r="P64" s="16" t="inlineStr"/>
+      <c r="Q64" s="16" t="inlineStr"/>
+      <c r="R64" s="16" t="inlineStr"/>
+      <c r="S64" s="16" t="inlineStr"/>
+      <c r="T64" s="16" t="inlineStr"/>
+      <c r="U64" s="16" t="inlineStr"/>
+      <c r="V64" s="16" t="inlineStr"/>
+      <c r="W64" s="16" t="inlineStr"/>
+      <c r="X64" s="16" t="inlineStr"/>
+      <c r="Y64" s="16" t="inlineStr"/>
+      <c r="Z64" s="16" t="inlineStr"/>
+      <c r="AA64" s="16" t="inlineStr"/>
+      <c r="AB64" s="16" t="inlineStr"/>
+      <c r="AC64" s="16" t="inlineStr"/>
+      <c r="AD64" s="16" t="inlineStr"/>
+      <c r="AE64" s="16" t="inlineStr"/>
+      <c r="AF64" s="17" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>ITM-063</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Rheumatology</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>What are the differences between tacrolimus and JAK inhibitors in the management of MDA-5 associated interstitial lung disease?</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>Both **tacrolimus** (a calcineurin inhibitor) and **JAK inhibitors** (primarily tofacitinib) are key immunosuppressive agents used in MDA-5-associated ILD, but they differ in mechanism, efficacy data, guideline positioning, and clinical context. Emerging evidence suggests **tofacitinib may offer a survival advantage over tacrolimus**, though both remain important components of treatment regimens.
 **Mechanism of Action**
@@ -6883,7 +6921,7 @@
 Would you like to explore the specific dosing protocols and monitoring strategies for tofacitinib versus tacrolimus in MDA-5 ILD, or the role of combination JAK-CNI regimens in refractory cases?</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="15" t="inlineStr">
         <is>
           <t>The management of anti-melanoma differentiation-associated gene 5 (anti-MDA5) positive dermatomyositis is notoriously challenging due to its strong association with rapidly progressive interstitial lung disease (RP-ILD), a condition with a high mortality rate.
 Historically, **tacrolimus** (a calcineurin inhibitor or CNI) has been a cornerstone of therapy. However, **Janus kinase (JAK) inhibitors** (such as tofacitinib and baricitinib) have emerged as highly effective, targeted alternatives. Recent multi-center cohort studies and clinical trials have directly compared the two.
@@ -6911,51 +6949,51 @@
 While **tacrolimus** is a traditional T-cell suppressant long used in combination therapies for myositis, **JAK inhibitors** offer a targeted mechanism that directly neutralizes the interferon-driven cytokine storm inherent to anti-MDA5 disease. Consequently, JAK inhibitors have demonstrated a statistically significant survival advantage over tacrolimus, especially when administered early in the disease course, though both therapies require intense monitoring for life-threatening opportunistic infections.</t>
         </is>
       </c>
-      <c r="F65" s="13" t="inlineStr"/>
-      <c r="G65" s="13" t="inlineStr"/>
-      <c r="H65" s="13" t="inlineStr"/>
-      <c r="I65" s="13" t="inlineStr"/>
-      <c r="J65" s="13" t="inlineStr"/>
-      <c r="K65" s="13" t="inlineStr"/>
-      <c r="L65" s="13" t="inlineStr"/>
-      <c r="M65" s="13" t="inlineStr"/>
-      <c r="N65" s="13" t="inlineStr"/>
-      <c r="O65" s="13" t="inlineStr"/>
-      <c r="P65" s="13" t="inlineStr"/>
-      <c r="Q65" s="13" t="inlineStr"/>
-      <c r="R65" s="13" t="inlineStr"/>
-      <c r="S65" s="13" t="inlineStr"/>
-      <c r="T65" s="13" t="inlineStr"/>
-      <c r="U65" s="13" t="inlineStr"/>
-      <c r="V65" s="13" t="inlineStr"/>
-      <c r="W65" s="13" t="inlineStr"/>
-      <c r="X65" s="13" t="inlineStr"/>
-      <c r="Y65" s="13" t="inlineStr"/>
-      <c r="Z65" s="13" t="inlineStr"/>
-      <c r="AA65" s="13" t="inlineStr"/>
-      <c r="AB65" s="13" t="inlineStr"/>
-      <c r="AC65" s="13" t="inlineStr"/>
-      <c r="AD65" s="13" t="inlineStr"/>
-      <c r="AE65" s="13" t="inlineStr"/>
-      <c r="AF65" s="14" t="inlineStr"/>
+      <c r="F65" s="16" t="inlineStr"/>
+      <c r="G65" s="16" t="inlineStr"/>
+      <c r="H65" s="16" t="inlineStr"/>
+      <c r="I65" s="16" t="inlineStr"/>
+      <c r="J65" s="16" t="inlineStr"/>
+      <c r="K65" s="16" t="inlineStr"/>
+      <c r="L65" s="16" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr"/>
+      <c r="O65" s="16" t="inlineStr"/>
+      <c r="P65" s="16" t="inlineStr"/>
+      <c r="Q65" s="16" t="inlineStr"/>
+      <c r="R65" s="16" t="inlineStr"/>
+      <c r="S65" s="16" t="inlineStr"/>
+      <c r="T65" s="16" t="inlineStr"/>
+      <c r="U65" s="16" t="inlineStr"/>
+      <c r="V65" s="16" t="inlineStr"/>
+      <c r="W65" s="16" t="inlineStr"/>
+      <c r="X65" s="16" t="inlineStr"/>
+      <c r="Y65" s="16" t="inlineStr"/>
+      <c r="Z65" s="16" t="inlineStr"/>
+      <c r="AA65" s="16" t="inlineStr"/>
+      <c r="AB65" s="16" t="inlineStr"/>
+      <c r="AC65" s="16" t="inlineStr"/>
+      <c r="AD65" s="16" t="inlineStr"/>
+      <c r="AE65" s="16" t="inlineStr"/>
+      <c r="AF65" s="17" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>ITM-064</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>Neurology</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>If a patient with a history of stroke shows regression of existing plaque but development of new ulceration at the same arterial site on follow-up CTA, does this finding require any change in management beyond continuing aspirin therapy?</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>Yes — **new plaque ulceration at a previously symptomatic carotid site represents a high-risk vulnerable plaque feature that warrants management intensification beyond aspirin monotherapy**, even in the context of overall plaque regression. Several domains of care should be reassessed.
 **Why ulceration matters clinically**
@@ -6986,7 +7024,7 @@
 Anand SS, Eikelboom JW, Dyal L, et al. Rivaroxaban Plus Aspirin Versus Aspirin in Relation to Vascular Risk in the COMPASS Trial. Journal of the American College of Cardiology. 2019;73(25):3271-3280. doi:10.1016/j.jacc.2019.02.079.</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr">
         <is>
           <t>This is an excellent and nuanced question, because it pits two seemingly contradictory imaging findings against each other—plaque *regression* (reassuring) versus new *ulceration* (concerning). The short answer is that the development of new ulceration at a symptomatic site generally warrants more than just continued aspirin, and here's why.
 ### Why the new ulceration matters more than the regression
@@ -7013,51 +7051,51 @@
 *An important caveat: I'm an AI and this is general educational information synthesized from the literature, not individualized medical advice. The actual decision depends on the degree of stenosis, the patient's symptom timing and burden, comorbidities, and procedural risk, and should be made by the treating stroke and vascular team. Please ensure these findings are reviewed in that clinical context.*</t>
         </is>
       </c>
-      <c r="F66" s="13" t="inlineStr"/>
-      <c r="G66" s="13" t="inlineStr"/>
-      <c r="H66" s="13" t="inlineStr"/>
-      <c r="I66" s="13" t="inlineStr"/>
-      <c r="J66" s="13" t="inlineStr"/>
-      <c r="K66" s="13" t="inlineStr"/>
-      <c r="L66" s="13" t="inlineStr"/>
-      <c r="M66" s="13" t="inlineStr"/>
-      <c r="N66" s="13" t="inlineStr"/>
-      <c r="O66" s="13" t="inlineStr"/>
-      <c r="P66" s="13" t="inlineStr"/>
-      <c r="Q66" s="13" t="inlineStr"/>
-      <c r="R66" s="13" t="inlineStr"/>
-      <c r="S66" s="13" t="inlineStr"/>
-      <c r="T66" s="13" t="inlineStr"/>
-      <c r="U66" s="13" t="inlineStr"/>
-      <c r="V66" s="13" t="inlineStr"/>
-      <c r="W66" s="13" t="inlineStr"/>
-      <c r="X66" s="13" t="inlineStr"/>
-      <c r="Y66" s="13" t="inlineStr"/>
-      <c r="Z66" s="13" t="inlineStr"/>
-      <c r="AA66" s="13" t="inlineStr"/>
-      <c r="AB66" s="13" t="inlineStr"/>
-      <c r="AC66" s="13" t="inlineStr"/>
-      <c r="AD66" s="13" t="inlineStr"/>
-      <c r="AE66" s="13" t="inlineStr"/>
-      <c r="AF66" s="14" t="inlineStr"/>
+      <c r="F66" s="16" t="inlineStr"/>
+      <c r="G66" s="16" t="inlineStr"/>
+      <c r="H66" s="16" t="inlineStr"/>
+      <c r="I66" s="16" t="inlineStr"/>
+      <c r="J66" s="16" t="inlineStr"/>
+      <c r="K66" s="16" t="inlineStr"/>
+      <c r="L66" s="16" t="inlineStr"/>
+      <c r="M66" s="16" t="inlineStr"/>
+      <c r="N66" s="16" t="inlineStr"/>
+      <c r="O66" s="16" t="inlineStr"/>
+      <c r="P66" s="16" t="inlineStr"/>
+      <c r="Q66" s="16" t="inlineStr"/>
+      <c r="R66" s="16" t="inlineStr"/>
+      <c r="S66" s="16" t="inlineStr"/>
+      <c r="T66" s="16" t="inlineStr"/>
+      <c r="U66" s="16" t="inlineStr"/>
+      <c r="V66" s="16" t="inlineStr"/>
+      <c r="W66" s="16" t="inlineStr"/>
+      <c r="X66" s="16" t="inlineStr"/>
+      <c r="Y66" s="16" t="inlineStr"/>
+      <c r="Z66" s="16" t="inlineStr"/>
+      <c r="AA66" s="16" t="inlineStr"/>
+      <c r="AB66" s="16" t="inlineStr"/>
+      <c r="AC66" s="16" t="inlineStr"/>
+      <c r="AD66" s="16" t="inlineStr"/>
+      <c r="AE66" s="16" t="inlineStr"/>
+      <c r="AF66" s="17" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>ITM-065</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>Neurology</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t>If a patient with a history of stroke shows regression of existing plaque but development of new ulceration at the same arterial site on follow-up CTA, does this finding require any change in management beyond continuing aspirin therapy?</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>**Yes, the development of a new plaque ulceration requires an immediate reassessment and likely a change in management, even if the overall plaque volume has regressed.**
 While the regression of plaque volume suggests that lipid-lowering therapies (like statins) are working to reduce the overall atherosclerotic burden, the appearance of a **new ulceration** is a major warning sign. In clinical terms, a new ulceration means that the plaque's fibrous cap has ruptured, exposing the highly thrombogenic (clot-promoting) inner core of the plaque to the circulating blood.
@@ -7080,7 +7118,7 @@
 ***Disclaimer:** This information is for educational purposes and should not replace professional medical advice. A physician must evaluate the specific CTA images, the degree of stenosis, and the patient's comprehensive medical history to make definitive treatment decisions.*</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="15" t="inlineStr">
         <is>
           <t>Yes — **new plaque ulceration at a previously symptomatic carotid site represents a high-risk vulnerable plaque feature that warrants management intensification beyond aspirin monotherapy**, even in the context of overall plaque regression. Several domains of care should be reassessed.
 **Why ulceration matters clinically**
@@ -7111,51 +7149,51 @@
 Anand SS, Eikelboom JW, Dyal L, et al. Rivaroxaban Plus Aspirin Versus Aspirin in Relation to Vascular Risk in the COMPASS Trial. Journal of the American College of Cardiology. 2019;73(25):3271-3280. doi:10.1016/j.jacc.2019.02.079.</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr"/>
-      <c r="G67" s="13" t="inlineStr"/>
-      <c r="H67" s="13" t="inlineStr"/>
-      <c r="I67" s="13" t="inlineStr"/>
-      <c r="J67" s="13" t="inlineStr"/>
-      <c r="K67" s="13" t="inlineStr"/>
-      <c r="L67" s="13" t="inlineStr"/>
-      <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="13" t="inlineStr"/>
-      <c r="O67" s="13" t="inlineStr"/>
-      <c r="P67" s="13" t="inlineStr"/>
-      <c r="Q67" s="13" t="inlineStr"/>
-      <c r="R67" s="13" t="inlineStr"/>
-      <c r="S67" s="13" t="inlineStr"/>
-      <c r="T67" s="13" t="inlineStr"/>
-      <c r="U67" s="13" t="inlineStr"/>
-      <c r="V67" s="13" t="inlineStr"/>
-      <c r="W67" s="13" t="inlineStr"/>
-      <c r="X67" s="13" t="inlineStr"/>
-      <c r="Y67" s="13" t="inlineStr"/>
-      <c r="Z67" s="13" t="inlineStr"/>
-      <c r="AA67" s="13" t="inlineStr"/>
-      <c r="AB67" s="13" t="inlineStr"/>
-      <c r="AC67" s="13" t="inlineStr"/>
-      <c r="AD67" s="13" t="inlineStr"/>
-      <c r="AE67" s="13" t="inlineStr"/>
-      <c r="AF67" s="14" t="inlineStr"/>
+      <c r="F67" s="16" t="inlineStr"/>
+      <c r="G67" s="16" t="inlineStr"/>
+      <c r="H67" s="16" t="inlineStr"/>
+      <c r="I67" s="16" t="inlineStr"/>
+      <c r="J67" s="16" t="inlineStr"/>
+      <c r="K67" s="16" t="inlineStr"/>
+      <c r="L67" s="16" t="inlineStr"/>
+      <c r="M67" s="16" t="inlineStr"/>
+      <c r="N67" s="16" t="inlineStr"/>
+      <c r="O67" s="16" t="inlineStr"/>
+      <c r="P67" s="16" t="inlineStr"/>
+      <c r="Q67" s="16" t="inlineStr"/>
+      <c r="R67" s="16" t="inlineStr"/>
+      <c r="S67" s="16" t="inlineStr"/>
+      <c r="T67" s="16" t="inlineStr"/>
+      <c r="U67" s="16" t="inlineStr"/>
+      <c r="V67" s="16" t="inlineStr"/>
+      <c r="W67" s="16" t="inlineStr"/>
+      <c r="X67" s="16" t="inlineStr"/>
+      <c r="Y67" s="16" t="inlineStr"/>
+      <c r="Z67" s="16" t="inlineStr"/>
+      <c r="AA67" s="16" t="inlineStr"/>
+      <c r="AB67" s="16" t="inlineStr"/>
+      <c r="AC67" s="16" t="inlineStr"/>
+      <c r="AD67" s="16" t="inlineStr"/>
+      <c r="AE67" s="16" t="inlineStr"/>
+      <c r="AF67" s="17" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="A68" s="14" t="inlineStr">
         <is>
           <t>ITM-066</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>Neurology</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr">
         <is>
           <t>If a patient with a history of stroke shows regression of existing plaque but development of new ulceration at the same arterial site on follow-up CTA, does this finding require any change in management beyond continuing aspirin therapy?</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>Yes — **new plaque ulceration at a previously symptomatic carotid site represents a high-risk vulnerable plaque feature that warrants management intensification beyond aspirin monotherapy**, even in the context of overall plaque regression. Several domains of care should be reassessed.
 **Why ulceration matters clinically**
@@ -7186,7 +7224,7 @@
 Anand SS, Eikelboom JW, Dyal L, et al. Rivaroxaban Plus Aspirin Versus Aspirin in Relation to Vascular Risk in the COMPASS Trial. Journal of the American College of Cardiology. 2019;73(25):3271-3280. doi:10.1016/j.jacc.2019.02.079.</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>**Short answer: not automatically — but it should not be dismissed as “no change needed” without specialist review.** A new plaque ulceration on follow-up CTA is a **higher-risk plaque feature** and can be associated with ipsilateral ischemic events, even if the overall plaque burden has regressed. However, major stroke/carotid guidelines generally base major treatment changes—especially carotid endarterectomy or stenting—on **whether the lesion is symptomatic and the degree/location of stenosis**, not on ulceration alone. CTA-detected carotid plaque ulceration has been associated with ipsilateral cerebrovascular ischemia, but evidence is less definitive that ulceration alone mandates an intervention.
 Management usually depends on these key questions:
@@ -7201,51 +7239,51 @@
 So, if the patient is **clinically stable, has no new neurologic symptoms, and has no significant stenosis**, the plan may indeed be **continued single antiplatelet therapy plus aggressive vascular risk-factor management**. But if they are only on aspirin, the finding should prompt the treating neurologist/vascular specialist to confirm that secondary prevention is optimized and to decide whether additional imaging, closer follow-up, or vascular surgery consultation is warranted.</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr"/>
-      <c r="G68" s="13" t="inlineStr"/>
-      <c r="H68" s="13" t="inlineStr"/>
-      <c r="I68" s="13" t="inlineStr"/>
-      <c r="J68" s="13" t="inlineStr"/>
-      <c r="K68" s="13" t="inlineStr"/>
-      <c r="L68" s="13" t="inlineStr"/>
-      <c r="M68" s="13" t="inlineStr"/>
-      <c r="N68" s="13" t="inlineStr"/>
-      <c r="O68" s="13" t="inlineStr"/>
-      <c r="P68" s="13" t="inlineStr"/>
-      <c r="Q68" s="13" t="inlineStr"/>
-      <c r="R68" s="13" t="inlineStr"/>
-      <c r="S68" s="13" t="inlineStr"/>
-      <c r="T68" s="13" t="inlineStr"/>
-      <c r="U68" s="13" t="inlineStr"/>
-      <c r="V68" s="13" t="inlineStr"/>
-      <c r="W68" s="13" t="inlineStr"/>
-      <c r="X68" s="13" t="inlineStr"/>
-      <c r="Y68" s="13" t="inlineStr"/>
-      <c r="Z68" s="13" t="inlineStr"/>
-      <c r="AA68" s="13" t="inlineStr"/>
-      <c r="AB68" s="13" t="inlineStr"/>
-      <c r="AC68" s="13" t="inlineStr"/>
-      <c r="AD68" s="13" t="inlineStr"/>
-      <c r="AE68" s="13" t="inlineStr"/>
-      <c r="AF68" s="14" t="inlineStr"/>
+      <c r="F68" s="16" t="inlineStr"/>
+      <c r="G68" s="16" t="inlineStr"/>
+      <c r="H68" s="16" t="inlineStr"/>
+      <c r="I68" s="16" t="inlineStr"/>
+      <c r="J68" s="16" t="inlineStr"/>
+      <c r="K68" s="16" t="inlineStr"/>
+      <c r="L68" s="16" t="inlineStr"/>
+      <c r="M68" s="16" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr"/>
+      <c r="O68" s="16" t="inlineStr"/>
+      <c r="P68" s="16" t="inlineStr"/>
+      <c r="Q68" s="16" t="inlineStr"/>
+      <c r="R68" s="16" t="inlineStr"/>
+      <c r="S68" s="16" t="inlineStr"/>
+      <c r="T68" s="16" t="inlineStr"/>
+      <c r="U68" s="16" t="inlineStr"/>
+      <c r="V68" s="16" t="inlineStr"/>
+      <c r="W68" s="16" t="inlineStr"/>
+      <c r="X68" s="16" t="inlineStr"/>
+      <c r="Y68" s="16" t="inlineStr"/>
+      <c r="Z68" s="16" t="inlineStr"/>
+      <c r="AA68" s="16" t="inlineStr"/>
+      <c r="AB68" s="16" t="inlineStr"/>
+      <c r="AC68" s="16" t="inlineStr"/>
+      <c r="AD68" s="16" t="inlineStr"/>
+      <c r="AE68" s="16" t="inlineStr"/>
+      <c r="AF68" s="17" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>ITM-067</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>What is the next step in managing persistently elevated lipid levels in a patient already on maximum-dose atorvastatin?</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>**Next step:** confirm adherence/lifestyle and rule out secondary causes, then **add a non-statin LDL-lowering agent—typically ezetimibe 10 mg daily—to maximally tolerated atorvastatin** if LDL-C remains above goal.
 Why: Statins remain the foundation, but current ACC/AHA guidance recommends adding **non-statin therapy** when LDL-C is not adequately lowered with lifestyle + statin therapy; options include **ezetimibe**, **bempedoic acid**, and/or a **PCSK9 monoclonal antibody**, chosen by ASCVD risk, LDL-C level, needed LDL reduction, cost/access, and patient preference.
@@ -7253,7 +7291,7 @@
 So the board-style answer is: **Add ezetimibe**; if LDL-C remains elevated, **consider PCSK9 inhibitor or bempedoic acid** depending on risk and LDL target.</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr">
         <is>
           <t>### Practice Guideline
 The **ACC/AHA** recommends a stepwise approach to adding **nonstatin therapies** for patients with persistently elevated LDL-C on maximally tolerated statin therapy.
@@ -7280,51 +7318,51 @@
 Would you like to explore the specific LDL-C thresholds and risk-enhancing factors that define "very high risk" ASCVD and guide the intensity of nonstatin therapy escalation?</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr"/>
-      <c r="G69" s="13" t="inlineStr"/>
-      <c r="H69" s="13" t="inlineStr"/>
-      <c r="I69" s="13" t="inlineStr"/>
-      <c r="J69" s="13" t="inlineStr"/>
-      <c r="K69" s="13" t="inlineStr"/>
-      <c r="L69" s="13" t="inlineStr"/>
-      <c r="M69" s="13" t="inlineStr"/>
-      <c r="N69" s="13" t="inlineStr"/>
-      <c r="O69" s="13" t="inlineStr"/>
-      <c r="P69" s="13" t="inlineStr"/>
-      <c r="Q69" s="13" t="inlineStr"/>
-      <c r="R69" s="13" t="inlineStr"/>
-      <c r="S69" s="13" t="inlineStr"/>
-      <c r="T69" s="13" t="inlineStr"/>
-      <c r="U69" s="13" t="inlineStr"/>
-      <c r="V69" s="13" t="inlineStr"/>
-      <c r="W69" s="13" t="inlineStr"/>
-      <c r="X69" s="13" t="inlineStr"/>
-      <c r="Y69" s="13" t="inlineStr"/>
-      <c r="Z69" s="13" t="inlineStr"/>
-      <c r="AA69" s="13" t="inlineStr"/>
-      <c r="AB69" s="13" t="inlineStr"/>
-      <c r="AC69" s="13" t="inlineStr"/>
-      <c r="AD69" s="13" t="inlineStr"/>
-      <c r="AE69" s="13" t="inlineStr"/>
-      <c r="AF69" s="14" t="inlineStr"/>
+      <c r="F69" s="16" t="inlineStr"/>
+      <c r="G69" s="16" t="inlineStr"/>
+      <c r="H69" s="16" t="inlineStr"/>
+      <c r="I69" s="16" t="inlineStr"/>
+      <c r="J69" s="16" t="inlineStr"/>
+      <c r="K69" s="16" t="inlineStr"/>
+      <c r="L69" s="16" t="inlineStr"/>
+      <c r="M69" s="16" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr"/>
+      <c r="O69" s="16" t="inlineStr"/>
+      <c r="P69" s="16" t="inlineStr"/>
+      <c r="Q69" s="16" t="inlineStr"/>
+      <c r="R69" s="16" t="inlineStr"/>
+      <c r="S69" s="16" t="inlineStr"/>
+      <c r="T69" s="16" t="inlineStr"/>
+      <c r="U69" s="16" t="inlineStr"/>
+      <c r="V69" s="16" t="inlineStr"/>
+      <c r="W69" s="16" t="inlineStr"/>
+      <c r="X69" s="16" t="inlineStr"/>
+      <c r="Y69" s="16" t="inlineStr"/>
+      <c r="Z69" s="16" t="inlineStr"/>
+      <c r="AA69" s="16" t="inlineStr"/>
+      <c r="AB69" s="16" t="inlineStr"/>
+      <c r="AC69" s="16" t="inlineStr"/>
+      <c r="AD69" s="16" t="inlineStr"/>
+      <c r="AE69" s="16" t="inlineStr"/>
+      <c r="AF69" s="17" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>ITM-068</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>Hospital-Based Medicine</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>Should you adjust a patient's glargine insulin when they are made NPO?</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>**Yes, you should adjust (reduce) a patient’s glargine insulin when they are made NPO, but you should rarely discontinue it entirely.**
 Glargine is a long-acting basal insulin designed to manage baseline hepatic glucose production, not meal-time spikes. Because the patient will not be taking in calories, the risk of hypoglycemia increases; however, entirely removing basal insulin puts the patient at risk for severe hyperglycemia or Diabetic Ketoacidosis (DKA).
@@ -7344,7 +7382,7 @@
 *Disclaimer: This information reflects standard clinical guidelines (such as those from the ADA). Actual dosing should always be individualized based on the patient's renal function, baseline glycemic control, home insulin sensitivity, and specific institutional protocols.*</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr">
         <is>
           <t>**Glargine insulin should be continued but reduced by approximately 20–25% of the home dose** when a patient is made NPO, with prandial insulin held entirely. Basal insulin should never be completely withheld, particularly in patients with type 1 diabetes, as it is essential for preventing ketoacidosis and maintaining baseline glucose control.
 **Key Recommendations by Guideline Source**
@@ -7364,51 +7402,51 @@
 Would you like to explore specific perioperative insulin management protocols, including the transition from subcutaneous to intravenous insulin for major surgical procedures?</t>
         </is>
       </c>
-      <c r="F70" s="13" t="inlineStr"/>
-      <c r="G70" s="13" t="inlineStr"/>
-      <c r="H70" s="13" t="inlineStr"/>
-      <c r="I70" s="13" t="inlineStr"/>
-      <c r="J70" s="13" t="inlineStr"/>
-      <c r="K70" s="13" t="inlineStr"/>
-      <c r="L70" s="13" t="inlineStr"/>
-      <c r="M70" s="13" t="inlineStr"/>
-      <c r="N70" s="13" t="inlineStr"/>
-      <c r="O70" s="13" t="inlineStr"/>
-      <c r="P70" s="13" t="inlineStr"/>
-      <c r="Q70" s="13" t="inlineStr"/>
-      <c r="R70" s="13" t="inlineStr"/>
-      <c r="S70" s="13" t="inlineStr"/>
-      <c r="T70" s="13" t="inlineStr"/>
-      <c r="U70" s="13" t="inlineStr"/>
-      <c r="V70" s="13" t="inlineStr"/>
-      <c r="W70" s="13" t="inlineStr"/>
-      <c r="X70" s="13" t="inlineStr"/>
-      <c r="Y70" s="13" t="inlineStr"/>
-      <c r="Z70" s="13" t="inlineStr"/>
-      <c r="AA70" s="13" t="inlineStr"/>
-      <c r="AB70" s="13" t="inlineStr"/>
-      <c r="AC70" s="13" t="inlineStr"/>
-      <c r="AD70" s="13" t="inlineStr"/>
-      <c r="AE70" s="13" t="inlineStr"/>
-      <c r="AF70" s="14" t="inlineStr"/>
+      <c r="F70" s="16" t="inlineStr"/>
+      <c r="G70" s="16" t="inlineStr"/>
+      <c r="H70" s="16" t="inlineStr"/>
+      <c r="I70" s="16" t="inlineStr"/>
+      <c r="J70" s="16" t="inlineStr"/>
+      <c r="K70" s="16" t="inlineStr"/>
+      <c r="L70" s="16" t="inlineStr"/>
+      <c r="M70" s="16" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr"/>
+      <c r="O70" s="16" t="inlineStr"/>
+      <c r="P70" s="16" t="inlineStr"/>
+      <c r="Q70" s="16" t="inlineStr"/>
+      <c r="R70" s="16" t="inlineStr"/>
+      <c r="S70" s="16" t="inlineStr"/>
+      <c r="T70" s="16" t="inlineStr"/>
+      <c r="U70" s="16" t="inlineStr"/>
+      <c r="V70" s="16" t="inlineStr"/>
+      <c r="W70" s="16" t="inlineStr"/>
+      <c r="X70" s="16" t="inlineStr"/>
+      <c r="Y70" s="16" t="inlineStr"/>
+      <c r="Z70" s="16" t="inlineStr"/>
+      <c r="AA70" s="16" t="inlineStr"/>
+      <c r="AB70" s="16" t="inlineStr"/>
+      <c r="AC70" s="16" t="inlineStr"/>
+      <c r="AD70" s="16" t="inlineStr"/>
+      <c r="AE70" s="16" t="inlineStr"/>
+      <c r="AF70" s="17" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>ITM-069</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>Hospital-Based Medicine</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>Should you adjust a patient's glargine insulin when they are made NPO?</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>**Glargine insulin should be continued but reduced by approximately 20–25% of the home dose** when a patient is made NPO, with prandial insulin held entirely. Basal insulin should never be completely withheld, particularly in patients with type 1 diabetes, as it is essential for preventing ketoacidosis and maintaining baseline glucose control.
 **Key Recommendations by Guideline Source**
@@ -7428,7 +7466,7 @@
 Would you like to explore specific perioperative insulin management protocols, including the transition from subcutaneous to intravenous insulin for major surgical procedures?</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E71" s="15" t="inlineStr">
         <is>
           <t>**Yes—usually you adjust/reduce glargine when a patient is made NPO, but you generally should *not hold basal insulin entirely*.** Glargine is basal insulin, and patients—especially those with **type 1 diabetes**—need basal insulin even when not eating to prevent ketosis/DKA; ADA 2026 specifically emphasizes that basal insulin should not be held in type 1 diabetes.
 A common approach:
@@ -7440,51 +7478,51 @@
 So the short answer: **reduce glargine modestly—often to 75–80%—but don’t stop basal insulin, especially in type 1 diabetes.**</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr"/>
-      <c r="G71" s="13" t="inlineStr"/>
-      <c r="H71" s="13" t="inlineStr"/>
-      <c r="I71" s="13" t="inlineStr"/>
-      <c r="J71" s="13" t="inlineStr"/>
-      <c r="K71" s="13" t="inlineStr"/>
-      <c r="L71" s="13" t="inlineStr"/>
-      <c r="M71" s="13" t="inlineStr"/>
-      <c r="N71" s="13" t="inlineStr"/>
-      <c r="O71" s="13" t="inlineStr"/>
-      <c r="P71" s="13" t="inlineStr"/>
-      <c r="Q71" s="13" t="inlineStr"/>
-      <c r="R71" s="13" t="inlineStr"/>
-      <c r="S71" s="13" t="inlineStr"/>
-      <c r="T71" s="13" t="inlineStr"/>
-      <c r="U71" s="13" t="inlineStr"/>
-      <c r="V71" s="13" t="inlineStr"/>
-      <c r="W71" s="13" t="inlineStr"/>
-      <c r="X71" s="13" t="inlineStr"/>
-      <c r="Y71" s="13" t="inlineStr"/>
-      <c r="Z71" s="13" t="inlineStr"/>
-      <c r="AA71" s="13" t="inlineStr"/>
-      <c r="AB71" s="13" t="inlineStr"/>
-      <c r="AC71" s="13" t="inlineStr"/>
-      <c r="AD71" s="13" t="inlineStr"/>
-      <c r="AE71" s="13" t="inlineStr"/>
-      <c r="AF71" s="14" t="inlineStr"/>
+      <c r="F71" s="16" t="inlineStr"/>
+      <c r="G71" s="16" t="inlineStr"/>
+      <c r="H71" s="16" t="inlineStr"/>
+      <c r="I71" s="16" t="inlineStr"/>
+      <c r="J71" s="16" t="inlineStr"/>
+      <c r="K71" s="16" t="inlineStr"/>
+      <c r="L71" s="16" t="inlineStr"/>
+      <c r="M71" s="16" t="inlineStr"/>
+      <c r="N71" s="16" t="inlineStr"/>
+      <c r="O71" s="16" t="inlineStr"/>
+      <c r="P71" s="16" t="inlineStr"/>
+      <c r="Q71" s="16" t="inlineStr"/>
+      <c r="R71" s="16" t="inlineStr"/>
+      <c r="S71" s="16" t="inlineStr"/>
+      <c r="T71" s="16" t="inlineStr"/>
+      <c r="U71" s="16" t="inlineStr"/>
+      <c r="V71" s="16" t="inlineStr"/>
+      <c r="W71" s="16" t="inlineStr"/>
+      <c r="X71" s="16" t="inlineStr"/>
+      <c r="Y71" s="16" t="inlineStr"/>
+      <c r="Z71" s="16" t="inlineStr"/>
+      <c r="AA71" s="16" t="inlineStr"/>
+      <c r="AB71" s="16" t="inlineStr"/>
+      <c r="AC71" s="16" t="inlineStr"/>
+      <c r="AD71" s="16" t="inlineStr"/>
+      <c r="AE71" s="16" t="inlineStr"/>
+      <c r="AF71" s="17" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>ITM-070</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" s="15" t="inlineStr">
         <is>
           <t>Should we be concerned about continuing lithium in a patient with bipolar I disorder who was recently started on furosemide 40 mg for fluid retention, given that the lithium level is 0.8 and creatinine is currently normal, especially with an upcoming knee replacement surgery in a few days?</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="15" t="inlineStr">
         <is>
           <t>### Lithium + Furosemide + Upcoming Surgery: Yes, This Warrants Concern
 This is a genuinely high-risk situation that deserves careful management. There are several overlapping factors that converge to increase the risk of lithium toxicity. Let me walk through them.
@@ -7522,7 +7560,7 @@
 Would you like me to look up any current society guidelines (e.g., perioperative medication management protocols) for more specific timing recommendations?</t>
         </is>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr">
         <is>
           <t>### Drug Label
 According to the FDA-approved drug label, **diuretics — including furosemide — may reduce lithium's renal clearance and increase serum lithium concentrations** due to diuretic-induced sodium loss. The label recommends **more frequent monitoring of serum electrolytes and lithium concentrations** when these agents are co-administered, with lithium dosage reduction based on serum levels and clinical response. The furosemide label goes further, stating that **lithium generally should not be given with diuretics** because they reduce lithium's renal clearance and add a high risk of lithium toxicity. The current lithium level of 0.8 mEq/L is at the upper end of the maintenance target range (0.8–1.0 mEq/L), meaning there is limited margin before reaching supratherapeutic levels if furosemide raises the level further.
@@ -7547,51 +7585,51 @@
 Would you like to explore specific alternative analgesic strategies for postoperative pain management in this patient, given that NSAIDs should be avoided with concurrent lithium use?</t>
         </is>
       </c>
-      <c r="F72" s="13" t="inlineStr"/>
-      <c r="G72" s="13" t="inlineStr"/>
-      <c r="H72" s="13" t="inlineStr"/>
-      <c r="I72" s="13" t="inlineStr"/>
-      <c r="J72" s="13" t="inlineStr"/>
-      <c r="K72" s="13" t="inlineStr"/>
-      <c r="L72" s="13" t="inlineStr"/>
-      <c r="M72" s="13" t="inlineStr"/>
-      <c r="N72" s="13" t="inlineStr"/>
-      <c r="O72" s="13" t="inlineStr"/>
-      <c r="P72" s="13" t="inlineStr"/>
-      <c r="Q72" s="13" t="inlineStr"/>
-      <c r="R72" s="13" t="inlineStr"/>
-      <c r="S72" s="13" t="inlineStr"/>
-      <c r="T72" s="13" t="inlineStr"/>
-      <c r="U72" s="13" t="inlineStr"/>
-      <c r="V72" s="13" t="inlineStr"/>
-      <c r="W72" s="13" t="inlineStr"/>
-      <c r="X72" s="13" t="inlineStr"/>
-      <c r="Y72" s="13" t="inlineStr"/>
-      <c r="Z72" s="13" t="inlineStr"/>
-      <c r="AA72" s="13" t="inlineStr"/>
-      <c r="AB72" s="13" t="inlineStr"/>
-      <c r="AC72" s="13" t="inlineStr"/>
-      <c r="AD72" s="13" t="inlineStr"/>
-      <c r="AE72" s="13" t="inlineStr"/>
-      <c r="AF72" s="14" t="inlineStr"/>
+      <c r="F72" s="16" t="inlineStr"/>
+      <c r="G72" s="16" t="inlineStr"/>
+      <c r="H72" s="16" t="inlineStr"/>
+      <c r="I72" s="16" t="inlineStr"/>
+      <c r="J72" s="16" t="inlineStr"/>
+      <c r="K72" s="16" t="inlineStr"/>
+      <c r="L72" s="16" t="inlineStr"/>
+      <c r="M72" s="16" t="inlineStr"/>
+      <c r="N72" s="16" t="inlineStr"/>
+      <c r="O72" s="16" t="inlineStr"/>
+      <c r="P72" s="16" t="inlineStr"/>
+      <c r="Q72" s="16" t="inlineStr"/>
+      <c r="R72" s="16" t="inlineStr"/>
+      <c r="S72" s="16" t="inlineStr"/>
+      <c r="T72" s="16" t="inlineStr"/>
+      <c r="U72" s="16" t="inlineStr"/>
+      <c r="V72" s="16" t="inlineStr"/>
+      <c r="W72" s="16" t="inlineStr"/>
+      <c r="X72" s="16" t="inlineStr"/>
+      <c r="Y72" s="16" t="inlineStr"/>
+      <c r="Z72" s="16" t="inlineStr"/>
+      <c r="AA72" s="16" t="inlineStr"/>
+      <c r="AB72" s="16" t="inlineStr"/>
+      <c r="AC72" s="16" t="inlineStr"/>
+      <c r="AD72" s="16" t="inlineStr"/>
+      <c r="AE72" s="16" t="inlineStr"/>
+      <c r="AF72" s="17" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="inlineStr">
+      <c r="A73" s="14" t="inlineStr">
         <is>
           <t>ITM-071</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>Should we be concerned about continuing lithium in a patient with bipolar I disorder who was recently started on furosemide 40 mg for fluid retention, given that the lithium level is 0.8 and creatinine is currently normal, especially with an upcoming knee replacement surgery in a few days?</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>### Drug Label
 According to the FDA-approved drug label, **diuretics — including furosemide — may reduce lithium's renal clearance and increase serum lithium concentrations** due to diuretic-induced sodium loss. The label recommends **more frequent monitoring of serum electrolytes and lithium concentrations** when these agents are co-administered, with lithium dosage reduction based on serum levels and clinical response. The furosemide label goes further, stating that **lithium generally should not be given with diuretics** because they reduce lithium's renal clearance and add a high risk of lithium toxicity. The current lithium level of 0.8 mEq/L is at the upper end of the maintenance target range (0.8–1.0 mEq/L), meaning there is limited margin before reaching supratherapeutic levels if furosemide raises the level further.
@@ -7616,7 +7654,7 @@
 Would you like to explore specific alternative analgesic strategies for postoperative pain management in this patient, given that NSAIDs should be avoided with concurrent lithium use?</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="15" t="inlineStr">
         <is>
           <t>*Disclaimer: I am an AI, not a doctor. The following information is for educational purposes and should be discussed immediately with the patient’s healthcare team (psychiatrist, orthopedic surgeon, and anesthesiologist) before making any changes to their medication regimen.*
 **Yes, there should be significant concern.** While the patient currently has a normal creatinine and a therapeutic lithium level (0.8 mEq/L), the combination of starting a new diuretic and an upcoming major orthopedic surgery creates a **high-risk scenario for acute lithium toxicity.**
@@ -7639,51 +7677,51 @@
 **Next Steps:** Contact the patient's prescribing psychiatrist and the pre-operative anesthesia clinic immediately to flag the recent addition of furosemide and establish a safe, formal plan for holding and restarting lithium around the knee replacement.</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr"/>
-      <c r="G73" s="13" t="inlineStr"/>
-      <c r="H73" s="13" t="inlineStr"/>
-      <c r="I73" s="13" t="inlineStr"/>
-      <c r="J73" s="13" t="inlineStr"/>
-      <c r="K73" s="13" t="inlineStr"/>
-      <c r="L73" s="13" t="inlineStr"/>
-      <c r="M73" s="13" t="inlineStr"/>
-      <c r="N73" s="13" t="inlineStr"/>
-      <c r="O73" s="13" t="inlineStr"/>
-      <c r="P73" s="13" t="inlineStr"/>
-      <c r="Q73" s="13" t="inlineStr"/>
-      <c r="R73" s="13" t="inlineStr"/>
-      <c r="S73" s="13" t="inlineStr"/>
-      <c r="T73" s="13" t="inlineStr"/>
-      <c r="U73" s="13" t="inlineStr"/>
-      <c r="V73" s="13" t="inlineStr"/>
-      <c r="W73" s="13" t="inlineStr"/>
-      <c r="X73" s="13" t="inlineStr"/>
-      <c r="Y73" s="13" t="inlineStr"/>
-      <c r="Z73" s="13" t="inlineStr"/>
-      <c r="AA73" s="13" t="inlineStr"/>
-      <c r="AB73" s="13" t="inlineStr"/>
-      <c r="AC73" s="13" t="inlineStr"/>
-      <c r="AD73" s="13" t="inlineStr"/>
-      <c r="AE73" s="13" t="inlineStr"/>
-      <c r="AF73" s="14" t="inlineStr"/>
+      <c r="F73" s="16" t="inlineStr"/>
+      <c r="G73" s="16" t="inlineStr"/>
+      <c r="H73" s="16" t="inlineStr"/>
+      <c r="I73" s="16" t="inlineStr"/>
+      <c r="J73" s="16" t="inlineStr"/>
+      <c r="K73" s="16" t="inlineStr"/>
+      <c r="L73" s="16" t="inlineStr"/>
+      <c r="M73" s="16" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr"/>
+      <c r="O73" s="16" t="inlineStr"/>
+      <c r="P73" s="16" t="inlineStr"/>
+      <c r="Q73" s="16" t="inlineStr"/>
+      <c r="R73" s="16" t="inlineStr"/>
+      <c r="S73" s="16" t="inlineStr"/>
+      <c r="T73" s="16" t="inlineStr"/>
+      <c r="U73" s="16" t="inlineStr"/>
+      <c r="V73" s="16" t="inlineStr"/>
+      <c r="W73" s="16" t="inlineStr"/>
+      <c r="X73" s="16" t="inlineStr"/>
+      <c r="Y73" s="16" t="inlineStr"/>
+      <c r="Z73" s="16" t="inlineStr"/>
+      <c r="AA73" s="16" t="inlineStr"/>
+      <c r="AB73" s="16" t="inlineStr"/>
+      <c r="AC73" s="16" t="inlineStr"/>
+      <c r="AD73" s="16" t="inlineStr"/>
+      <c r="AE73" s="16" t="inlineStr"/>
+      <c r="AF73" s="17" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="A74" s="14" t="inlineStr">
         <is>
           <t>ITM-072</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Nephrology</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t>What is the appropriate treatment for C. difficile infection in a patient with end-stage renal disease on peritoneal dialysis?</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>The standard treatment for C. difficile infection (CDI) in a patient with ESRD on peritoneal dialysis follows the same general guidelines as for the broader population: **oral fidaxomicin 200 mg twice daily for 10 days** (preferred) or **oral vancomycin 125 mg four times daily for 10 days** for an initial non-severe or severe episode. Importantly, **no dose adjustment is required** for either agent in ESRD, as both are minimally absorbed systemically and exert their effect locally within the gut lumen.
 **Treatment by Severity**
@@ -7705,7 +7743,7 @@
 Would you like to explore the management approach when a PD patient presents with concurrent CDI and culture-negative peritonitis, including when to hold intraperitoneal antibiotics?</t>
         </is>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr">
         <is>
           <t>The treatment of *Clostridioides difficile* infection (CDI) in a patient with end-stage renal disease (ESRD) on peritoneal dialysis (PD) generally follows the same IDSA/SHEA clinical guidelines as the general population. Because the primary medications act locally within the gastrointestinal tract, **no renal dose adjustments are required** for either first-line agent.
 Here is the appropriate approach and specific considerations for this patient population:
@@ -7727,51 +7765,51 @@
 * **High Risk of Recurrence:** Patients with ESRD are considered at high risk for recurrent CDI due to frequent hospitalizations, frequent antibiotic use, and altered immunity. If the patient has a recurrence, prolonged/tapered courses of oral vancomycin or a standard course of fidaxomicin are used. **Bezlotoxumab** (a monoclonal antibody against *C. diff* toxin B) may also be considered as an adjunctive IV infusion to prevent recurrences, though it should be used with caution if the patient has a history of congestive heart failure, which is common in the ESRD population.</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr"/>
-      <c r="G74" s="13" t="inlineStr"/>
-      <c r="H74" s="13" t="inlineStr"/>
-      <c r="I74" s="13" t="inlineStr"/>
-      <c r="J74" s="13" t="inlineStr"/>
-      <c r="K74" s="13" t="inlineStr"/>
-      <c r="L74" s="13" t="inlineStr"/>
-      <c r="M74" s="13" t="inlineStr"/>
-      <c r="N74" s="13" t="inlineStr"/>
-      <c r="O74" s="13" t="inlineStr"/>
-      <c r="P74" s="13" t="inlineStr"/>
-      <c r="Q74" s="13" t="inlineStr"/>
-      <c r="R74" s="13" t="inlineStr"/>
-      <c r="S74" s="13" t="inlineStr"/>
-      <c r="T74" s="13" t="inlineStr"/>
-      <c r="U74" s="13" t="inlineStr"/>
-      <c r="V74" s="13" t="inlineStr"/>
-      <c r="W74" s="13" t="inlineStr"/>
-      <c r="X74" s="13" t="inlineStr"/>
-      <c r="Y74" s="13" t="inlineStr"/>
-      <c r="Z74" s="13" t="inlineStr"/>
-      <c r="AA74" s="13" t="inlineStr"/>
-      <c r="AB74" s="13" t="inlineStr"/>
-      <c r="AC74" s="13" t="inlineStr"/>
-      <c r="AD74" s="13" t="inlineStr"/>
-      <c r="AE74" s="13" t="inlineStr"/>
-      <c r="AF74" s="14" t="inlineStr"/>
+      <c r="F74" s="16" t="inlineStr"/>
+      <c r="G74" s="16" t="inlineStr"/>
+      <c r="H74" s="16" t="inlineStr"/>
+      <c r="I74" s="16" t="inlineStr"/>
+      <c r="J74" s="16" t="inlineStr"/>
+      <c r="K74" s="16" t="inlineStr"/>
+      <c r="L74" s="16" t="inlineStr"/>
+      <c r="M74" s="16" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr"/>
+      <c r="O74" s="16" t="inlineStr"/>
+      <c r="P74" s="16" t="inlineStr"/>
+      <c r="Q74" s="16" t="inlineStr"/>
+      <c r="R74" s="16" t="inlineStr"/>
+      <c r="S74" s="16" t="inlineStr"/>
+      <c r="T74" s="16" t="inlineStr"/>
+      <c r="U74" s="16" t="inlineStr"/>
+      <c r="V74" s="16" t="inlineStr"/>
+      <c r="W74" s="16" t="inlineStr"/>
+      <c r="X74" s="16" t="inlineStr"/>
+      <c r="Y74" s="16" t="inlineStr"/>
+      <c r="Z74" s="16" t="inlineStr"/>
+      <c r="AA74" s="16" t="inlineStr"/>
+      <c r="AB74" s="16" t="inlineStr"/>
+      <c r="AC74" s="16" t="inlineStr"/>
+      <c r="AD74" s="16" t="inlineStr"/>
+      <c r="AE74" s="16" t="inlineStr"/>
+      <c r="AF74" s="17" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>ITM-073</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>Nephrology</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C75" s="15" t="inlineStr">
         <is>
           <t>What is the appropriate treatment for C. difficile infection in a patient with end-stage renal disease on peritoneal dialysis?</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="15" t="inlineStr">
         <is>
           <t>The standard treatment for C. difficile infection (CDI) in a patient with ESRD on peritoneal dialysis follows the same general guidelines as for the broader population: **oral fidaxomicin 200 mg twice daily for 10 days** (preferred) or **oral vancomycin 125 mg four times daily for 10 days** for an initial non-severe or severe episode. Importantly, **no dose adjustment is required** for either agent in ESRD, as both are minimally absorbed systemically and exert their effect locally within the gut lumen.
 **Treatment by Severity**
@@ -7793,7 +7831,7 @@
 Would you like to explore the management approach when a PD patient presents with concurrent CDI and culture-negative peritonitis, including when to hold intraperitoneal antibiotics?</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="15" t="inlineStr">
         <is>
           <t>**Short answer:** In an **end-stage renal disease (ESRD) patient on peritoneal dialysis (PD)**, treat *C. difficile* infection the **same as other adults**, but with extra attention to volume/electrolytes, recurrence risk, and possible vancomycin absorption if fulminant colitis is present.
 ### 1) Initial, non-fulminant CDI — preferred regimen
@@ -7827,51 +7865,51 @@
 **Bottom line:** For most ESRD/PD patients with non-fulminant CDI, use **fidaxomicin 200 mg PO BID x10 days** if available; **oral vancomycin 125 mg QID x10 days** is an acceptable alternative. No renal/PD dose adjustment is needed, but fulminant disease requires high-dose enteral vancomycin + IV metronidazole and urgent specialist involvement.</t>
         </is>
       </c>
-      <c r="F75" s="13" t="inlineStr"/>
-      <c r="G75" s="13" t="inlineStr"/>
-      <c r="H75" s="13" t="inlineStr"/>
-      <c r="I75" s="13" t="inlineStr"/>
-      <c r="J75" s="13" t="inlineStr"/>
-      <c r="K75" s="13" t="inlineStr"/>
-      <c r="L75" s="13" t="inlineStr"/>
-      <c r="M75" s="13" t="inlineStr"/>
-      <c r="N75" s="13" t="inlineStr"/>
-      <c r="O75" s="13" t="inlineStr"/>
-      <c r="P75" s="13" t="inlineStr"/>
-      <c r="Q75" s="13" t="inlineStr"/>
-      <c r="R75" s="13" t="inlineStr"/>
-      <c r="S75" s="13" t="inlineStr"/>
-      <c r="T75" s="13" t="inlineStr"/>
-      <c r="U75" s="13" t="inlineStr"/>
-      <c r="V75" s="13" t="inlineStr"/>
-      <c r="W75" s="13" t="inlineStr"/>
-      <c r="X75" s="13" t="inlineStr"/>
-      <c r="Y75" s="13" t="inlineStr"/>
-      <c r="Z75" s="13" t="inlineStr"/>
-      <c r="AA75" s="13" t="inlineStr"/>
-      <c r="AB75" s="13" t="inlineStr"/>
-      <c r="AC75" s="13" t="inlineStr"/>
-      <c r="AD75" s="13" t="inlineStr"/>
-      <c r="AE75" s="13" t="inlineStr"/>
-      <c r="AF75" s="14" t="inlineStr"/>
+      <c r="F75" s="16" t="inlineStr"/>
+      <c r="G75" s="16" t="inlineStr"/>
+      <c r="H75" s="16" t="inlineStr"/>
+      <c r="I75" s="16" t="inlineStr"/>
+      <c r="J75" s="16" t="inlineStr"/>
+      <c r="K75" s="16" t="inlineStr"/>
+      <c r="L75" s="16" t="inlineStr"/>
+      <c r="M75" s="16" t="inlineStr"/>
+      <c r="N75" s="16" t="inlineStr"/>
+      <c r="O75" s="16" t="inlineStr"/>
+      <c r="P75" s="16" t="inlineStr"/>
+      <c r="Q75" s="16" t="inlineStr"/>
+      <c r="R75" s="16" t="inlineStr"/>
+      <c r="S75" s="16" t="inlineStr"/>
+      <c r="T75" s="16" t="inlineStr"/>
+      <c r="U75" s="16" t="inlineStr"/>
+      <c r="V75" s="16" t="inlineStr"/>
+      <c r="W75" s="16" t="inlineStr"/>
+      <c r="X75" s="16" t="inlineStr"/>
+      <c r="Y75" s="16" t="inlineStr"/>
+      <c r="Z75" s="16" t="inlineStr"/>
+      <c r="AA75" s="16" t="inlineStr"/>
+      <c r="AB75" s="16" t="inlineStr"/>
+      <c r="AC75" s="16" t="inlineStr"/>
+      <c r="AD75" s="16" t="inlineStr"/>
+      <c r="AE75" s="16" t="inlineStr"/>
+      <c r="AF75" s="17" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="inlineStr">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>ITM-074</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>Radiology</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C76" s="15" t="inlineStr">
         <is>
           <t>What are the most frequently examined procedural indications for musculoskeletal ultrasound?</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>The most frequently examined procedural indications for musculoskeletal ultrasound (MSKUS) span both **diagnostic** and **interventional** applications, organized broadly by anatomic region and procedure type.
 **Diagnostic Indications**
@@ -7898,7 +7936,7 @@
 Would you like to explore the evidence comparing ultrasound-guided versus landmark-based injection accuracy and outcomes for a specific joint or condition?</t>
         </is>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr">
         <is>
           <t>Musculoskeletal (MSK) ultrasound is an indispensable tool in modern medical practice. Because it offers real-time, high-resolution imaging without ionizing radiation, it is widely used to guide percutaneous (through the skin) procedures. Ultrasound guidance significantly improves the accuracy, efficacy, and safety of these interventions by allowing the clinician to visualize the needle tip, target tissue, and surrounding neurovascular structures simultaneously.
 The most frequently examined procedural indications for MSK ultrasound fall into several core categories:
@@ -7922,51 +7960,51 @@
 By standardizing these procedures, guidelines set by organizations like the American Institute of Ultrasound in Medicine (AIUM) and the American College of Emergency Physicians (ACEP) have made ultrasound-guided interventions a cornerstone of rheumatology, sports medicine, orthopedics, physical medicine and rehabilitation (PM&amp;R), and emergency medicine.</t>
         </is>
       </c>
-      <c r="F76" s="13" t="inlineStr"/>
-      <c r="G76" s="13" t="inlineStr"/>
-      <c r="H76" s="13" t="inlineStr"/>
-      <c r="I76" s="13" t="inlineStr"/>
-      <c r="J76" s="13" t="inlineStr"/>
-      <c r="K76" s="13" t="inlineStr"/>
-      <c r="L76" s="13" t="inlineStr"/>
-      <c r="M76" s="13" t="inlineStr"/>
-      <c r="N76" s="13" t="inlineStr"/>
-      <c r="O76" s="13" t="inlineStr"/>
-      <c r="P76" s="13" t="inlineStr"/>
-      <c r="Q76" s="13" t="inlineStr"/>
-      <c r="R76" s="13" t="inlineStr"/>
-      <c r="S76" s="13" t="inlineStr"/>
-      <c r="T76" s="13" t="inlineStr"/>
-      <c r="U76" s="13" t="inlineStr"/>
-      <c r="V76" s="13" t="inlineStr"/>
-      <c r="W76" s="13" t="inlineStr"/>
-      <c r="X76" s="13" t="inlineStr"/>
-      <c r="Y76" s="13" t="inlineStr"/>
-      <c r="Z76" s="13" t="inlineStr"/>
-      <c r="AA76" s="13" t="inlineStr"/>
-      <c r="AB76" s="13" t="inlineStr"/>
-      <c r="AC76" s="13" t="inlineStr"/>
-      <c r="AD76" s="13" t="inlineStr"/>
-      <c r="AE76" s="13" t="inlineStr"/>
-      <c r="AF76" s="14" t="inlineStr"/>
+      <c r="F76" s="16" t="inlineStr"/>
+      <c r="G76" s="16" t="inlineStr"/>
+      <c r="H76" s="16" t="inlineStr"/>
+      <c r="I76" s="16" t="inlineStr"/>
+      <c r="J76" s="16" t="inlineStr"/>
+      <c r="K76" s="16" t="inlineStr"/>
+      <c r="L76" s="16" t="inlineStr"/>
+      <c r="M76" s="16" t="inlineStr"/>
+      <c r="N76" s="16" t="inlineStr"/>
+      <c r="O76" s="16" t="inlineStr"/>
+      <c r="P76" s="16" t="inlineStr"/>
+      <c r="Q76" s="16" t="inlineStr"/>
+      <c r="R76" s="16" t="inlineStr"/>
+      <c r="S76" s="16" t="inlineStr"/>
+      <c r="T76" s="16" t="inlineStr"/>
+      <c r="U76" s="16" t="inlineStr"/>
+      <c r="V76" s="16" t="inlineStr"/>
+      <c r="W76" s="16" t="inlineStr"/>
+      <c r="X76" s="16" t="inlineStr"/>
+      <c r="Y76" s="16" t="inlineStr"/>
+      <c r="Z76" s="16" t="inlineStr"/>
+      <c r="AA76" s="16" t="inlineStr"/>
+      <c r="AB76" s="16" t="inlineStr"/>
+      <c r="AC76" s="16" t="inlineStr"/>
+      <c r="AD76" s="16" t="inlineStr"/>
+      <c r="AE76" s="16" t="inlineStr"/>
+      <c r="AF76" s="17" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>ITM-075</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>Otolaryngology</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>What is the evaluation approach for chronic hoarseness?</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>### Practice Guideline
 The **American Academy of Otolaryngology-Head and Neck Surgery (AAO-HNS)** recommends a systematic approach to evaluating chronic hoarseness (dysphonia) centered on **targeted history, physical examination, and laryngoscopy**.
@@ -7993,7 +8031,7 @@
 Would you like to explore the specific workup and management approach for vocal cord paralysis identified on laryngoscopy?</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
         <is>
           <t>**Chronic hoarseness/dysphonia** is generally approached as a symptom that needs **laryngeal visualization if it persists beyond ~4 weeks**, or sooner if there are concerning features. The key goal is to identify benign inflammatory/functional causes while not missing vocal fold paralysis, neurologic disease, or laryngeal cancer. AAO-HNSF guidelines recommend laryngoscopy when dysphonia does not improve within 4 weeks, and immediately if a serious cause is suspected.
 ### 1) Initial assessment: history
@@ -8060,51 +8098,51 @@
 **Chronic hoarseness = hoarseness persisting &gt;4 weeks should be evaluated with laryngoscopy.** Do a careful history and head/neck exam, look for red flags requiring urgent ENT referral, avoid empiric antibiotics/steroids/reflux therapy without indication, and let laryngoscopy guide further imaging, biopsy, voice therapy, or medical treatment.</t>
         </is>
       </c>
-      <c r="F77" s="13" t="inlineStr"/>
-      <c r="G77" s="13" t="inlineStr"/>
-      <c r="H77" s="13" t="inlineStr"/>
-      <c r="I77" s="13" t="inlineStr"/>
-      <c r="J77" s="13" t="inlineStr"/>
-      <c r="K77" s="13" t="inlineStr"/>
-      <c r="L77" s="13" t="inlineStr"/>
-      <c r="M77" s="13" t="inlineStr"/>
-      <c r="N77" s="13" t="inlineStr"/>
-      <c r="O77" s="13" t="inlineStr"/>
-      <c r="P77" s="13" t="inlineStr"/>
-      <c r="Q77" s="13" t="inlineStr"/>
-      <c r="R77" s="13" t="inlineStr"/>
-      <c r="S77" s="13" t="inlineStr"/>
-      <c r="T77" s="13" t="inlineStr"/>
-      <c r="U77" s="13" t="inlineStr"/>
-      <c r="V77" s="13" t="inlineStr"/>
-      <c r="W77" s="13" t="inlineStr"/>
-      <c r="X77" s="13" t="inlineStr"/>
-      <c r="Y77" s="13" t="inlineStr"/>
-      <c r="Z77" s="13" t="inlineStr"/>
-      <c r="AA77" s="13" t="inlineStr"/>
-      <c r="AB77" s="13" t="inlineStr"/>
-      <c r="AC77" s="13" t="inlineStr"/>
-      <c r="AD77" s="13" t="inlineStr"/>
-      <c r="AE77" s="13" t="inlineStr"/>
-      <c r="AF77" s="14" t="inlineStr"/>
+      <c r="F77" s="16" t="inlineStr"/>
+      <c r="G77" s="16" t="inlineStr"/>
+      <c r="H77" s="16" t="inlineStr"/>
+      <c r="I77" s="16" t="inlineStr"/>
+      <c r="J77" s="16" t="inlineStr"/>
+      <c r="K77" s="16" t="inlineStr"/>
+      <c r="L77" s="16" t="inlineStr"/>
+      <c r="M77" s="16" t="inlineStr"/>
+      <c r="N77" s="16" t="inlineStr"/>
+      <c r="O77" s="16" t="inlineStr"/>
+      <c r="P77" s="16" t="inlineStr"/>
+      <c r="Q77" s="16" t="inlineStr"/>
+      <c r="R77" s="16" t="inlineStr"/>
+      <c r="S77" s="16" t="inlineStr"/>
+      <c r="T77" s="16" t="inlineStr"/>
+      <c r="U77" s="16" t="inlineStr"/>
+      <c r="V77" s="16" t="inlineStr"/>
+      <c r="W77" s="16" t="inlineStr"/>
+      <c r="X77" s="16" t="inlineStr"/>
+      <c r="Y77" s="16" t="inlineStr"/>
+      <c r="Z77" s="16" t="inlineStr"/>
+      <c r="AA77" s="16" t="inlineStr"/>
+      <c r="AB77" s="16" t="inlineStr"/>
+      <c r="AC77" s="16" t="inlineStr"/>
+      <c r="AD77" s="16" t="inlineStr"/>
+      <c r="AE77" s="16" t="inlineStr"/>
+      <c r="AF77" s="17" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="A78" s="14" t="inlineStr">
         <is>
           <t>ITM-076</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>Cardiology</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>What are the indications for permanent pacemaker implantation in congenital complete heart block?</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>The indications for permanent pacemaker implantation in congenital complete atrioventricular block (CCAVB) are well defined across multiple guidelines, with the most current being the **2021 PACES Expert Consensus Statement** and the **2018 ACC/AHA/HRS Bradycardia Guidelines**. The recommendations are stratified by class of recommendation and vary by age group.
 **Class I (Indicated)**
@@ -8138,7 +8176,7 @@
 Mikulski MF, Well A, Shmorhun D, et al. Pacemaker Management and in-Hospital Outcomes in Neonatal Congenital Atrioventricular Block. JACC. Clinical Electrophysiology. 2023;9(9):1977-1986. doi:10.1016/j.jacep.2023.05.003.</t>
         </is>
       </c>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr">
         <is>
           <t>The indications for permanent pacemaker implantation in patients with congenital complete heart block (CCHB) are primarily determined by the presence of symptoms, the patient's age and resting heart rate, the site of the block (narrow vs. wide QRS), and the presence of underlying structural congenital heart disease or ventricular dysfunction.
 The most widely adopted guidelines come from the **2018 ACC/AHA/HRS Guidelines on the Evaluation and Management of Patients With Bradycardia** and the **2021 ESC Guidelines on Cardiac Pacing and Cardiac Resynchronization Therapy**.
@@ -8164,51 +8202,51 @@
 * **Physiological Pacing:** Because chronic right ventricular apical pacing can induce heart failure over time (pacing-induced cardiomyopathy), modern guidelines often emphasize pacing configurations that preserve ventricular function, such as left ventricular epicardial pacing in children, or cardiac resynchronization therapy (CRT) / conduction system pacing (CSP) when transvenous systems are an option.</t>
         </is>
       </c>
-      <c r="F78" s="13" t="inlineStr"/>
-      <c r="G78" s="13" t="inlineStr"/>
-      <c r="H78" s="13" t="inlineStr"/>
-      <c r="I78" s="13" t="inlineStr"/>
-      <c r="J78" s="13" t="inlineStr"/>
-      <c r="K78" s="13" t="inlineStr"/>
-      <c r="L78" s="13" t="inlineStr"/>
-      <c r="M78" s="13" t="inlineStr"/>
-      <c r="N78" s="13" t="inlineStr"/>
-      <c r="O78" s="13" t="inlineStr"/>
-      <c r="P78" s="13" t="inlineStr"/>
-      <c r="Q78" s="13" t="inlineStr"/>
-      <c r="R78" s="13" t="inlineStr"/>
-      <c r="S78" s="13" t="inlineStr"/>
-      <c r="T78" s="13" t="inlineStr"/>
-      <c r="U78" s="13" t="inlineStr"/>
-      <c r="V78" s="13" t="inlineStr"/>
-      <c r="W78" s="13" t="inlineStr"/>
-      <c r="X78" s="13" t="inlineStr"/>
-      <c r="Y78" s="13" t="inlineStr"/>
-      <c r="Z78" s="13" t="inlineStr"/>
-      <c r="AA78" s="13" t="inlineStr"/>
-      <c r="AB78" s="13" t="inlineStr"/>
-      <c r="AC78" s="13" t="inlineStr"/>
-      <c r="AD78" s="13" t="inlineStr"/>
-      <c r="AE78" s="13" t="inlineStr"/>
-      <c r="AF78" s="14" t="inlineStr"/>
+      <c r="F78" s="16" t="inlineStr"/>
+      <c r="G78" s="16" t="inlineStr"/>
+      <c r="H78" s="16" t="inlineStr"/>
+      <c r="I78" s="16" t="inlineStr"/>
+      <c r="J78" s="16" t="inlineStr"/>
+      <c r="K78" s="16" t="inlineStr"/>
+      <c r="L78" s="16" t="inlineStr"/>
+      <c r="M78" s="16" t="inlineStr"/>
+      <c r="N78" s="16" t="inlineStr"/>
+      <c r="O78" s="16" t="inlineStr"/>
+      <c r="P78" s="16" t="inlineStr"/>
+      <c r="Q78" s="16" t="inlineStr"/>
+      <c r="R78" s="16" t="inlineStr"/>
+      <c r="S78" s="16" t="inlineStr"/>
+      <c r="T78" s="16" t="inlineStr"/>
+      <c r="U78" s="16" t="inlineStr"/>
+      <c r="V78" s="16" t="inlineStr"/>
+      <c r="W78" s="16" t="inlineStr"/>
+      <c r="X78" s="16" t="inlineStr"/>
+      <c r="Y78" s="16" t="inlineStr"/>
+      <c r="Z78" s="16" t="inlineStr"/>
+      <c r="AA78" s="16" t="inlineStr"/>
+      <c r="AB78" s="16" t="inlineStr"/>
+      <c r="AC78" s="16" t="inlineStr"/>
+      <c r="AD78" s="16" t="inlineStr"/>
+      <c r="AE78" s="16" t="inlineStr"/>
+      <c r="AF78" s="17" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>ITM-077</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>Urology</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>What are the brand names, generic names, and dosages of medications used to treat overactive bladder (OAB)?</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
         <is>
           <t>The FDA-approved medications for overactive bladder span three main drug classes: **antimuscarinics (anticholinergics), β3-adrenergic agonists, and onabotulinumtoxinA**. Below is a comprehensive summary organized by class.
 **Antimuscarinics (Anticholinergics)**
@@ -8225,7 +8263,7 @@
 Would you like to explore the comparative efficacy and side effect profiles of these agents to guide selection for a specific patient population?</t>
         </is>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E79" s="15" t="inlineStr">
         <is>
           <t>### Medications for Overactive Bladder (OAB)
 OAB medications fall into two main categories: **antimuscarinics (anticholinergics)** and **beta-3 adrenergic agonists**. Here's a breakdown by drug class:
@@ -8258,51 +8296,51 @@
 This information is for educational purposes. **Always consult a healthcare provider or pharmacist** for personalized dosing, drug interactions, and to determine the most appropriate treatment, as individual needs vary. Would you like more detail on any specific medication?</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr"/>
-      <c r="G79" s="13" t="inlineStr"/>
-      <c r="H79" s="13" t="inlineStr"/>
-      <c r="I79" s="13" t="inlineStr"/>
-      <c r="J79" s="13" t="inlineStr"/>
-      <c r="K79" s="13" t="inlineStr"/>
-      <c r="L79" s="13" t="inlineStr"/>
-      <c r="M79" s="13" t="inlineStr"/>
-      <c r="N79" s="13" t="inlineStr"/>
-      <c r="O79" s="13" t="inlineStr"/>
-      <c r="P79" s="13" t="inlineStr"/>
-      <c r="Q79" s="13" t="inlineStr"/>
-      <c r="R79" s="13" t="inlineStr"/>
-      <c r="S79" s="13" t="inlineStr"/>
-      <c r="T79" s="13" t="inlineStr"/>
-      <c r="U79" s="13" t="inlineStr"/>
-      <c r="V79" s="13" t="inlineStr"/>
-      <c r="W79" s="13" t="inlineStr"/>
-      <c r="X79" s="13" t="inlineStr"/>
-      <c r="Y79" s="13" t="inlineStr"/>
-      <c r="Z79" s="13" t="inlineStr"/>
-      <c r="AA79" s="13" t="inlineStr"/>
-      <c r="AB79" s="13" t="inlineStr"/>
-      <c r="AC79" s="13" t="inlineStr"/>
-      <c r="AD79" s="13" t="inlineStr"/>
-      <c r="AE79" s="13" t="inlineStr"/>
-      <c r="AF79" s="14" t="inlineStr"/>
+      <c r="F79" s="16" t="inlineStr"/>
+      <c r="G79" s="16" t="inlineStr"/>
+      <c r="H79" s="16" t="inlineStr"/>
+      <c r="I79" s="16" t="inlineStr"/>
+      <c r="J79" s="16" t="inlineStr"/>
+      <c r="K79" s="16" t="inlineStr"/>
+      <c r="L79" s="16" t="inlineStr"/>
+      <c r="M79" s="16" t="inlineStr"/>
+      <c r="N79" s="16" t="inlineStr"/>
+      <c r="O79" s="16" t="inlineStr"/>
+      <c r="P79" s="16" t="inlineStr"/>
+      <c r="Q79" s="16" t="inlineStr"/>
+      <c r="R79" s="16" t="inlineStr"/>
+      <c r="S79" s="16" t="inlineStr"/>
+      <c r="T79" s="16" t="inlineStr"/>
+      <c r="U79" s="16" t="inlineStr"/>
+      <c r="V79" s="16" t="inlineStr"/>
+      <c r="W79" s="16" t="inlineStr"/>
+      <c r="X79" s="16" t="inlineStr"/>
+      <c r="Y79" s="16" t="inlineStr"/>
+      <c r="Z79" s="16" t="inlineStr"/>
+      <c r="AA79" s="16" t="inlineStr"/>
+      <c r="AB79" s="16" t="inlineStr"/>
+      <c r="AC79" s="16" t="inlineStr"/>
+      <c r="AD79" s="16" t="inlineStr"/>
+      <c r="AE79" s="16" t="inlineStr"/>
+      <c r="AF79" s="17" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="A80" s="14" t="inlineStr">
         <is>
           <t>ITM-078</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B80" s="14" t="inlineStr">
         <is>
           <t>Dermatology</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>What is the management of erosive pustular dermatosis of the scalp?</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>**Management of erosive pustular dermatosis of the scalp (EPDS)** is usually dermatology-led and focuses on excluding mimics, removing crusts, controlling inflammation, preventing relapse, and surveilling for skin cancer.
 1. **Confirm the diagnosis / exclude important mimics**
@@ -8325,7 +8363,7 @@
 **Typical practical regimen:** gentle crust removal + bland dressings, then **ultra-potent topical steroid for a few weeks**, taper once healed, and switch to or maintain with **tacrolimus ointment** if recurrent or steroid-dependent.</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr">
         <is>
           <t>The first-line treatment for erosive pustular dermatosis of the scalp (EPDS) is **high-potency topical corticosteroids** (e.g., clobetasol, betamethasone), with **topical calcineurin inhibitors** (tacrolimus 0.1%) recommended for maintenance therapy or as a steroid-sparing alternative. There are no formal treatment guidelines, and all available evidence is limited to case reports and case series.
 **First-Line: Topical Corticosteroids**
@@ -8347,51 +8385,51 @@
 Would you like to explore the role of photodynamic therapy protocols in more detail, including the curettage-PDT approach and its outcomes?</t>
         </is>
       </c>
-      <c r="F80" s="13" t="inlineStr"/>
-      <c r="G80" s="13" t="inlineStr"/>
-      <c r="H80" s="13" t="inlineStr"/>
-      <c r="I80" s="13" t="inlineStr"/>
-      <c r="J80" s="13" t="inlineStr"/>
-      <c r="K80" s="13" t="inlineStr"/>
-      <c r="L80" s="13" t="inlineStr"/>
-      <c r="M80" s="13" t="inlineStr"/>
-      <c r="N80" s="13" t="inlineStr"/>
-      <c r="O80" s="13" t="inlineStr"/>
-      <c r="P80" s="13" t="inlineStr"/>
-      <c r="Q80" s="13" t="inlineStr"/>
-      <c r="R80" s="13" t="inlineStr"/>
-      <c r="S80" s="13" t="inlineStr"/>
-      <c r="T80" s="13" t="inlineStr"/>
-      <c r="U80" s="13" t="inlineStr"/>
-      <c r="V80" s="13" t="inlineStr"/>
-      <c r="W80" s="13" t="inlineStr"/>
-      <c r="X80" s="13" t="inlineStr"/>
-      <c r="Y80" s="13" t="inlineStr"/>
-      <c r="Z80" s="13" t="inlineStr"/>
-      <c r="AA80" s="13" t="inlineStr"/>
-      <c r="AB80" s="13" t="inlineStr"/>
-      <c r="AC80" s="13" t="inlineStr"/>
-      <c r="AD80" s="13" t="inlineStr"/>
-      <c r="AE80" s="13" t="inlineStr"/>
-      <c r="AF80" s="14" t="inlineStr"/>
+      <c r="F80" s="16" t="inlineStr"/>
+      <c r="G80" s="16" t="inlineStr"/>
+      <c r="H80" s="16" t="inlineStr"/>
+      <c r="I80" s="16" t="inlineStr"/>
+      <c r="J80" s="16" t="inlineStr"/>
+      <c r="K80" s="16" t="inlineStr"/>
+      <c r="L80" s="16" t="inlineStr"/>
+      <c r="M80" s="16" t="inlineStr"/>
+      <c r="N80" s="16" t="inlineStr"/>
+      <c r="O80" s="16" t="inlineStr"/>
+      <c r="P80" s="16" t="inlineStr"/>
+      <c r="Q80" s="16" t="inlineStr"/>
+      <c r="R80" s="16" t="inlineStr"/>
+      <c r="S80" s="16" t="inlineStr"/>
+      <c r="T80" s="16" t="inlineStr"/>
+      <c r="U80" s="16" t="inlineStr"/>
+      <c r="V80" s="16" t="inlineStr"/>
+      <c r="W80" s="16" t="inlineStr"/>
+      <c r="X80" s="16" t="inlineStr"/>
+      <c r="Y80" s="16" t="inlineStr"/>
+      <c r="Z80" s="16" t="inlineStr"/>
+      <c r="AA80" s="16" t="inlineStr"/>
+      <c r="AB80" s="16" t="inlineStr"/>
+      <c r="AC80" s="16" t="inlineStr"/>
+      <c r="AD80" s="16" t="inlineStr"/>
+      <c r="AE80" s="16" t="inlineStr"/>
+      <c r="AF80" s="17" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="A81" s="14" t="inlineStr">
         <is>
           <t>ITM-079</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>Oncology / Hematology</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>What imaging modality does the NCCN recommend for staging a patient with T2A, N0 non-small cell lung cancer to guide treatment decisions?</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>For a patient with **T2a, N0 NSCLC** (stage IB if peripheral, or stage I if central), the NCCN Guidelines recommend the following imaging modalities as part of the pretreatment evaluation:
 1. **FDG-PET/CT scan** (skull base to mid-thigh, if not previously done) — the primary staging imaging modality
@@ -8409,7 +8447,7 @@
 Would you like to explore the specific biomarker testing and perioperative therapy evaluation recommended for stage IB (T2a, N0) NSCLC before surgical resection?</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="15" t="inlineStr">
         <is>
           <t>I have sufficient information to answer this question.
 For staging a patient with clinical stage T2a, N0 non-small cell lung cancer (NSCLC), the NCCN recommends **whole-body FDG-PET/CT** (fluorodeoxyglucose positron emission tomography/computed tomography) as the key imaging modality to guide treatment decisions.
@@ -8424,33 +8462,33 @@
 **In summary:** The cornerstone modality the NCCN recommends for staging T2a, N0 NSCLC is **whole-body FDG-PET/CT** (following an initial contrast-enhanced chest/upper abdomen CT), with the addition of **brain MRI** for this stage IB disease.</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr"/>
-      <c r="G81" s="13" t="inlineStr"/>
-      <c r="H81" s="13" t="inlineStr"/>
-      <c r="I81" s="13" t="inlineStr"/>
-      <c r="J81" s="13" t="inlineStr"/>
-      <c r="K81" s="13" t="inlineStr"/>
-      <c r="L81" s="13" t="inlineStr"/>
-      <c r="M81" s="13" t="inlineStr"/>
-      <c r="N81" s="13" t="inlineStr"/>
-      <c r="O81" s="13" t="inlineStr"/>
-      <c r="P81" s="13" t="inlineStr"/>
-      <c r="Q81" s="13" t="inlineStr"/>
-      <c r="R81" s="13" t="inlineStr"/>
-      <c r="S81" s="13" t="inlineStr"/>
-      <c r="T81" s="13" t="inlineStr"/>
-      <c r="U81" s="13" t="inlineStr"/>
-      <c r="V81" s="13" t="inlineStr"/>
-      <c r="W81" s="13" t="inlineStr"/>
-      <c r="X81" s="13" t="inlineStr"/>
-      <c r="Y81" s="13" t="inlineStr"/>
-      <c r="Z81" s="13" t="inlineStr"/>
-      <c r="AA81" s="13" t="inlineStr"/>
-      <c r="AB81" s="13" t="inlineStr"/>
-      <c r="AC81" s="13" t="inlineStr"/>
-      <c r="AD81" s="13" t="inlineStr"/>
-      <c r="AE81" s="13" t="inlineStr"/>
-      <c r="AF81" s="14" t="inlineStr"/>
+      <c r="F81" s="16" t="inlineStr"/>
+      <c r="G81" s="16" t="inlineStr"/>
+      <c r="H81" s="16" t="inlineStr"/>
+      <c r="I81" s="16" t="inlineStr"/>
+      <c r="J81" s="16" t="inlineStr"/>
+      <c r="K81" s="16" t="inlineStr"/>
+      <c r="L81" s="16" t="inlineStr"/>
+      <c r="M81" s="16" t="inlineStr"/>
+      <c r="N81" s="16" t="inlineStr"/>
+      <c r="O81" s="16" t="inlineStr"/>
+      <c r="P81" s="16" t="inlineStr"/>
+      <c r="Q81" s="16" t="inlineStr"/>
+      <c r="R81" s="16" t="inlineStr"/>
+      <c r="S81" s="16" t="inlineStr"/>
+      <c r="T81" s="16" t="inlineStr"/>
+      <c r="U81" s="16" t="inlineStr"/>
+      <c r="V81" s="16" t="inlineStr"/>
+      <c r="W81" s="16" t="inlineStr"/>
+      <c r="X81" s="16" t="inlineStr"/>
+      <c r="Y81" s="16" t="inlineStr"/>
+      <c r="Z81" s="16" t="inlineStr"/>
+      <c r="AA81" s="16" t="inlineStr"/>
+      <c r="AB81" s="16" t="inlineStr"/>
+      <c r="AC81" s="16" t="inlineStr"/>
+      <c r="AD81" s="16" t="inlineStr"/>
+      <c r="AE81" s="16" t="inlineStr"/>
+      <c r="AF81" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="26">
